--- a/Methanol/Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna/Datenbank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D485EC8E-1ED9-48D2-BD39-808F219BD247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7669CA18-678E-4C19-8005-BB134C241C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1442,18 +1442,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1544,137 +1538,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1682,9 +1568,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1698,19 +1581,127 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -2046,1296 +2037,1296 @@
   <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="44" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="43" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="44" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="44" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="53" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="44" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="44" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="44" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="44" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="44" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="44" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="44"/>
+    <col min="1" max="1" width="10.88671875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="5" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="41" t="s">
+      <c r="B1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="41" t="s">
+      <c r="C1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="41" t="s">
+      <c r="D1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="42" t="s">
+      <c r="E1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="43"/>
+      <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="47" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="47" t="s">
+      <c r="D2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="8">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="47" t="s">
+      <c r="F2" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="49"/>
+      <c r="A3" s="42"/>
       <c r="B3" s="50"/>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="44" t="s">
+      <c r="D3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="51">
+      <c r="E3" s="9">
         <v>50</v>
       </c>
-      <c r="F3" s="44" t="s">
+      <c r="F3" s="6" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="49"/>
+      <c r="A4" s="42"/>
       <c r="B4" s="50"/>
-      <c r="C4" s="44" t="s">
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="52">
+      <c r="E4" s="10">
         <v>1000</v>
       </c>
-      <c r="F4" s="44" t="s">
+      <c r="F4" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="49"/>
+      <c r="A5" s="42"/>
       <c r="B5" s="50"/>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="53">
+      <c r="E5" s="11">
         <v>0.03</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="49"/>
+      <c r="A6" s="42"/>
       <c r="B6" s="50"/>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="12">
         <v>20</v>
       </c>
-      <c r="F6" s="44" t="s">
+      <c r="F6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="49"/>
+      <c r="A7" s="42"/>
       <c r="B7" s="50"/>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="53">
+      <c r="E7" s="11">
         <v>0.08</v>
       </c>
-      <c r="F7" s="44" t="s">
+      <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="49"/>
-      <c r="B8" s="55" t="s">
+      <c r="A8" s="42"/>
+      <c r="B8" s="53" t="s">
         <v>231</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="56" t="s">
+      <c r="D8" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="57">
+      <c r="E8" s="14">
         <v>1.5</v>
       </c>
-      <c r="F8" s="56" t="s">
+      <c r="F8" s="13" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="49"/>
+      <c r="A9" s="42"/>
       <c r="B9" s="50"/>
-      <c r="C9" s="44" t="s">
+      <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E9" s="51">
+      <c r="E9" s="9">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="44" t="s">
+      <c r="F9" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="49"/>
+      <c r="A10" s="42"/>
       <c r="B10" s="50"/>
-      <c r="C10" s="89" t="s">
+      <c r="C10" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="89" t="s">
+      <c r="D10" s="36" t="s">
         <v>235</v>
       </c>
-      <c r="E10" s="93">
+      <c r="E10" s="40">
         <v>0</v>
       </c>
-      <c r="F10" s="90" t="s">
+      <c r="F10" s="37" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="49"/>
+      <c r="A11" s="42"/>
       <c r="B11" s="50"/>
-      <c r="C11" s="89" t="s">
+      <c r="C11" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="89" t="s">
+      <c r="D11" s="36" t="s">
         <v>236</v>
       </c>
-      <c r="E11" s="91">
-        <f>0.05*5000</f>
-        <v>250</v>
-      </c>
-      <c r="F11" s="92" t="s">
+      <c r="E11" s="38">
+        <f>0.05*5110</f>
+        <v>255.5</v>
+      </c>
+      <c r="F11" s="39" t="s">
         <v>396</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="49"/>
+      <c r="A12" s="42"/>
       <c r="B12" s="50"/>
-      <c r="C12" s="44" t="s">
+      <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E12" s="51">
+      <c r="E12" s="9">
         <v>0.189</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="6" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="49"/>
+      <c r="A13" s="42"/>
       <c r="B13" s="50"/>
-      <c r="C13" s="44" t="s">
+      <c r="C13" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E13" s="51">
+      <c r="E13" s="9">
         <v>1.375</v>
       </c>
-      <c r="F13" s="44" t="s">
+      <c r="F13" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="49"/>
+      <c r="A14" s="42"/>
       <c r="B14" s="50"/>
-      <c r="C14" s="44" t="s">
+      <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="E14" s="54">
+      <c r="E14" s="12">
         <v>25</v>
       </c>
-      <c r="F14" s="44" t="s">
+      <c r="F14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="49"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="59" t="s">
+      <c r="A15" s="42"/>
+      <c r="B15" s="54"/>
+      <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="E15" s="60">
+      <c r="E15" s="16">
         <v>0.08</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="49"/>
-      <c r="B16" s="55" t="s">
+      <c r="A16" s="42"/>
+      <c r="B16" s="53" t="s">
         <v>273</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="56" t="s">
+      <c r="D16" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="17">
         <v>3.7</v>
       </c>
-      <c r="F16" s="56" t="s">
+      <c r="F16" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="49"/>
+      <c r="A17" s="42"/>
       <c r="B17" s="50"/>
-      <c r="C17" s="44" t="s">
+      <c r="C17" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="44" t="s">
+      <c r="D17" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E17" s="53">
+      <c r="E17" s="11">
         <v>0.27</v>
       </c>
-      <c r="F17" s="44" t="s">
+      <c r="F17" s="6" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="49"/>
+      <c r="A18" s="42"/>
       <c r="B18" s="50"/>
-      <c r="C18" s="44" t="s">
+      <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="D18" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E18" s="53">
+      <c r="E18" s="11">
         <v>700</v>
       </c>
-      <c r="F18" s="44" t="s">
+      <c r="F18" s="6" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="49"/>
+      <c r="A19" s="42"/>
       <c r="B19" s="50"/>
-      <c r="C19" s="44" t="s">
+      <c r="C19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="44" t="s">
+      <c r="D19" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E19" s="53">
+      <c r="E19" s="11">
         <v>0.02</v>
       </c>
-      <c r="F19" s="44" t="s">
+      <c r="F19" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="49"/>
+      <c r="A20" s="42"/>
       <c r="B20" s="50"/>
-      <c r="C20" s="44" t="s">
+      <c r="C20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="11">
         <v>20</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="49"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="59" t="s">
+      <c r="A21" s="42"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="E21" s="60">
+      <c r="E21" s="16">
         <v>0.05</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="49"/>
-      <c r="B22" s="88" t="s">
+      <c r="A22" s="42"/>
+      <c r="B22" s="55" t="s">
         <v>342</v>
       </c>
-      <c r="C22" s="44" t="s">
+      <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="9">
         <v>0.2</v>
       </c>
-      <c r="F22" s="44" t="s">
+      <c r="F22" s="6" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="49"/>
-      <c r="B23" s="88"/>
-      <c r="C23" s="44" t="s">
+      <c r="A23" s="42"/>
+      <c r="B23" s="55"/>
+      <c r="C23" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="D23" s="44" t="s">
+      <c r="D23" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="E23" s="51">
+      <c r="E23" s="9">
         <v>0.92800000000000005</v>
       </c>
-      <c r="F23" s="44" t="s">
+      <c r="F23" s="6" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49"/>
-      <c r="B24" s="88"/>
-      <c r="C24" s="44" t="s">
+      <c r="A24" s="42"/>
+      <c r="B24" s="55"/>
+      <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="44" t="s">
+      <c r="D24" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="E24" s="51">
+      <c r="E24" s="9">
         <v>1640</v>
       </c>
-      <c r="F24" s="44" t="s">
+      <c r="F24" s="6" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
-      <c r="B25" s="88"/>
-      <c r="C25" s="44" t="s">
+      <c r="A25" s="42"/>
+      <c r="B25" s="55"/>
+      <c r="C25" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="D25" s="44" t="s">
+      <c r="D25" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="E25" s="53">
+      <c r="E25" s="11">
         <v>0.04</v>
       </c>
-      <c r="F25" s="44" t="s">
+      <c r="F25" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
-      <c r="B26" s="88"/>
-      <c r="C26" s="44" t="s">
+      <c r="A26" s="42"/>
+      <c r="B26" s="55"/>
+      <c r="C26" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D26" s="44" t="s">
+      <c r="D26" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E26" s="53">
+      <c r="E26" s="11">
         <v>2.5</v>
       </c>
-      <c r="F26" s="44" t="s">
+      <c r="F26" s="6" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="49"/>
-      <c r="B27" s="88"/>
-      <c r="C27" s="44" t="s">
+      <c r="A27" s="42"/>
+      <c r="B27" s="55"/>
+      <c r="C27" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="D27" s="44" t="s">
+      <c r="D27" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="E27" s="53">
+      <c r="E27" s="11">
         <v>1.5</v>
       </c>
-      <c r="F27" s="44" t="s">
+      <c r="F27" s="6" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="44" t="s">
+      <c r="A28" s="42"/>
+      <c r="B28" s="55"/>
+      <c r="C28" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="D28" s="44" t="s">
+      <c r="D28" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="11">
         <v>1.5E-3</v>
       </c>
-      <c r="F28" s="44" t="s">
+      <c r="F28" s="6" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="49"/>
-      <c r="B29" s="88"/>
-      <c r="C29" s="44" t="s">
+      <c r="A29" s="42"/>
+      <c r="B29" s="55"/>
+      <c r="C29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="44" t="s">
+      <c r="D29" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="E29" s="54">
+      <c r="E29" s="12">
         <v>25</v>
       </c>
-      <c r="F29" s="44" t="s">
+      <c r="F29" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="49"/>
-      <c r="B30" s="88"/>
-      <c r="C30" s="44" t="s">
+      <c r="A30" s="42"/>
+      <c r="B30" s="55"/>
+      <c r="C30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="44" t="s">
+      <c r="D30" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="E30" s="53">
+      <c r="E30" s="11">
         <v>0.08</v>
       </c>
-      <c r="F30" s="44" t="s">
+      <c r="F30" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="47" t="s">
+      <c r="D31" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="63">
+      <c r="E31" s="18">
         <v>490</v>
       </c>
-      <c r="F31" s="47" t="s">
+      <c r="F31" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="49"/>
-      <c r="B32" s="64"/>
-      <c r="C32" s="44" t="s">
+      <c r="A32" s="42"/>
+      <c r="B32" s="46"/>
+      <c r="C32" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="44" t="s">
+      <c r="D32" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="53">
+      <c r="E32" s="11">
         <v>0.01</v>
       </c>
-      <c r="F32" s="44" t="s">
+      <c r="F32" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="49"/>
-      <c r="B33" s="64"/>
-      <c r="C33" s="44" t="s">
+      <c r="A33" s="42"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="44" t="s">
+      <c r="D33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="54">
+      <c r="E33" s="12">
         <v>20</v>
       </c>
-      <c r="F33" s="44" t="s">
+      <c r="F33" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="49"/>
-      <c r="B34" s="64"/>
-      <c r="C34" s="44" t="s">
+      <c r="A34" s="42"/>
+      <c r="B34" s="46"/>
+      <c r="C34" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="44" t="s">
+      <c r="D34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="65">
+      <c r="E34" s="19">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F34" s="44" t="s">
+      <c r="F34" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="49"/>
-      <c r="B35" s="64"/>
-      <c r="C35" s="44" t="s">
+      <c r="A35" s="42"/>
+      <c r="B35" s="46"/>
+      <c r="C35" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="44" t="s">
+      <c r="D35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="53">
+      <c r="E35" s="11">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F35" s="44" t="s">
+      <c r="F35" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="49"/>
-      <c r="B36" s="64"/>
-      <c r="C36" s="44" t="s">
+      <c r="A36" s="42"/>
+      <c r="B36" s="46"/>
+      <c r="C36" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="44" t="s">
+      <c r="D36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="53">
+      <c r="E36" s="11">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F36" s="44" t="s">
+      <c r="F36" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="49"/>
-      <c r="B37" s="64"/>
-      <c r="C37" s="44" t="s">
+      <c r="A37" s="42"/>
+      <c r="B37" s="46"/>
+      <c r="C37" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="44" t="s">
+      <c r="D37" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="53">
+      <c r="E37" s="11">
         <v>0.05</v>
       </c>
-      <c r="F37" s="44" t="s">
+      <c r="F37" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="49"/>
-      <c r="B38" s="66"/>
-      <c r="C38" s="59" t="s">
+      <c r="A38" s="42"/>
+      <c r="B38" s="47"/>
+      <c r="C38" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="59" t="s">
+      <c r="D38" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="60">
+      <c r="E38" s="16">
         <v>0</v>
       </c>
-      <c r="F38" s="59" t="s">
+      <c r="F38" s="15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="49"/>
-      <c r="B39" s="67" t="s">
+      <c r="A39" s="42"/>
+      <c r="B39" s="48" t="s">
         <v>317</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="C39" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="47" t="s">
+      <c r="D39" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="E39" s="63">
+      <c r="E39" s="18">
         <v>2.83</v>
       </c>
-      <c r="F39" s="47" t="s">
+      <c r="F39" s="7" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="49"/>
-      <c r="B40" s="64"/>
-      <c r="C40" s="44" t="s">
+      <c r="A40" s="42"/>
+      <c r="B40" s="46"/>
+      <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="44" t="s">
+      <c r="D40" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="E40" s="53">
+      <c r="E40" s="11">
         <v>0.03</v>
       </c>
-      <c r="F40" s="44" t="s">
+      <c r="F40" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="49"/>
-      <c r="B41" s="64"/>
-      <c r="C41" s="44" t="s">
+      <c r="A41" s="42"/>
+      <c r="B41" s="46"/>
+      <c r="C41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="44" t="s">
+      <c r="D41" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="E41" s="54">
+      <c r="E41" s="12">
         <v>30</v>
       </c>
-      <c r="F41" s="44" t="s">
+      <c r="F41" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="49"/>
-      <c r="B42" s="64"/>
-      <c r="C42" s="44" t="s">
+      <c r="A42" s="42"/>
+      <c r="B42" s="46"/>
+      <c r="C42" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="44" t="s">
+      <c r="D42" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="E42" s="53">
+      <c r="E42" s="11">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F42" s="44" t="s">
+      <c r="F42" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="49"/>
-      <c r="B43" s="64"/>
-      <c r="C43" s="44" t="s">
+      <c r="A43" s="42"/>
+      <c r="B43" s="46"/>
+      <c r="C43" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="44" t="s">
+      <c r="D43" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="E43" s="53">
+      <c r="E43" s="11">
         <v>0.98</v>
       </c>
-      <c r="F43" s="44" t="s">
+      <c r="F43" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="49"/>
-      <c r="B44" s="64"/>
-      <c r="C44" s="44" t="s">
+      <c r="A44" s="42"/>
+      <c r="B44" s="46"/>
+      <c r="C44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="44" t="s">
+      <c r="D44" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E44" s="53">
+      <c r="E44" s="11">
         <v>0.98</v>
       </c>
-      <c r="F44" s="44" t="s">
+      <c r="F44" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="49"/>
-      <c r="B45" s="64"/>
-      <c r="C45" s="44" t="s">
+      <c r="A45" s="42"/>
+      <c r="B45" s="46"/>
+      <c r="C45" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="44" t="s">
+      <c r="D45" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="E45" s="53">
+      <c r="E45" s="11">
         <v>0.05</v>
       </c>
-      <c r="F45" s="44" t="s">
+      <c r="F45" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="49"/>
-      <c r="B46" s="64"/>
-      <c r="C46" s="59" t="s">
+      <c r="A46" s="42"/>
+      <c r="B46" s="46"/>
+      <c r="C46" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="59" t="s">
+      <c r="D46" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="E46" s="60">
+      <c r="E46" s="16">
         <v>0</v>
       </c>
-      <c r="F46" s="59" t="s">
+      <c r="F46" s="15" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="49"/>
-      <c r="B47" s="67" t="s">
+      <c r="A47" s="42"/>
+      <c r="B47" s="48" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="56" t="s">
+      <c r="C47" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="56" t="s">
+      <c r="D47" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="61">
+      <c r="E47" s="17">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F47" s="56" t="s">
+      <c r="F47" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="49"/>
+      <c r="A48" s="42"/>
       <c r="B48" s="50"/>
-      <c r="C48" s="44" t="s">
+      <c r="C48" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="44" t="s">
+      <c r="D48" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="51">
+      <c r="E48" s="9">
         <f>E49*4</f>
         <v>424</v>
       </c>
-      <c r="F48" s="44" t="s">
+      <c r="F48" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="49"/>
+      <c r="A49" s="42"/>
       <c r="B49" s="50"/>
-      <c r="C49" s="44" t="s">
+      <c r="C49" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="44" t="s">
+      <c r="D49" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="51">
+      <c r="E49" s="9">
         <v>106</v>
       </c>
-      <c r="F49" s="44" t="s">
+      <c r="F49" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="49"/>
+      <c r="A50" s="42"/>
       <c r="B50" s="50"/>
-      <c r="C50" s="44" t="s">
+      <c r="C50" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D50" s="44" t="s">
+      <c r="D50" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="53">
+      <c r="E50" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F50" s="44" t="s">
+      <c r="F50" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="49"/>
+      <c r="A51" s="42"/>
       <c r="B51" s="50"/>
-      <c r="C51" s="44" t="s">
+      <c r="C51" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D51" s="44" t="s">
+      <c r="D51" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="53">
+      <c r="E51" s="11">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F51" s="44" t="s">
+      <c r="F51" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="49"/>
+      <c r="A52" s="42"/>
       <c r="B52" s="50"/>
-      <c r="C52" s="44" t="s">
+      <c r="C52" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="44" t="s">
+      <c r="D52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="53">
+      <c r="E52" s="11">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F52" s="44" t="s">
+      <c r="F52" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="49"/>
+      <c r="A53" s="42"/>
       <c r="B53" s="50"/>
-      <c r="C53" s="44" t="s">
+      <c r="C53" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D53" s="44" t="s">
+      <c r="D53" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="51">
+      <c r="E53" s="9">
         <v>0.25</v>
       </c>
-      <c r="F53" s="44" t="s">
+      <c r="F53" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="49"/>
+      <c r="A54" s="42"/>
       <c r="B54" s="50"/>
-      <c r="C54" s="44" t="s">
+      <c r="C54" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="44" t="s">
+      <c r="D54" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="53">
+      <c r="E54" s="11">
         <v>0</v>
       </c>
-      <c r="F54" s="44" t="s">
+      <c r="F54" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="49"/>
+      <c r="A55" s="42"/>
       <c r="B55" s="50"/>
-      <c r="C55" s="44" t="s">
+      <c r="C55" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="44" t="s">
+      <c r="D55" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="54">
+      <c r="E55" s="12">
         <v>15</v>
       </c>
-      <c r="F55" s="44" t="s">
+      <c r="F55" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="68"/>
-      <c r="B56" s="69"/>
-      <c r="C56" s="70" t="s">
+      <c r="A56" s="43"/>
+      <c r="B56" s="51"/>
+      <c r="C56" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="70" t="s">
+      <c r="D56" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="71">
+      <c r="E56" s="21">
         <v>0.1</v>
       </c>
-      <c r="F56" s="70" t="s">
+      <c r="F56" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="72" t="s">
+      <c r="B57" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="73" t="s">
+      <c r="C57" s="23" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="73" t="s">
+      <c r="D57" s="23" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="74">
+      <c r="E57" s="24">
         <v>0.1699</v>
       </c>
-      <c r="F57" s="73" t="s">
+      <c r="F57" s="23" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="75"/>
-      <c r="B58" s="76" t="s">
+      <c r="A58" s="44"/>
+      <c r="B58" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="C58" s="77" t="s">
+      <c r="C58" s="26" t="s">
         <v>383</v>
       </c>
-      <c r="D58" s="77" t="s">
+      <c r="D58" s="26" t="s">
         <v>384</v>
       </c>
-      <c r="E58" s="78">
+      <c r="E58" s="27">
         <v>5</v>
       </c>
-      <c r="F58" s="77" t="s">
+      <c r="F58" s="26" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="75"/>
-      <c r="B59" s="79" t="s">
+      <c r="A59" s="44"/>
+      <c r="B59" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="C59" s="80" t="s">
+      <c r="C59" s="29" t="s">
         <v>344</v>
       </c>
-      <c r="D59" s="80" t="s">
+      <c r="D59" s="29" t="s">
         <v>345</v>
       </c>
-      <c r="E59" s="81">
+      <c r="E59" s="30">
         <v>0</v>
       </c>
-      <c r="F59" s="80" t="s">
+      <c r="F59" s="29" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="49"/>
-      <c r="B60" s="67" t="s">
+      <c r="A60" s="42"/>
+      <c r="B60" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="C60" s="56" t="s">
+      <c r="C60" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D60" s="56" t="s">
+      <c r="D60" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E60" s="61">
+      <c r="E60" s="17">
         <v>0.99</v>
       </c>
-      <c r="F60" s="56" t="s">
+      <c r="F60" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="49"/>
-      <c r="B61" s="64"/>
-      <c r="C61" s="44" t="s">
+      <c r="A61" s="42"/>
+      <c r="B61" s="46"/>
+      <c r="C61" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D61" s="44" t="s">
+      <c r="D61" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="82">
+      <c r="E61" s="31">
         <v>1100</v>
       </c>
-      <c r="F61" s="44" t="s">
+      <c r="F61" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="49"/>
-      <c r="B62" s="64"/>
-      <c r="C62" s="44" t="s">
+      <c r="A62" s="42"/>
+      <c r="B62" s="46"/>
+      <c r="C62" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D62" s="44" t="s">
+      <c r="D62" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="82">
+      <c r="E62" s="31">
         <v>17.84</v>
       </c>
-      <c r="F62" s="44" t="s">
+      <c r="F62" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="49"/>
-      <c r="B63" s="64"/>
-      <c r="C63" s="44" t="s">
+      <c r="A63" s="42"/>
+      <c r="B63" s="46"/>
+      <c r="C63" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D63" s="44" t="s">
+      <c r="D63" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E63" s="51">
+      <c r="E63" s="9">
         <v>0</v>
       </c>
-      <c r="F63" s="44" t="s">
+      <c r="F63" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="49"/>
-      <c r="B64" s="64"/>
-      <c r="C64" s="44" t="s">
+      <c r="A64" s="42"/>
+      <c r="B64" s="46"/>
+      <c r="C64" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D64" s="44" t="s">
+      <c r="D64" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E64" s="54">
+      <c r="E64" s="12">
         <v>25</v>
       </c>
-      <c r="F64" s="44" t="s">
+      <c r="F64" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="49"/>
-      <c r="B65" s="64"/>
-      <c r="C65" s="44" t="s">
+      <c r="A65" s="42"/>
+      <c r="B65" s="46"/>
+      <c r="C65" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D65" s="44" t="s">
+      <c r="D65" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E65" s="51">
+      <c r="E65" s="9">
         <v>1000000</v>
       </c>
-      <c r="F65" s="44" t="s">
+      <c r="F65" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="49"/>
-      <c r="B66" s="66"/>
-      <c r="C66" s="59" t="s">
+      <c r="A66" s="42"/>
+      <c r="B66" s="47"/>
+      <c r="C66" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D66" s="59" t="s">
+      <c r="D66" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E66" s="60">
+      <c r="E66" s="16">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F66" s="59" t="s">
+      <c r="F66" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="49"/>
-      <c r="B67" s="67" t="s">
+      <c r="A67" s="42"/>
+      <c r="B67" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="56" t="s">
+      <c r="C67" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D67" s="56" t="s">
+      <c r="D67" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E67" s="61">
+      <c r="E67" s="17">
         <v>0.997</v>
       </c>
-      <c r="F67" s="56" t="s">
+      <c r="F67" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="49"/>
-      <c r="B68" s="64"/>
-      <c r="C68" s="44" t="s">
+      <c r="A68" s="42"/>
+      <c r="B68" s="46"/>
+      <c r="C68" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D68" s="44" t="s">
+      <c r="D68" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E68" s="82">
+      <c r="E68" s="31">
         <v>1080</v>
       </c>
-      <c r="F68" s="44" t="s">
+      <c r="F68" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="49"/>
-      <c r="B69" s="64"/>
-      <c r="C69" s="44" t="s">
+      <c r="A69" s="42"/>
+      <c r="B69" s="46"/>
+      <c r="C69" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D69" s="44" t="s">
+      <c r="D69" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E69" s="82">
+      <c r="E69" s="31">
         <v>12.68</v>
       </c>
-      <c r="F69" s="44" t="s">
+      <c r="F69" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="49"/>
-      <c r="B70" s="64"/>
-      <c r="C70" s="44" t="s">
+      <c r="A70" s="42"/>
+      <c r="B70" s="46"/>
+      <c r="C70" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D70" s="44" t="s">
+      <c r="D70" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E70" s="83">
+      <c r="E70" s="32">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F70" s="44" t="s">
+      <c r="F70" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="49"/>
-      <c r="B71" s="64"/>
-      <c r="C71" s="44" t="s">
+      <c r="A71" s="42"/>
+      <c r="B71" s="46"/>
+      <c r="C71" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D71" s="44" t="s">
+      <c r="D71" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E71" s="54">
+      <c r="E71" s="12">
         <v>25</v>
       </c>
-      <c r="F71" s="44" t="s">
+      <c r="F71" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="49"/>
-      <c r="B72" s="64"/>
-      <c r="C72" s="44" t="s">
+      <c r="A72" s="42"/>
+      <c r="B72" s="46"/>
+      <c r="C72" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D72" s="44" t="s">
+      <c r="D72" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E72" s="84">
+      <c r="E72" s="33">
         <v>1000000</v>
       </c>
-      <c r="F72" s="44" t="s">
+      <c r="F72" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="68"/>
-      <c r="B73" s="85"/>
-      <c r="C73" s="70" t="s">
+      <c r="A73" s="43"/>
+      <c r="B73" s="49"/>
+      <c r="C73" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D73" s="70" t="s">
+      <c r="D73" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="E73" s="71">
+      <c r="E73" s="21">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F73" s="70" t="s">
+      <c r="F73" s="20" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="45" t="s">
+      <c r="A74" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B74" s="86" t="s">
+      <c r="B74" s="34" t="s">
         <v>73</v>
       </c>
-      <c r="C74" s="73" t="s">
+      <c r="C74" s="23" t="s">
         <v>77</v>
       </c>
-      <c r="D74" s="73" t="s">
+      <c r="D74" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="E74" s="74">
+      <c r="E74" s="24">
         <v>-1E-4</v>
       </c>
-      <c r="F74" s="73" t="s">
+      <c r="F74" s="23" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="49"/>
-      <c r="B75" s="43" t="s">
+      <c r="A75" s="42"/>
+      <c r="B75" s="5" t="s">
         <v>299</v>
       </c>
-      <c r="C75" s="44" t="s">
+      <c r="C75" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="D75" s="44" t="s">
+      <c r="D75" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E75" s="53">
+      <c r="E75" s="11">
         <v>-1E-4</v>
       </c>
-      <c r="F75" s="44" t="s">
+      <c r="F75" s="6" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="49"/>
-      <c r="B76" s="87" t="s">
+      <c r="A76" s="42"/>
+      <c r="B76" s="35" t="s">
         <v>79</v>
       </c>
-      <c r="C76" s="77" t="s">
+      <c r="C76" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="D76" s="77" t="s">
+      <c r="D76" s="26" t="s">
         <v>81</v>
       </c>
-      <c r="E76" s="78">
+      <c r="E76" s="27">
         <v>-1.5</v>
       </c>
-      <c r="F76" s="77" t="s">
+      <c r="F76" s="26" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="68"/>
-      <c r="B77" s="41" t="s">
+      <c r="A77" s="43"/>
+      <c r="B77" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C77" s="70" t="s">
+      <c r="C77" s="20" t="s">
         <v>274</v>
       </c>
-      <c r="D77" s="70" t="s">
+      <c r="D77" s="20" t="s">
         <v>272</v>
       </c>
-      <c r="E77" s="71">
+      <c r="E77" s="21">
         <v>-0.6</v>
       </c>
-      <c r="F77" s="70" t="s">
+      <c r="F77" s="20" t="s">
         <v>275</v>
       </c>
     </row>
@@ -3366,2022 +3357,2011 @@
   <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="14.5546875" style="59" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="59" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="59" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" style="59" customWidth="1"/>
+    <col min="6" max="6" width="37.5546875" style="59" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="59"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="56" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="57" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="57" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="60" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="61" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="62" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="62" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="63"/>
+      <c r="F2" s="62" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="25"/>
-      <c r="B3" s="33"/>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="64"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="59" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="66"/>
+      <c r="F3" s="59" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="25"/>
-      <c r="B4" s="33"/>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="1" t="s">
+      <c r="E4" s="67"/>
+      <c r="F4" s="59" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="25"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="64"/>
+      <c r="B5" s="65"/>
+      <c r="C5" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="68"/>
+      <c r="F5" s="59" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="25"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="1" t="s">
+      <c r="A6" s="64"/>
+      <c r="B6" s="65"/>
+      <c r="C6" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="59" t="s">
         <v>144</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="69"/>
+      <c r="F6" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="25"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="64"/>
+      <c r="B7" s="65"/>
+      <c r="C7" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="59" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="69"/>
+      <c r="F7" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="1" t="s">
+      <c r="A8" s="64"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="59" t="s">
         <v>197</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="1" t="s">
+      <c r="E8" s="69"/>
+      <c r="F8" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="1" t="s">
+      <c r="A9" s="64"/>
+      <c r="B9" s="65"/>
+      <c r="C9" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="59" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="1" t="s">
+      <c r="E9" s="69"/>
+      <c r="F9" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="1" t="s">
+      <c r="A10" s="64"/>
+      <c r="B10" s="65"/>
+      <c r="C10" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="59" t="s">
         <v>196</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="1" t="s">
+      <c r="E10" s="69"/>
+      <c r="F10" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="25"/>
-      <c r="B11" s="33"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="65"/>
+      <c r="E11" s="68"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="25"/>
-      <c r="B12" s="36" t="s">
+      <c r="A12" s="64"/>
+      <c r="B12" s="70" t="s">
         <v>231</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="71" t="s">
         <v>247</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11" t="s">
+      <c r="E12" s="72"/>
+      <c r="F12" s="71" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="25"/>
-      <c r="B13" s="33"/>
-      <c r="C13" s="1" t="s">
+      <c r="A13" s="64"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="59" t="s">
         <v>255</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="59" t="s">
         <v>298</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="1" t="s">
+      <c r="E13" s="66"/>
+      <c r="F13" s="59" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="25"/>
-      <c r="B14" s="33"/>
-      <c r="C14" s="1" t="s">
+      <c r="A14" s="64"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="59" t="s">
         <v>248</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="66"/>
+      <c r="F14" s="66" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="25"/>
-      <c r="B15" s="33"/>
-      <c r="C15" s="1" t="s">
+      <c r="A15" s="64"/>
+      <c r="B15" s="65"/>
+      <c r="C15" s="59" t="s">
         <v>256</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="59" t="s">
         <v>257</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="68"/>
+      <c r="F15" s="59" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="25"/>
-      <c r="B16" s="33"/>
-      <c r="C16" s="1" t="s">
+      <c r="A16" s="64"/>
+      <c r="B16" s="65"/>
+      <c r="C16" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="59" t="s">
         <v>249</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="66"/>
+      <c r="F16" s="59" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="25"/>
-      <c r="B17" s="33"/>
-      <c r="C17" s="1" t="s">
+      <c r="A17" s="64"/>
+      <c r="B17" s="65"/>
+      <c r="C17" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="59" t="s">
         <v>250</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="1" t="s">
+      <c r="E17" s="66"/>
+      <c r="F17" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="25"/>
-      <c r="B18" s="33"/>
-      <c r="C18" s="1" t="s">
+      <c r="A18" s="64"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="59" t="s">
         <v>251</v>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="1" t="s">
+      <c r="E18" s="69"/>
+      <c r="F18" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="25"/>
-      <c r="B19" s="33"/>
-      <c r="C19" s="1" t="s">
+      <c r="A19" s="64"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="59" t="s">
         <v>252</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="1" t="s">
+      <c r="E19" s="69"/>
+      <c r="F19" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="25"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="1" t="s">
+      <c r="A20" s="64"/>
+      <c r="B20" s="65"/>
+      <c r="C20" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="59" t="s">
         <v>253</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="1" t="s">
+      <c r="E20" s="69"/>
+      <c r="F20" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="1" t="s">
+      <c r="A21" s="64"/>
+      <c r="B21" s="65"/>
+      <c r="C21" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="59" t="s">
         <v>254</v>
       </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="69"/>
+      <c r="F21" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="25"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="64"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="74"/>
+      <c r="D22" s="74"/>
+      <c r="E22" s="75"/>
+      <c r="F22" s="74"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="25"/>
-      <c r="B23" s="36" t="s">
+      <c r="A23" s="64"/>
+      <c r="B23" s="70" t="s">
         <v>273</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="59" t="s">
         <v>285</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="1" t="s">
+      <c r="E23" s="66"/>
+      <c r="F23" s="59" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="25"/>
-      <c r="B24" s="33"/>
-      <c r="C24" s="1" t="s">
+      <c r="A24" s="64"/>
+      <c r="B24" s="65"/>
+      <c r="C24" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="59" t="s">
         <v>286</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="1" t="s">
+      <c r="E24" s="66"/>
+      <c r="F24" s="59" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="25"/>
-      <c r="B25" s="33"/>
-      <c r="C25" s="1" t="s">
+      <c r="A25" s="64"/>
+      <c r="B25" s="65"/>
+      <c r="C25" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="59" t="s">
         <v>287</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="1" t="s">
+      <c r="E25" s="68"/>
+      <c r="F25" s="59" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="25"/>
-      <c r="B26" s="33"/>
-      <c r="C26" s="1" t="s">
+      <c r="A26" s="64"/>
+      <c r="B26" s="65"/>
+      <c r="C26" s="59" t="s">
         <v>295</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="59" t="s">
         <v>296</v>
       </c>
-      <c r="E26" s="10"/>
-      <c r="F26" s="1" t="s">
+      <c r="E26" s="69"/>
+      <c r="F26" s="59" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="25"/>
-      <c r="B27" s="33"/>
-      <c r="C27" s="1" t="s">
+      <c r="A27" s="64"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="59" t="s">
         <v>288</v>
       </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="1" t="s">
+      <c r="E27" s="69"/>
+      <c r="F27" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="25"/>
-      <c r="B28" s="33"/>
-      <c r="C28" s="1" t="s">
+      <c r="A28" s="64"/>
+      <c r="B28" s="65"/>
+      <c r="C28" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="59" t="s">
         <v>289</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="1" t="s">
+      <c r="E28" s="69"/>
+      <c r="F28" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="25"/>
-      <c r="B29" s="33"/>
-      <c r="C29" s="1" t="s">
+      <c r="A29" s="64"/>
+      <c r="B29" s="65"/>
+      <c r="C29" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="59" t="s">
         <v>290</v>
       </c>
-      <c r="E29" s="10"/>
-      <c r="F29" s="1" t="s">
+      <c r="E29" s="69"/>
+      <c r="F29" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="25"/>
-      <c r="B30" s="33"/>
-      <c r="C30" s="1" t="s">
+      <c r="A30" s="64"/>
+      <c r="B30" s="65"/>
+      <c r="C30" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="59" t="s">
         <v>291</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="1" t="s">
+      <c r="E30" s="68"/>
+      <c r="F30" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="25"/>
-      <c r="B31" s="33"/>
-      <c r="C31" s="1" t="s">
+      <c r="A31" s="64"/>
+      <c r="B31" s="65"/>
+      <c r="C31" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="59" t="s">
         <v>292</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="1" t="s">
+      <c r="E31" s="68"/>
+      <c r="F31" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="25"/>
-      <c r="B32" s="37"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="13"/>
+      <c r="A32" s="64"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="74"/>
+      <c r="D32" s="74"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="74"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="25"/>
-      <c r="B33" s="38" t="s">
+      <c r="A33" s="64"/>
+      <c r="B33" s="76" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="59" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="59" t="s">
         <v>361</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="1" t="s">
+      <c r="E33" s="66"/>
+      <c r="F33" s="59" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="25"/>
-      <c r="B34" s="38"/>
-      <c r="C34" s="1" t="s">
+      <c r="A34" s="64"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="59" t="s">
         <v>362</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="1" t="s">
+      <c r="E34" s="66"/>
+      <c r="F34" s="59" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="25"/>
-      <c r="B35" s="38"/>
-      <c r="C35" s="1" t="s">
+      <c r="A35" s="64"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="59" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="59" t="s">
         <v>363</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="1" t="s">
+      <c r="E35" s="68"/>
+      <c r="F35" s="59" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="25"/>
-      <c r="B36" s="38"/>
-      <c r="C36" s="1" t="s">
+      <c r="A36" s="64"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="59" t="s">
         <v>283</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="59" t="s">
         <v>365</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="1" t="s">
+      <c r="E36" s="68"/>
+      <c r="F36" s="59" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="25"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="1" t="s">
+      <c r="A37" s="64"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="59" t="s">
         <v>372</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="59" t="s">
         <v>375</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="1" t="s">
+      <c r="E37" s="68"/>
+      <c r="F37" s="59" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="25"/>
-      <c r="B38" s="38"/>
-      <c r="C38" s="1" t="s">
+      <c r="A38" s="64"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="59" t="s">
         <v>260</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="59" t="s">
         <v>364</v>
       </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="1" t="s">
+      <c r="E38" s="69"/>
+      <c r="F38" s="59" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="25"/>
-      <c r="B39" s="38"/>
-      <c r="C39" s="1" t="s">
+      <c r="A39" s="64"/>
+      <c r="B39" s="76"/>
+      <c r="C39" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="59" t="s">
         <v>366</v>
       </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="1" t="s">
+      <c r="E39" s="69"/>
+      <c r="F39" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="25"/>
-      <c r="B40" s="38"/>
-      <c r="C40" s="1" t="s">
+      <c r="A40" s="64"/>
+      <c r="B40" s="76"/>
+      <c r="C40" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="59" t="s">
         <v>369</v>
       </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="1" t="s">
+      <c r="E40" s="69"/>
+      <c r="F40" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="25"/>
-      <c r="B41" s="38"/>
-      <c r="C41" s="1" t="s">
+      <c r="A41" s="64"/>
+      <c r="B41" s="76"/>
+      <c r="C41" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="59" t="s">
         <v>381</v>
       </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="1" t="s">
+      <c r="E41" s="69"/>
+      <c r="F41" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="25"/>
-      <c r="B42" s="38"/>
-      <c r="C42" s="1" t="s">
+      <c r="A42" s="64"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="59" t="s">
         <v>367</v>
       </c>
-      <c r="E42" s="10"/>
-      <c r="F42" s="1" t="s">
+      <c r="E42" s="69"/>
+      <c r="F42" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="25"/>
-      <c r="B43" s="38"/>
-      <c r="C43" s="1" t="s">
+      <c r="A43" s="64"/>
+      <c r="B43" s="76"/>
+      <c r="C43" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="59" t="s">
         <v>368</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="1" t="s">
+      <c r="E43" s="68"/>
+      <c r="F43" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="25"/>
-      <c r="B44" s="38"/>
-      <c r="C44" s="1" t="s">
+      <c r="A44" s="64"/>
+      <c r="B44" s="76"/>
+      <c r="C44" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="59" t="s">
         <v>370</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="1" t="s">
+      <c r="E44" s="68"/>
+      <c r="F44" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="25"/>
-      <c r="B45" s="38"/>
-      <c r="E45" s="9"/>
+      <c r="A45" s="64"/>
+      <c r="B45" s="76"/>
+      <c r="E45" s="68"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="60" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="77" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="62" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="62" t="s">
         <v>104</v>
       </c>
-      <c r="E46" s="15"/>
-      <c r="F46" s="2" t="s">
+      <c r="E46" s="78"/>
+      <c r="F46" s="62" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="25"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="1" t="s">
+      <c r="A47" s="64"/>
+      <c r="B47" s="76"/>
+      <c r="C47" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="1" t="s">
+      <c r="E47" s="68"/>
+      <c r="F47" s="59" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="25"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="1" t="s">
+      <c r="A48" s="64"/>
+      <c r="B48" s="76"/>
+      <c r="C48" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="E48" s="10"/>
-      <c r="F48" s="1" t="s">
+      <c r="E48" s="69"/>
+      <c r="F48" s="59" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="25"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="1" t="s">
+      <c r="A49" s="64"/>
+      <c r="B49" s="76"/>
+      <c r="C49" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="1" t="s">
+      <c r="E49" s="68"/>
+      <c r="F49" s="59" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="25"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="1" t="s">
+      <c r="A50" s="64"/>
+      <c r="B50" s="76"/>
+      <c r="C50" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="1" t="s">
+      <c r="E50" s="68"/>
+      <c r="F50" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="25"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="1" t="s">
+      <c r="A51" s="64"/>
+      <c r="B51" s="76"/>
+      <c r="C51" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="59" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="1" t="s">
+      <c r="E51" s="68"/>
+      <c r="F51" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="25"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="1" t="s">
+      <c r="A52" s="64"/>
+      <c r="B52" s="76"/>
+      <c r="C52" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="59" t="s">
         <v>201</v>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="1" t="s">
+      <c r="E52" s="68"/>
+      <c r="F52" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="25"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="1" t="s">
+      <c r="A53" s="64"/>
+      <c r="B53" s="76"/>
+      <c r="C53" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="59" t="s">
         <v>172</v>
       </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="1" t="s">
+      <c r="E53" s="68"/>
+      <c r="F53" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="25"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="1" t="s">
+      <c r="A54" s="64"/>
+      <c r="B54" s="76"/>
+      <c r="C54" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="59" t="s">
         <v>195</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="1" t="s">
+      <c r="E54" s="68"/>
+      <c r="F54" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="25"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="13"/>
+      <c r="A55" s="64"/>
+      <c r="B55" s="79"/>
+      <c r="C55" s="74"/>
+      <c r="D55" s="74"/>
+      <c r="E55" s="75"/>
+      <c r="F55" s="74"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="25"/>
-      <c r="B56" s="29" t="s">
+      <c r="A56" s="64"/>
+      <c r="B56" s="76" t="s">
         <v>317</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="59" t="s">
         <v>327</v>
       </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="1" t="s">
+      <c r="E56" s="66"/>
+      <c r="F56" s="59" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="25"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="1" t="s">
+      <c r="A57" s="64"/>
+      <c r="B57" s="76"/>
+      <c r="C57" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="59" t="s">
         <v>328</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="1" t="s">
+      <c r="E57" s="68"/>
+      <c r="F57" s="59" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="25"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="1" t="s">
+      <c r="A58" s="64"/>
+      <c r="B58" s="76"/>
+      <c r="C58" s="59" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="59" t="s">
         <v>329</v>
       </c>
-      <c r="E58" s="10"/>
-      <c r="F58" s="1" t="s">
+      <c r="E58" s="69"/>
+      <c r="F58" s="59" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="25"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="1" t="s">
+      <c r="A59" s="64"/>
+      <c r="B59" s="76"/>
+      <c r="C59" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="59" t="s">
         <v>330</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="1" t="s">
+      <c r="E59" s="68"/>
+      <c r="F59" s="59" t="s">
         <v>395</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="25"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="1" t="s">
+      <c r="A60" s="64"/>
+      <c r="B60" s="76"/>
+      <c r="C60" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="59" t="s">
         <v>331</v>
       </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="1" t="s">
+      <c r="E60" s="68"/>
+      <c r="F60" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="25"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="1" t="s">
+      <c r="A61" s="64"/>
+      <c r="B61" s="76"/>
+      <c r="C61" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="59" t="s">
         <v>332</v>
       </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="1" t="s">
+      <c r="E61" s="68"/>
+      <c r="F61" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="25"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="1" t="s">
+      <c r="A62" s="64"/>
+      <c r="B62" s="76"/>
+      <c r="C62" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="59" t="s">
         <v>333</v>
       </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="1" t="s">
+      <c r="E62" s="68"/>
+      <c r="F62" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="25"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="1" t="s">
+      <c r="A63" s="64"/>
+      <c r="B63" s="76"/>
+      <c r="C63" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="59" t="s">
         <v>334</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="1" t="s">
+      <c r="E63" s="68"/>
+      <c r="F63" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="25"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="1" t="s">
+      <c r="A64" s="64"/>
+      <c r="B64" s="76"/>
+      <c r="C64" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="59" t="s">
         <v>335</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="1" t="s">
+      <c r="E64" s="68"/>
+      <c r="F64" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="25"/>
-      <c r="B65" s="30"/>
-      <c r="E65" s="9"/>
+      <c r="A65" s="64"/>
+      <c r="B65" s="79"/>
+      <c r="E65" s="68"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="25"/>
-      <c r="B66" s="31" t="s">
+      <c r="A66" s="64"/>
+      <c r="B66" s="80" t="s">
         <v>6</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="71" t="s">
         <v>101</v>
       </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="11" t="s">
+      <c r="E66" s="81"/>
+      <c r="F66" s="71" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="25"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="1" t="s">
+      <c r="A67" s="64"/>
+      <c r="B67" s="76"/>
+      <c r="C67" s="59" t="s">
         <v>114</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="59" t="s">
         <v>103</v>
       </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="1" t="s">
+      <c r="E67" s="68"/>
+      <c r="F67" s="59" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="25"/>
-      <c r="B68" s="33"/>
-      <c r="C68" s="1" t="s">
+      <c r="A68" s="64"/>
+      <c r="B68" s="65"/>
+      <c r="C68" s="59" t="s">
         <v>112</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="59" t="s">
         <v>113</v>
       </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="1" t="s">
+      <c r="E68" s="66"/>
+      <c r="F68" s="59" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="25"/>
-      <c r="B69" s="33"/>
-      <c r="C69" s="1" t="s">
+      <c r="A69" s="64"/>
+      <c r="B69" s="65"/>
+      <c r="C69" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="59" t="s">
         <v>186</v>
       </c>
-      <c r="E69" s="7"/>
-      <c r="F69" s="1" t="s">
+      <c r="E69" s="66"/>
+      <c r="F69" s="59" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="25"/>
-      <c r="B70" s="33"/>
-      <c r="C70" s="1" t="s">
+      <c r="A70" s="64"/>
+      <c r="B70" s="65"/>
+      <c r="C70" s="59" t="s">
         <v>127</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="E70" s="7"/>
-      <c r="F70" s="1" t="s">
+      <c r="E70" s="66"/>
+      <c r="F70" s="59" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="25"/>
-      <c r="B71" s="33"/>
-      <c r="C71" s="1" t="s">
+      <c r="A71" s="64"/>
+      <c r="B71" s="65"/>
+      <c r="C71" s="59" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="1" t="s">
+      <c r="E71" s="68"/>
+      <c r="F71" s="59" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="25"/>
-      <c r="B72" s="33"/>
-      <c r="C72" s="1" t="s">
+      <c r="A72" s="64"/>
+      <c r="B72" s="65"/>
+      <c r="C72" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="59" t="s">
         <v>146</v>
       </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="1" t="s">
+      <c r="E72" s="66"/>
+      <c r="F72" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="25"/>
-      <c r="B73" s="33"/>
-      <c r="C73" s="1" t="s">
+      <c r="A73" s="64"/>
+      <c r="B73" s="65"/>
+      <c r="C73" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="59" t="s">
         <v>158</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="1" t="s">
+      <c r="E73" s="68"/>
+      <c r="F73" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="25"/>
-      <c r="B74" s="33"/>
-      <c r="C74" s="1" t="s">
+      <c r="A74" s="64"/>
+      <c r="B74" s="65"/>
+      <c r="C74" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="59" t="s">
         <v>202</v>
       </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="1" t="s">
+      <c r="E74" s="68"/>
+      <c r="F74" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="25"/>
-      <c r="B75" s="33"/>
-      <c r="C75" s="1" t="s">
+      <c r="A75" s="64"/>
+      <c r="B75" s="65"/>
+      <c r="C75" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="59" t="s">
         <v>171</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="1" t="s">
+      <c r="E75" s="68"/>
+      <c r="F75" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="25"/>
-      <c r="B76" s="33"/>
-      <c r="C76" s="1" t="s">
+      <c r="A76" s="64"/>
+      <c r="B76" s="65"/>
+      <c r="C76" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="59" t="s">
         <v>194</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="1" t="s">
+      <c r="E76" s="68"/>
+      <c r="F76" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="26"/>
-      <c r="B77" s="34"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="17"/>
+      <c r="A77" s="82"/>
+      <c r="B77" s="83"/>
+      <c r="C77" s="84"/>
+      <c r="D77" s="84"/>
+      <c r="E77" s="85"/>
+      <c r="F77" s="84"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="24" t="s">
+      <c r="A78" s="60" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="35" t="s">
+      <c r="B78" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="62" t="s">
         <v>118</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="62" t="s">
         <v>117</v>
       </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="2" t="s">
+      <c r="E78" s="78"/>
+      <c r="F78" s="62" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="25"/>
-      <c r="B79" s="39"/>
-      <c r="C79" s="21" t="s">
+      <c r="A79" s="64"/>
+      <c r="B79" s="86"/>
+      <c r="C79" s="87" t="s">
         <v>154</v>
       </c>
-      <c r="D79" s="21" t="s">
+      <c r="D79" s="87" t="s">
         <v>153</v>
       </c>
-      <c r="E79" s="22"/>
-      <c r="F79" s="21" t="s">
+      <c r="E79" s="88"/>
+      <c r="F79" s="87" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="25"/>
-      <c r="B80" s="37"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="23"/>
-      <c r="F80" s="13"/>
+      <c r="A80" s="64"/>
+      <c r="B80" s="73"/>
+      <c r="C80" s="74"/>
+      <c r="D80" s="74"/>
+      <c r="E80" s="89"/>
+      <c r="F80" s="74"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="25"/>
-      <c r="B81" s="36" t="s">
+      <c r="A81" s="64"/>
+      <c r="B81" s="70" t="s">
         <v>343</v>
       </c>
-      <c r="C81" s="11" t="s">
+      <c r="C81" s="71" t="s">
         <v>346</v>
       </c>
-      <c r="D81" s="11" t="s">
+      <c r="D81" s="71" t="s">
         <v>349</v>
       </c>
-      <c r="E81" s="12"/>
-      <c r="F81" s="11" t="s">
+      <c r="E81" s="72"/>
+      <c r="F81" s="71" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="25"/>
-      <c r="B82" s="39"/>
-      <c r="C82" s="21" t="s">
+      <c r="A82" s="64"/>
+      <c r="B82" s="86"/>
+      <c r="C82" s="87" t="s">
         <v>347</v>
       </c>
-      <c r="D82" s="21" t="s">
+      <c r="D82" s="87" t="s">
         <v>350</v>
       </c>
-      <c r="E82" s="22"/>
-      <c r="F82" s="21" t="s">
+      <c r="E82" s="88"/>
+      <c r="F82" s="87" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="25"/>
-      <c r="B83" s="37"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="23"/>
-      <c r="F83" s="13"/>
+      <c r="A83" s="64"/>
+      <c r="B83" s="73"/>
+      <c r="C83" s="74"/>
+      <c r="D83" s="74"/>
+      <c r="E83" s="89"/>
+      <c r="F83" s="74"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="25"/>
-      <c r="B84" s="39" t="s">
+      <c r="A84" s="64"/>
+      <c r="B84" s="86" t="s">
         <v>385</v>
       </c>
-      <c r="C84" s="21" t="s">
+      <c r="C84" s="87" t="s">
         <v>386</v>
       </c>
-      <c r="D84" s="21" t="s">
+      <c r="D84" s="87" t="s">
         <v>388</v>
       </c>
-      <c r="E84" s="22"/>
-      <c r="F84" s="21" t="s">
+      <c r="E84" s="88"/>
+      <c r="F84" s="87" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="25"/>
-      <c r="B85" s="39"/>
-      <c r="C85" s="1" t="s">
+      <c r="A85" s="64"/>
+      <c r="B85" s="86"/>
+      <c r="C85" s="59" t="s">
         <v>387</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="59" t="s">
         <v>389</v>
       </c>
-      <c r="E85" s="7"/>
-      <c r="F85" s="1" t="s">
+      <c r="E85" s="66"/>
+      <c r="F85" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="25"/>
-      <c r="B86" s="39"/>
-      <c r="E86" s="7"/>
+      <c r="A86" s="64"/>
+      <c r="B86" s="86"/>
+      <c r="E86" s="66"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="25"/>
-      <c r="B87" s="31" t="s">
+      <c r="A87" s="64"/>
+      <c r="B87" s="80" t="s">
         <v>4</v>
       </c>
-      <c r="C87" s="11" t="s">
+      <c r="C87" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="D87" s="11" t="s">
+      <c r="D87" s="71" t="s">
         <v>100</v>
       </c>
-      <c r="E87" s="16"/>
-      <c r="F87" s="11" t="s">
+      <c r="E87" s="81"/>
+      <c r="F87" s="71" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="25"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="1" t="s">
+      <c r="A88" s="64"/>
+      <c r="B88" s="76"/>
+      <c r="C88" s="59" t="s">
         <v>108</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="59" t="s">
         <v>110</v>
       </c>
-      <c r="E88" s="19"/>
-      <c r="F88" s="1" t="s">
+      <c r="E88" s="1"/>
+      <c r="F88" s="59" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="25"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="1" t="s">
+      <c r="A89" s="64"/>
+      <c r="B89" s="76"/>
+      <c r="C89" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="E89" s="19"/>
-      <c r="F89" s="1" t="s">
+      <c r="E89" s="1"/>
+      <c r="F89" s="59" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="25"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="1" t="s">
+      <c r="A90" s="64"/>
+      <c r="B90" s="76"/>
+      <c r="C90" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="59" t="s">
         <v>145</v>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="1" t="s">
+      <c r="E90" s="66"/>
+      <c r="F90" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="25"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="1" t="s">
+      <c r="A91" s="64"/>
+      <c r="B91" s="76"/>
+      <c r="C91" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="59" t="s">
         <v>157</v>
       </c>
-      <c r="E91" s="10"/>
-      <c r="F91" s="1" t="s">
+      <c r="E91" s="69"/>
+      <c r="F91" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="25"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="1" t="s">
+      <c r="A92" s="64"/>
+      <c r="B92" s="76"/>
+      <c r="C92" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="59" t="s">
         <v>163</v>
       </c>
-      <c r="E92" s="7"/>
-      <c r="F92" s="1" t="s">
+      <c r="E92" s="66"/>
+      <c r="F92" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="25"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="1" t="s">
+      <c r="A93" s="64"/>
+      <c r="B93" s="76"/>
+      <c r="C93" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" s="59" t="s">
         <v>200</v>
       </c>
-      <c r="E93" s="7"/>
-      <c r="F93" s="1" t="s">
+      <c r="E93" s="66"/>
+      <c r="F93" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="25"/>
-      <c r="B94" s="29"/>
-      <c r="C94" s="1" t="s">
+      <c r="A94" s="64"/>
+      <c r="B94" s="76"/>
+      <c r="C94" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D94" s="59" t="s">
         <v>170</v>
       </c>
-      <c r="E94" s="9"/>
-      <c r="F94" s="1" t="s">
+      <c r="E94" s="68"/>
+      <c r="F94" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="25"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="1" t="s">
+      <c r="A95" s="64"/>
+      <c r="B95" s="76"/>
+      <c r="C95" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="59" t="s">
         <v>192</v>
       </c>
-      <c r="E95" s="9"/>
-      <c r="F95" s="1" t="s">
+      <c r="E95" s="68"/>
+      <c r="F95" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="25"/>
-      <c r="B96" s="30"/>
+      <c r="A96" s="64"/>
+      <c r="B96" s="79"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="25"/>
-      <c r="B97" s="31" t="s">
+      <c r="A97" s="64"/>
+      <c r="B97" s="80" t="s">
         <v>5</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="71" t="s">
         <v>97</v>
       </c>
-      <c r="D97" s="11" t="s">
+      <c r="D97" s="71" t="s">
         <v>102</v>
       </c>
-      <c r="E97" s="16"/>
-      <c r="F97" s="11" t="s">
+      <c r="E97" s="81"/>
+      <c r="F97" s="71" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="25"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="1" t="s">
+      <c r="A98" s="64"/>
+      <c r="B98" s="76"/>
+      <c r="C98" s="59" t="s">
         <v>109</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" s="59" t="s">
         <v>107</v>
       </c>
-      <c r="E98" s="19"/>
-      <c r="F98" s="1" t="s">
+      <c r="E98" s="1"/>
+      <c r="F98" s="59" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="25"/>
-      <c r="B99" s="29"/>
-      <c r="C99" s="1" t="s">
+      <c r="A99" s="64"/>
+      <c r="B99" s="76"/>
+      <c r="C99" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" s="59" t="s">
         <v>120</v>
       </c>
-      <c r="E99" s="19"/>
-      <c r="F99" s="1" t="s">
+      <c r="E99" s="1"/>
+      <c r="F99" s="59" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="25"/>
-      <c r="B100" s="29"/>
-      <c r="C100" s="1" t="s">
+      <c r="A100" s="64"/>
+      <c r="B100" s="76"/>
+      <c r="C100" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="E100" s="19"/>
-      <c r="F100" s="1" t="s">
+      <c r="E100" s="1"/>
+      <c r="F100" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="25"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="1" t="s">
+      <c r="A101" s="64"/>
+      <c r="B101" s="76"/>
+      <c r="C101" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" s="59" t="s">
         <v>155</v>
       </c>
-      <c r="E101" s="10"/>
-      <c r="F101" s="1" t="s">
+      <c r="E101" s="69"/>
+      <c r="F101" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="25"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="1" t="s">
+      <c r="A102" s="64"/>
+      <c r="B102" s="76"/>
+      <c r="C102" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" s="59" t="s">
         <v>161</v>
       </c>
-      <c r="E102" s="20"/>
-      <c r="F102" s="1" t="s">
+      <c r="E102" s="90"/>
+      <c r="F102" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="25"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="1" t="s">
+      <c r="A103" s="64"/>
+      <c r="B103" s="76"/>
+      <c r="C103" s="59" t="s">
         <v>198</v>
       </c>
-      <c r="D103" s="1" t="s">
+      <c r="D103" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="E103" s="20"/>
-      <c r="F103" s="1" t="s">
+      <c r="E103" s="90"/>
+      <c r="F103" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="25"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="1" t="s">
+      <c r="A104" s="64"/>
+      <c r="B104" s="76"/>
+      <c r="C104" s="59" t="s">
         <v>168</v>
       </c>
-      <c r="D104" s="1" t="s">
+      <c r="D104" s="59" t="s">
         <v>169</v>
       </c>
-      <c r="E104" s="9"/>
-      <c r="F104" s="1" t="s">
+      <c r="E104" s="68"/>
+      <c r="F104" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="25"/>
-      <c r="B105" s="29"/>
-      <c r="C105" s="1" t="s">
+      <c r="A105" s="64"/>
+      <c r="B105" s="76"/>
+      <c r="C105" s="59" t="s">
         <v>190</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="59" t="s">
         <v>191</v>
       </c>
-      <c r="E105" s="9"/>
-      <c r="F105" s="1" t="s">
+      <c r="E105" s="68"/>
+      <c r="F105" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="26"/>
-      <c r="B106" s="32"/>
+      <c r="A106" s="82"/>
+      <c r="B106" s="91"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="24" t="s">
+      <c r="A107" s="60" t="s">
         <v>76</v>
       </c>
-      <c r="B107" s="35" t="s">
+      <c r="B107" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="C107" s="2" t="s">
+      <c r="C107" s="62" t="s">
         <v>130</v>
       </c>
-      <c r="D107" s="2" t="s">
+      <c r="D107" s="62" t="s">
         <v>129</v>
       </c>
-      <c r="E107" s="6"/>
-      <c r="F107" s="2" t="s">
+      <c r="E107" s="63"/>
+      <c r="F107" s="62" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="25"/>
-      <c r="B108" s="33"/>
-      <c r="C108" s="1" t="s">
+      <c r="A108" s="64"/>
+      <c r="B108" s="65"/>
+      <c r="C108" s="59" t="s">
         <v>230</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" s="59" t="s">
         <v>229</v>
       </c>
-      <c r="E108" s="9"/>
-      <c r="F108" s="1" t="s">
+      <c r="E108" s="68"/>
+      <c r="F108" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="25"/>
-      <c r="B109" s="33"/>
-      <c r="C109" s="1" t="s">
+      <c r="A109" s="64"/>
+      <c r="B109" s="65"/>
+      <c r="C109" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="E109" s="9"/>
-      <c r="F109" s="1" t="s">
+      <c r="E109" s="68"/>
+      <c r="F109" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="25"/>
-      <c r="B110" s="37"/>
-      <c r="C110" s="13"/>
-      <c r="D110" s="13"/>
-      <c r="E110" s="14"/>
-      <c r="F110" s="13"/>
+      <c r="A110" s="64"/>
+      <c r="B110" s="73"/>
+      <c r="C110" s="74"/>
+      <c r="D110" s="74"/>
+      <c r="E110" s="75"/>
+      <c r="F110" s="74"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="25"/>
-      <c r="B111" s="36" t="s">
+      <c r="A111" s="64"/>
+      <c r="B111" s="70" t="s">
         <v>303</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="59" t="s">
         <v>304</v>
       </c>
-      <c r="D111" s="1" t="s">
+      <c r="D111" s="59" t="s">
         <v>305</v>
       </c>
-      <c r="E111" s="9"/>
-      <c r="F111" s="1" t="s">
+      <c r="E111" s="68"/>
+      <c r="F111" s="59" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="25"/>
-      <c r="B112" s="33"/>
-      <c r="C112" s="1" t="s">
+      <c r="A112" s="64"/>
+      <c r="B112" s="65"/>
+      <c r="C112" s="59" t="s">
         <v>308</v>
       </c>
-      <c r="D112" s="1" t="s">
+      <c r="D112" s="59" t="s">
         <v>306</v>
       </c>
-      <c r="E112" s="9"/>
-      <c r="F112" s="1" t="s">
+      <c r="E112" s="68"/>
+      <c r="F112" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="25"/>
-      <c r="B113" s="33"/>
-      <c r="C113" s="1" t="s">
+      <c r="A113" s="64"/>
+      <c r="B113" s="65"/>
+      <c r="C113" s="59" t="s">
         <v>309</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="59" t="s">
         <v>307</v>
       </c>
-      <c r="E113" s="9"/>
-      <c r="F113" s="1" t="s">
+      <c r="E113" s="68"/>
+      <c r="F113" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="25"/>
-      <c r="B114" s="37"/>
-      <c r="E114" s="9"/>
+      <c r="A114" s="64"/>
+      <c r="B114" s="73"/>
+      <c r="E114" s="68"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="25"/>
-      <c r="B115" s="36" t="s">
+      <c r="A115" s="64"/>
+      <c r="B115" s="70" t="s">
         <v>79</v>
       </c>
-      <c r="C115" s="11" t="s">
+      <c r="C115" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="D115" s="11" t="s">
+      <c r="D115" s="71" t="s">
         <v>131</v>
       </c>
-      <c r="E115" s="16"/>
-      <c r="F115" s="11" t="s">
+      <c r="E115" s="81"/>
+      <c r="F115" s="71" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="25"/>
-      <c r="B116" s="33"/>
-      <c r="C116" s="1" t="s">
+      <c r="A116" s="64"/>
+      <c r="B116" s="65"/>
+      <c r="C116" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="59" t="s">
         <v>149</v>
       </c>
-      <c r="E116" s="9"/>
-      <c r="F116" s="1" t="s">
+      <c r="E116" s="68"/>
+      <c r="F116" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="25"/>
-      <c r="B117" s="37"/>
-      <c r="C117" s="13"/>
-      <c r="D117" s="13"/>
-      <c r="E117" s="14"/>
-      <c r="F117" s="13"/>
+      <c r="A117" s="64"/>
+      <c r="B117" s="73"/>
+      <c r="C117" s="74"/>
+      <c r="D117" s="74"/>
+      <c r="E117" s="75"/>
+      <c r="F117" s="74"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="25"/>
-      <c r="B118" s="36" t="s">
+      <c r="A118" s="64"/>
+      <c r="B118" s="70" t="s">
         <v>262</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="59" t="s">
         <v>261</v>
       </c>
-      <c r="D118" s="1" t="s">
+      <c r="D118" s="59" t="s">
         <v>264</v>
       </c>
-      <c r="E118" s="9"/>
-      <c r="F118" s="1" t="s">
+      <c r="E118" s="68"/>
+      <c r="F118" s="59" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="25"/>
-      <c r="B119" s="33"/>
-      <c r="C119" s="1" t="s">
+      <c r="A119" s="64"/>
+      <c r="B119" s="65"/>
+      <c r="C119" s="59" t="s">
         <v>263</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="59" t="s">
         <v>265</v>
       </c>
-      <c r="E119" s="9"/>
-      <c r="F119" s="1" t="s">
+      <c r="E119" s="68"/>
+      <c r="F119" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="120" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="26"/>
-      <c r="B120" s="34"/>
-      <c r="C120" s="17"/>
-      <c r="D120" s="17"/>
-      <c r="E120" s="18"/>
-      <c r="F120" s="17"/>
+      <c r="A120" s="82"/>
+      <c r="B120" s="83"/>
+      <c r="C120" s="84"/>
+      <c r="D120" s="84"/>
+      <c r="E120" s="85"/>
+      <c r="F120" s="84"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="24" t="s">
+      <c r="A121" s="60" t="s">
         <v>164</v>
       </c>
-      <c r="B121" s="35" t="s">
+      <c r="B121" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="C121" s="2" t="s">
+      <c r="C121" s="62" t="s">
         <v>174</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="D121" s="62" t="s">
         <v>173</v>
       </c>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2" t="s">
+      <c r="E121" s="62"/>
+      <c r="F121" s="62" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="27"/>
-      <c r="B122" s="33"/>
-      <c r="C122" s="1" t="s">
+      <c r="A122" s="92"/>
+      <c r="B122" s="65"/>
+      <c r="C122" s="59" t="s">
         <v>175</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" s="59" t="s">
         <v>176</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F122" s="59" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="27"/>
-      <c r="B123" s="37"/>
-      <c r="C123" s="13"/>
-      <c r="D123" s="13"/>
-      <c r="E123" s="13"/>
-      <c r="F123" s="13"/>
+      <c r="A123" s="92"/>
+      <c r="B123" s="73"/>
+      <c r="C123" s="74"/>
+      <c r="D123" s="74"/>
+      <c r="E123" s="74"/>
+      <c r="F123" s="74"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="27"/>
-      <c r="B124" s="36" t="s">
+      <c r="A124" s="92"/>
+      <c r="B124" s="70" t="s">
         <v>184</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="59" t="s">
         <v>166</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D124" s="59" t="s">
         <v>165</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="F124" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="27"/>
-      <c r="B125" s="33"/>
-      <c r="C125" s="1" t="s">
+      <c r="A125" s="92"/>
+      <c r="B125" s="65"/>
+      <c r="C125" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" s="59" t="s">
         <v>311</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F125" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="27"/>
-      <c r="B126" s="33"/>
-      <c r="C126" s="1" t="s">
+      <c r="A126" s="92"/>
+      <c r="B126" s="65"/>
+      <c r="C126" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" s="59" t="s">
         <v>177</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F126" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="27"/>
-      <c r="B127" s="33"/>
-      <c r="C127" s="1" t="s">
+      <c r="A127" s="92"/>
+      <c r="B127" s="65"/>
+      <c r="C127" s="59" t="s">
         <v>180</v>
       </c>
-      <c r="D127" s="1" t="s">
+      <c r="D127" s="59" t="s">
         <v>179</v>
       </c>
-      <c r="F127" s="1" t="s">
+      <c r="F127" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="27"/>
-      <c r="B128" s="33"/>
-      <c r="C128" s="1" t="s">
+      <c r="A128" s="92"/>
+      <c r="B128" s="65"/>
+      <c r="C128" s="59" t="s">
         <v>183</v>
       </c>
-      <c r="D128" s="1" t="s">
+      <c r="D128" s="59" t="s">
         <v>181</v>
       </c>
-      <c r="F128" s="1" t="s">
+      <c r="F128" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="27"/>
-      <c r="B129" s="33"/>
-      <c r="C129" s="1" t="s">
+      <c r="A129" s="92"/>
+      <c r="B129" s="65"/>
+      <c r="C129" s="59" t="s">
         <v>193</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="59" t="s">
         <v>189</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F129" s="59" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="27"/>
-      <c r="B130" s="33"/>
+      <c r="A130" s="92"/>
+      <c r="B130" s="65"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="27"/>
-      <c r="B131" s="36" t="s">
+      <c r="A131" s="92"/>
+      <c r="B131" s="70" t="s">
         <v>208</v>
       </c>
-      <c r="C131" s="11" t="s">
+      <c r="C131" s="71" t="s">
         <v>205</v>
       </c>
-      <c r="D131" s="11" t="s">
+      <c r="D131" s="71" t="s">
         <v>209</v>
       </c>
-      <c r="E131" s="11"/>
-      <c r="F131" s="11" t="s">
+      <c r="E131" s="71"/>
+      <c r="F131" s="71" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="27"/>
-      <c r="B132" s="33"/>
-      <c r="C132" s="1" t="s">
+      <c r="A132" s="92"/>
+      <c r="B132" s="65"/>
+      <c r="C132" s="59" t="s">
         <v>206</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="59" t="s">
         <v>212</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F132" s="59" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="27"/>
-      <c r="B133" s="33"/>
-      <c r="C133" s="1" t="s">
+      <c r="A133" s="92"/>
+      <c r="B133" s="65"/>
+      <c r="C133" s="59" t="s">
         <v>217</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" s="59" t="s">
         <v>216</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F133" s="59" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="27"/>
-      <c r="B134" s="33"/>
-      <c r="C134" s="1" t="s">
+      <c r="A134" s="92"/>
+      <c r="B134" s="65"/>
+      <c r="C134" s="59" t="s">
         <v>207</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="59" t="s">
         <v>211</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F134" s="59" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="27"/>
-      <c r="B135" s="33"/>
-      <c r="C135" s="1" t="s">
+      <c r="A135" s="92"/>
+      <c r="B135" s="65"/>
+      <c r="C135" s="59" t="s">
         <v>312</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" s="59" t="s">
         <v>313</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F135" s="59" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="27"/>
-      <c r="B136" s="33"/>
-      <c r="C136" s="1" t="s">
+      <c r="A136" s="92"/>
+      <c r="B136" s="65"/>
+      <c r="C136" s="59" t="s">
         <v>336</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="59" t="s">
         <v>337</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F136" s="59" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="27"/>
-      <c r="B137" s="33"/>
-      <c r="C137" s="1" t="s">
+      <c r="A137" s="92"/>
+      <c r="B137" s="65"/>
+      <c r="C137" s="59" t="s">
         <v>338</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" s="59" t="s">
         <v>339</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="F137" s="59" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="27"/>
-      <c r="B138" s="33"/>
-      <c r="C138" s="1" t="s">
+      <c r="A138" s="92"/>
+      <c r="B138" s="65"/>
+      <c r="C138" s="59" t="s">
         <v>219</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="59" t="s">
         <v>218</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F138" s="59" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="27"/>
-      <c r="B139" s="33"/>
-      <c r="C139" s="1" t="s">
+      <c r="A139" s="92"/>
+      <c r="B139" s="65"/>
+      <c r="C139" s="59" t="s">
         <v>223</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D139" s="59" t="s">
         <v>213</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F139" s="59" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="27"/>
-      <c r="B140" s="33"/>
-      <c r="C140" s="1" t="s">
+      <c r="A140" s="92"/>
+      <c r="B140" s="65"/>
+      <c r="C140" s="59" t="s">
         <v>204</v>
       </c>
-      <c r="D140" s="1" t="s">
+      <c r="D140" s="59" t="s">
         <v>222</v>
       </c>
-      <c r="F140" s="1" t="s">
+      <c r="F140" s="59" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="27"/>
-      <c r="B141" s="33"/>
-      <c r="C141" s="1" t="s">
+      <c r="A141" s="92"/>
+      <c r="B141" s="65"/>
+      <c r="C141" s="59" t="s">
         <v>266</v>
       </c>
-      <c r="D141" s="1" t="s">
+      <c r="D141" s="59" t="s">
         <v>371</v>
       </c>
-      <c r="F141" s="1" t="s">
+      <c r="F141" s="59" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="27"/>
-      <c r="B142" s="33"/>
-      <c r="C142" s="1" t="s">
+      <c r="A142" s="92"/>
+      <c r="B142" s="65"/>
+      <c r="C142" s="59" t="s">
         <v>268</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" s="59" t="s">
         <v>267</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F142" s="59" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="27"/>
-      <c r="B143" s="33"/>
+      <c r="A143" s="92"/>
+      <c r="B143" s="65"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="27"/>
-      <c r="B144" s="36" t="s">
+      <c r="A144" s="92"/>
+      <c r="B144" s="70" t="s">
         <v>224</v>
       </c>
-      <c r="C144" s="11" t="s">
+      <c r="C144" s="71" t="s">
         <v>226</v>
       </c>
-      <c r="D144" s="11" t="s">
+      <c r="D144" s="71" t="s">
         <v>225</v>
       </c>
-      <c r="E144" s="11"/>
-      <c r="F144" s="11" t="s">
+      <c r="E144" s="71"/>
+      <c r="F144" s="71" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="27"/>
-      <c r="B145" s="39"/>
-      <c r="C145" s="1" t="s">
+      <c r="A145" s="92"/>
+      <c r="B145" s="86"/>
+      <c r="C145" s="59" t="s">
         <v>314</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D145" s="59" t="s">
         <v>315</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="F145" s="59" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="27"/>
-      <c r="B146" s="39"/>
-      <c r="C146" s="1" t="s">
+      <c r="A146" s="92"/>
+      <c r="B146" s="86"/>
+      <c r="C146" s="59" t="s">
         <v>227</v>
       </c>
-      <c r="D146" s="1" t="s">
+      <c r="D146" s="59" t="s">
         <v>228</v>
       </c>
-      <c r="F146" s="1" t="s">
+      <c r="F146" s="59" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="27"/>
-      <c r="B147" s="39"/>
-      <c r="C147" s="1" t="s">
+      <c r="A147" s="92"/>
+      <c r="B147" s="86"/>
+      <c r="C147" s="59" t="s">
         <v>269</v>
       </c>
-      <c r="D147" s="1" t="s">
+      <c r="D147" s="59" t="s">
         <v>270</v>
       </c>
-      <c r="F147" s="1" t="s">
+      <c r="F147" s="59" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="27"/>
-      <c r="B148" s="39"/>
-      <c r="C148" s="1" t="s">
+      <c r="A148" s="92"/>
+      <c r="B148" s="86"/>
+      <c r="C148" s="59" t="s">
         <v>271</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="D148" s="59" t="s">
         <v>310</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="F148" s="59" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="27"/>
-      <c r="B149" s="37"/>
+      <c r="A149" s="92"/>
+      <c r="B149" s="73"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="27"/>
-      <c r="B150" s="36" t="s">
+      <c r="A150" s="92"/>
+      <c r="B150" s="70" t="s">
         <v>390</v>
       </c>
-      <c r="C150" s="11" t="s">
+      <c r="C150" s="71" t="s">
         <v>391</v>
       </c>
-      <c r="D150" s="11" t="s">
+      <c r="D150" s="71" t="s">
         <v>392</v>
       </c>
-      <c r="E150" s="11"/>
-      <c r="F150" s="11" t="s">
+      <c r="E150" s="71"/>
+      <c r="F150" s="71" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="27"/>
-      <c r="B151" s="33"/>
-      <c r="C151" s="1" t="s">
+      <c r="A151" s="92"/>
+      <c r="B151" s="65"/>
+      <c r="C151" s="59" t="s">
         <v>393</v>
       </c>
-      <c r="D151" s="1" t="s">
+      <c r="D151" s="59" t="s">
         <v>394</v>
       </c>
-      <c r="F151" s="1" t="s">
+      <c r="F151" s="59" t="s">
         <v>275</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="B144:B149"/>
-    <mergeCell ref="A121:A151"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="B124:B130"/>
-    <mergeCell ref="B131:B143"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="A107:A120"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="B111:B114"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
@@ -5397,6 +5377,17 @@
     <mergeCell ref="B97:B106"/>
     <mergeCell ref="B78:B80"/>
     <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="B144:B149"/>
+    <mergeCell ref="A121:A151"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="B124:B130"/>
+    <mergeCell ref="B131:B143"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="A107:A120"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="B111:B114"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7669CA18-678E-4C19-8005-BB134C241C39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55259489-E8F6-46AD-93F3-6F6BBC09001B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -463,9 +463,6 @@
     <t>€/kWa</t>
   </si>
   <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
     <t>(%_Kapa)/h</t>
   </si>
   <si>
@@ -748,9 +745,6 @@
     <t>kW_el</t>
   </si>
   <si>
-    <t>€ h / kg a</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -1373,6 +1367,12 @@
   </si>
   <si>
     <t>€/a per kg_CH3OH/h</t>
+  </si>
+  <si>
+    <t>€/ kg a</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -1588,6 +1588,30 @@
     <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1633,69 +1657,45 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2073,10 +2073,10 @@
       <c r="G1" s="5"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="41" t="s">
+      <c r="A2" s="63" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="52" t="s">
+      <c r="B2" s="74" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -2093,8 +2093,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="42"/>
-      <c r="B3" s="50"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="72"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
@@ -2105,12 +2105,12 @@
         <v>50</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="42"/>
-      <c r="B4" s="50"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="72"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
@@ -2125,8 +2125,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="42"/>
-      <c r="B5" s="50"/>
+      <c r="A5" s="64"/>
+      <c r="B5" s="72"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -2141,8 +2141,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="42"/>
-      <c r="B6" s="50"/>
+      <c r="A6" s="64"/>
+      <c r="B6" s="72"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
@@ -2157,8 +2157,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="42"/>
-      <c r="B7" s="50"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="72"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
@@ -2173,31 +2173,31 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="42"/>
-      <c r="B8" s="53" t="s">
-        <v>231</v>
+      <c r="A8" s="64"/>
+      <c r="B8" s="75" t="s">
+        <v>229</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E8" s="14">
         <v>1.5</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="42"/>
-      <c r="B9" s="50"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="72"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E9" s="9">
         <v>285.39999999999998</v>
@@ -2207,78 +2207,78 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="42"/>
-      <c r="B10" s="50"/>
+      <c r="A10" s="64"/>
+      <c r="B10" s="72"/>
       <c r="C10" s="36" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E10" s="40">
         <v>0</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="42"/>
-      <c r="B11" s="50"/>
+      <c r="A11" s="64"/>
+      <c r="B11" s="72"/>
       <c r="C11" s="36" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E11" s="38">
         <f>0.05*5110</f>
         <v>255.5</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="42"/>
-      <c r="B12" s="50"/>
+      <c r="A12" s="64"/>
+      <c r="B12" s="72"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E12" s="9">
         <v>0.189</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="42"/>
-      <c r="B13" s="50"/>
+      <c r="A13" s="64"/>
+      <c r="B13" s="72"/>
       <c r="C13" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="E13" s="9">
         <v>1.375</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="42"/>
-      <c r="B14" s="50"/>
+      <c r="A14" s="64"/>
+      <c r="B14" s="72"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E14" s="12">
         <v>25</v>
@@ -2288,13 +2288,13 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="42"/>
-      <c r="B15" s="54"/>
+      <c r="A15" s="64"/>
+      <c r="B15" s="76"/>
       <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E15" s="16">
         <v>0.08</v>
@@ -2304,15 +2304,15 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="42"/>
-      <c r="B16" s="53" t="s">
-        <v>273</v>
+      <c r="A16" s="64"/>
+      <c r="B16" s="75" t="s">
+        <v>271</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E16" s="17">
         <v>3.7</v>
@@ -2322,45 +2322,45 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="42"/>
-      <c r="B17" s="50"/>
+      <c r="A17" s="64"/>
+      <c r="B17" s="72"/>
       <c r="C17" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E17" s="11">
         <v>0.27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="42"/>
-      <c r="B18" s="50"/>
+      <c r="A18" s="64"/>
+      <c r="B18" s="72"/>
       <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E18" s="11">
         <v>700</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="42"/>
-      <c r="B19" s="50"/>
+      <c r="A19" s="64"/>
+      <c r="B19" s="72"/>
       <c r="C19" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E19" s="11">
         <v>0.02</v>
@@ -2370,13 +2370,13 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="42"/>
-      <c r="B20" s="50"/>
+      <c r="A20" s="64"/>
+      <c r="B20" s="72"/>
       <c r="C20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E20" s="11">
         <v>20</v>
@@ -2386,13 +2386,13 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="42"/>
-      <c r="B21" s="54"/>
+      <c r="A21" s="64"/>
+      <c r="B21" s="76"/>
       <c r="C21" s="15" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="E21" s="16">
         <v>0.05</v>
@@ -2402,63 +2402,63 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="42"/>
-      <c r="B22" s="55" t="s">
-        <v>342</v>
+      <c r="A22" s="64"/>
+      <c r="B22" s="77" t="s">
+        <v>340</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="E22" s="9">
         <v>0.2</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="42"/>
-      <c r="B23" s="55"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="77"/>
       <c r="C23" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E23" s="9">
         <v>0.92800000000000005</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="42"/>
-      <c r="B24" s="55"/>
+      <c r="A24" s="64"/>
+      <c r="B24" s="77"/>
       <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E24" s="9">
         <v>1640</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="42"/>
-      <c r="B25" s="55"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="77"/>
       <c r="C25" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E25" s="11">
         <v>0.04</v>
@@ -2468,61 +2468,61 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="42"/>
-      <c r="B26" s="55"/>
+      <c r="A26" s="64"/>
+      <c r="B26" s="77"/>
       <c r="C26" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E26" s="11">
         <v>2.5</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="42"/>
-      <c r="B27" s="55"/>
+      <c r="A27" s="64"/>
+      <c r="B27" s="77"/>
       <c r="C27" s="6" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E27" s="11">
         <v>1.5</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="42"/>
-      <c r="B28" s="55"/>
+      <c r="A28" s="64"/>
+      <c r="B28" s="77"/>
       <c r="C28" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E28" s="11">
         <v>1.5E-3</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="42"/>
-      <c r="B29" s="55"/>
+      <c r="A29" s="64"/>
+      <c r="B29" s="77"/>
       <c r="C29" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E29" s="12">
         <v>25</v>
@@ -2532,13 +2532,13 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="42"/>
-      <c r="B30" s="55"/>
+      <c r="A30" s="64"/>
+      <c r="B30" s="77"/>
       <c r="C30" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="E30" s="11">
         <v>0.08</v>
@@ -2548,10 +2548,10 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="41" t="s">
+      <c r="A31" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="45" t="s">
+      <c r="B31" s="67" t="s">
         <v>3</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -2564,12 +2564,12 @@
         <v>490</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="42"/>
-      <c r="B32" s="46"/>
+      <c r="A32" s="64"/>
+      <c r="B32" s="68"/>
       <c r="C32" s="6" t="s">
         <v>11</v>
       </c>
@@ -2584,8 +2584,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="42"/>
-      <c r="B33" s="46"/>
+      <c r="A33" s="64"/>
+      <c r="B33" s="68"/>
       <c r="C33" s="6" t="s">
         <v>13</v>
       </c>
@@ -2600,8 +2600,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="42"/>
-      <c r="B34" s="46"/>
+      <c r="A34" s="64"/>
+      <c r="B34" s="68"/>
       <c r="C34" s="6" t="s">
         <v>20</v>
       </c>
@@ -2612,12 +2612,12 @@
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="42"/>
-      <c r="B35" s="46"/>
+      <c r="A35" s="64"/>
+      <c r="B35" s="68"/>
       <c r="C35" s="6" t="s">
         <v>35</v>
       </c>
@@ -2632,8 +2632,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="42"/>
-      <c r="B36" s="46"/>
+      <c r="A36" s="64"/>
+      <c r="B36" s="68"/>
       <c r="C36" s="6" t="s">
         <v>36</v>
       </c>
@@ -2648,8 +2648,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="42"/>
-      <c r="B37" s="46"/>
+      <c r="A37" s="64"/>
+      <c r="B37" s="68"/>
       <c r="C37" s="6" t="s">
         <v>15</v>
       </c>
@@ -2664,8 +2664,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="42"/>
-      <c r="B38" s="47"/>
+      <c r="A38" s="64"/>
+      <c r="B38" s="69"/>
       <c r="C38" s="15" t="s">
         <v>88</v>
       </c>
@@ -2676,35 +2676,35 @@
         <v>0</v>
       </c>
       <c r="F38" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="42"/>
-      <c r="B39" s="48" t="s">
-        <v>317</v>
+      <c r="A39" s="64"/>
+      <c r="B39" s="70" t="s">
+        <v>315</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E39" s="18">
         <v>2.83</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="42"/>
-      <c r="B40" s="46"/>
+      <c r="A40" s="64"/>
+      <c r="B40" s="68"/>
       <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E40" s="11">
         <v>0.03</v>
@@ -2714,13 +2714,13 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="42"/>
-      <c r="B41" s="46"/>
+      <c r="A41" s="64"/>
+      <c r="B41" s="68"/>
       <c r="C41" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E41" s="12">
         <v>30</v>
@@ -2730,29 +2730,29 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="42"/>
-      <c r="B42" s="46"/>
+      <c r="A42" s="64"/>
+      <c r="B42" s="68"/>
       <c r="C42" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E42" s="11">
         <v>7.3999999999999999E-4</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="42"/>
-      <c r="B43" s="46"/>
+      <c r="A43" s="64"/>
+      <c r="B43" s="68"/>
       <c r="C43" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E43" s="11">
         <v>0.98</v>
@@ -2762,13 +2762,13 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="42"/>
-      <c r="B44" s="46"/>
+      <c r="A44" s="64"/>
+      <c r="B44" s="68"/>
       <c r="C44" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E44" s="11">
         <v>0.98</v>
@@ -2778,13 +2778,13 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="42"/>
-      <c r="B45" s="46"/>
+      <c r="A45" s="64"/>
+      <c r="B45" s="68"/>
       <c r="C45" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E45" s="11">
         <v>0.05</v>
@@ -2794,25 +2794,25 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="42"/>
-      <c r="B46" s="46"/>
+      <c r="A46" s="64"/>
+      <c r="B46" s="68"/>
       <c r="C46" s="15" t="s">
         <v>88</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="E46" s="16">
         <v>0</v>
       </c>
       <c r="F46" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="42"/>
-      <c r="B47" s="48" t="s">
-        <v>203</v>
+      <c r="A47" s="64"/>
+      <c r="B47" s="70" t="s">
+        <v>201</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>91</v>
@@ -2824,12 +2824,12 @@
         <v>1.6999999999999999E-3</v>
       </c>
       <c r="F47" s="13" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="42"/>
-      <c r="B48" s="50"/>
+      <c r="A48" s="64"/>
+      <c r="B48" s="72"/>
       <c r="C48" s="6" t="s">
         <v>21</v>
       </c>
@@ -2845,8 +2845,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="42"/>
-      <c r="B49" s="50"/>
+      <c r="A49" s="64"/>
+      <c r="B49" s="72"/>
       <c r="C49" s="6" t="s">
         <v>16</v>
       </c>
@@ -2861,8 +2861,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="42"/>
-      <c r="B50" s="50"/>
+      <c r="A50" s="64"/>
+      <c r="B50" s="72"/>
       <c r="C50" s="6" t="s">
         <v>17</v>
       </c>
@@ -2877,8 +2877,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="42"/>
-      <c r="B51" s="50"/>
+      <c r="A51" s="64"/>
+      <c r="B51" s="72"/>
       <c r="C51" s="6" t="s">
         <v>35</v>
       </c>
@@ -2893,8 +2893,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="42"/>
-      <c r="B52" s="50"/>
+      <c r="A52" s="64"/>
+      <c r="B52" s="72"/>
       <c r="C52" s="6" t="s">
         <v>36</v>
       </c>
@@ -2909,8 +2909,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="42"/>
-      <c r="B53" s="50"/>
+      <c r="A53" s="64"/>
+      <c r="B53" s="72"/>
       <c r="C53" s="6" t="s">
         <v>89</v>
       </c>
@@ -2925,8 +2925,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="42"/>
-      <c r="B54" s="50"/>
+      <c r="A54" s="64"/>
+      <c r="B54" s="72"/>
       <c r="C54" s="6" t="s">
         <v>88</v>
       </c>
@@ -2937,12 +2937,12 @@
         <v>0</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="42"/>
-      <c r="B55" s="50"/>
+      <c r="A55" s="64"/>
+      <c r="B55" s="72"/>
       <c r="C55" s="6" t="s">
         <v>13</v>
       </c>
@@ -2957,8 +2957,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="43"/>
-      <c r="B56" s="51"/>
+      <c r="A56" s="65"/>
+      <c r="B56" s="73"/>
       <c r="C56" s="20" t="s">
         <v>15</v>
       </c>
@@ -2973,7 +2973,7 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="41" t="s">
+      <c r="A57" s="63" t="s">
         <v>72</v>
       </c>
       <c r="B57" s="22" t="s">
@@ -2993,44 +2993,44 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="44"/>
+      <c r="A58" s="66"/>
       <c r="B58" s="25" t="s">
+        <v>380</v>
+      </c>
+      <c r="C58" s="26" t="s">
+        <v>381</v>
+      </c>
+      <c r="D58" s="26" t="s">
         <v>382</v>
-      </c>
-      <c r="C58" s="26" t="s">
-        <v>383</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>384</v>
       </c>
       <c r="E58" s="27">
         <v>5</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="44"/>
+      <c r="A59" s="66"/>
       <c r="B59" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="C59" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="D59" s="29" t="s">
         <v>343</v>
-      </c>
-      <c r="C59" s="29" t="s">
-        <v>344</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>345</v>
       </c>
       <c r="E59" s="30">
         <v>0</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="42"/>
-      <c r="B60" s="48" t="s">
+      <c r="A60" s="64"/>
+      <c r="B60" s="70" t="s">
         <v>4</v>
       </c>
       <c r="C60" s="13" t="s">
@@ -3047,8 +3047,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="42"/>
-      <c r="B61" s="46"/>
+      <c r="A61" s="64"/>
+      <c r="B61" s="68"/>
       <c r="C61" s="6" t="s">
         <v>10</v>
       </c>
@@ -3063,8 +3063,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="42"/>
-      <c r="B62" s="46"/>
+      <c r="A62" s="64"/>
+      <c r="B62" s="68"/>
       <c r="C62" s="6" t="s">
         <v>17</v>
       </c>
@@ -3079,8 +3079,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="42"/>
-      <c r="B63" s="46"/>
+      <c r="A63" s="64"/>
+      <c r="B63" s="68"/>
       <c r="C63" s="6" t="s">
         <v>18</v>
       </c>
@@ -3095,8 +3095,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="42"/>
-      <c r="B64" s="46"/>
+      <c r="A64" s="64"/>
+      <c r="B64" s="68"/>
       <c r="C64" s="6" t="s">
         <v>13</v>
       </c>
@@ -3111,8 +3111,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="42"/>
-      <c r="B65" s="46"/>
+      <c r="A65" s="64"/>
+      <c r="B65" s="68"/>
       <c r="C65" s="6" t="s">
         <v>68</v>
       </c>
@@ -3127,8 +3127,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="42"/>
-      <c r="B66" s="47"/>
+      <c r="A66" s="64"/>
+      <c r="B66" s="69"/>
       <c r="C66" s="15" t="s">
         <v>15</v>
       </c>
@@ -3143,8 +3143,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="42"/>
-      <c r="B67" s="48" t="s">
+      <c r="A67" s="64"/>
+      <c r="B67" s="70" t="s">
         <v>5</v>
       </c>
       <c r="C67" s="13" t="s">
@@ -3161,8 +3161,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="42"/>
-      <c r="B68" s="46"/>
+      <c r="A68" s="64"/>
+      <c r="B68" s="68"/>
       <c r="C68" s="6" t="s">
         <v>10</v>
       </c>
@@ -3177,8 +3177,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="42"/>
-      <c r="B69" s="46"/>
+      <c r="A69" s="64"/>
+      <c r="B69" s="68"/>
       <c r="C69" s="6" t="s">
         <v>17</v>
       </c>
@@ -3193,8 +3193,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="42"/>
-      <c r="B70" s="46"/>
+      <c r="A70" s="64"/>
+      <c r="B70" s="68"/>
       <c r="C70" s="6" t="s">
         <v>18</v>
       </c>
@@ -3209,8 +3209,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="42"/>
-      <c r="B71" s="46"/>
+      <c r="A71" s="64"/>
+      <c r="B71" s="68"/>
       <c r="C71" s="6" t="s">
         <v>13</v>
       </c>
@@ -3225,8 +3225,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="42"/>
-      <c r="B72" s="46"/>
+      <c r="A72" s="64"/>
+      <c r="B72" s="68"/>
       <c r="C72" s="6" t="s">
         <v>68</v>
       </c>
@@ -3241,8 +3241,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="43"/>
-      <c r="B73" s="49"/>
+      <c r="A73" s="65"/>
+      <c r="B73" s="71"/>
       <c r="C73" s="20" t="s">
         <v>15</v>
       </c>
@@ -3257,7 +3257,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="41" t="s">
+      <c r="A74" s="63" t="s">
         <v>76</v>
       </c>
       <c r="B74" s="34" t="s">
@@ -3277,25 +3277,25 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="42"/>
+      <c r="A75" s="64"/>
       <c r="B75" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>299</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>301</v>
       </c>
       <c r="E75" s="11">
         <v>-1E-4</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="42"/>
+      <c r="A76" s="64"/>
       <c r="B76" s="35" t="s">
         <v>79</v>
       </c>
@@ -3313,21 +3313,21 @@
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="43"/>
+      <c r="A77" s="65"/>
       <c r="B77" s="3" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E77" s="21">
         <v>-0.6</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -3357,2011 +3357,2022 @@
   <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="59" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="59" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="59" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="59" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="59" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="59"/>
+    <col min="1" max="1" width="14.5546875" style="44" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5546875" style="44" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="44" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" style="44" customWidth="1"/>
+    <col min="6" max="6" width="37.5546875" style="44" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="44"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="57" t="s">
+      <c r="B1" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="57" t="s">
+      <c r="C1" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D1" s="57" t="s">
+      <c r="D1" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="57" t="s">
+      <c r="F1" s="42" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="60" t="s">
+      <c r="A2" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="61" t="s">
+      <c r="B2" s="81" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="45" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="62" t="s">
+      <c r="E2" s="46"/>
+      <c r="F2" s="45" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="63"/>
-      <c r="F2" s="62" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="80"/>
+      <c r="B3" s="82"/>
+      <c r="C3" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="47"/>
+      <c r="F3" s="44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="80"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="48"/>
+      <c r="F4" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="80"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="44" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="49"/>
+      <c r="F5" s="44" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="80"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="50"/>
+      <c r="F6" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="80"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="50"/>
+      <c r="F7" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="80"/>
+      <c r="B8" s="82"/>
+      <c r="C8" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="50"/>
+      <c r="F8" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="80"/>
+      <c r="B9" s="82"/>
+      <c r="C9" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="50"/>
+      <c r="F9" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="80"/>
+      <c r="B10" s="82"/>
+      <c r="C10" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="50"/>
+      <c r="F10" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="80"/>
+      <c r="B11" s="82"/>
+      <c r="E11" s="49"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="80"/>
+      <c r="B12" s="83" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="52"/>
+      <c r="F12" s="51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="80"/>
+      <c r="B13" s="82"/>
+      <c r="C13" s="44" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="E13" s="47"/>
+      <c r="F13" s="44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="80"/>
+      <c r="B14" s="82"/>
+      <c r="C14" s="44" t="s">
+        <v>139</v>
+      </c>
+      <c r="D14" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="80"/>
+      <c r="B15" s="82"/>
+      <c r="C15" s="44" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="E15" s="49"/>
+      <c r="F15" s="44" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="80"/>
+      <c r="B16" s="82"/>
+      <c r="C16" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D16" s="44" t="s">
+        <v>247</v>
+      </c>
+      <c r="E16" s="47"/>
+      <c r="F16" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="80"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="44" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17" s="47"/>
+      <c r="F17" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="80"/>
+      <c r="B18" s="82"/>
+      <c r="C18" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" s="50"/>
+      <c r="F18" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="80"/>
+      <c r="B19" s="82"/>
+      <c r="C19" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="E19" s="50"/>
+      <c r="F19" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="80"/>
+      <c r="B20" s="82"/>
+      <c r="C20" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>251</v>
+      </c>
+      <c r="E20" s="50"/>
+      <c r="F20" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="80"/>
+      <c r="B21" s="82"/>
+      <c r="C21" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>252</v>
+      </c>
+      <c r="E21" s="50"/>
+      <c r="F21" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="80"/>
+      <c r="B22" s="84"/>
+      <c r="C22" s="53"/>
+      <c r="D22" s="53"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="53"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="80"/>
+      <c r="B23" s="83" t="s">
+        <v>271</v>
+      </c>
+      <c r="C23" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>283</v>
+      </c>
+      <c r="E23" s="47"/>
+      <c r="F23" s="44" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="80"/>
+      <c r="B24" s="82"/>
+      <c r="C24" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D24" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="E24" s="47"/>
+      <c r="F24" s="44" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="80"/>
+      <c r="B25" s="82"/>
+      <c r="C25" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="E25" s="49"/>
+      <c r="F25" s="44" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="80"/>
+      <c r="B26" s="82"/>
+      <c r="C26" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="D26" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="E26" s="50"/>
+      <c r="F26" s="44" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="80"/>
+      <c r="B27" s="82"/>
+      <c r="C27" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="E27" s="50"/>
+      <c r="F27" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="80"/>
+      <c r="B28" s="82"/>
+      <c r="C28" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="E28" s="50"/>
+      <c r="F28" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="80"/>
+      <c r="B29" s="82"/>
+      <c r="C29" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="E29" s="50"/>
+      <c r="F29" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="80"/>
+      <c r="B30" s="82"/>
+      <c r="C30" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="E30" s="49"/>
+      <c r="F30" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="80"/>
+      <c r="B31" s="82"/>
+      <c r="C31" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="E31" s="49"/>
+      <c r="F31" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="80"/>
+      <c r="B32" s="84"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="54"/>
+      <c r="F32" s="53"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="80"/>
+      <c r="B33" s="85" t="s">
+        <v>358</v>
+      </c>
+      <c r="C33" s="44" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="44" t="s">
+        <v>359</v>
+      </c>
+      <c r="E33" s="47"/>
+      <c r="F33" s="44" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="80"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="44" t="s">
+        <v>360</v>
+      </c>
+      <c r="E34" s="47"/>
+      <c r="F34" s="44" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="80"/>
+      <c r="B35" s="85"/>
+      <c r="C35" s="44" t="s">
+        <v>84</v>
+      </c>
+      <c r="D35" s="44" t="s">
+        <v>361</v>
+      </c>
+      <c r="E35" s="49"/>
+      <c r="F35" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="80"/>
+      <c r="B36" s="85"/>
+      <c r="C36" s="44" t="s">
+        <v>281</v>
+      </c>
+      <c r="D36" s="44" t="s">
+        <v>363</v>
+      </c>
+      <c r="E36" s="49"/>
+      <c r="F36" s="44" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="80"/>
+      <c r="B37" s="85"/>
+      <c r="C37" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D37" s="44" t="s">
+        <v>373</v>
+      </c>
+      <c r="E37" s="49"/>
+      <c r="F37" s="44" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="80"/>
+      <c r="B38" s="85"/>
+      <c r="C38" s="44" t="s">
+        <v>258</v>
+      </c>
+      <c r="D38" s="44" t="s">
+        <v>362</v>
+      </c>
+      <c r="E38" s="50"/>
+      <c r="F38" s="44" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="80"/>
+      <c r="B39" s="85"/>
+      <c r="C39" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="44" t="s">
+        <v>364</v>
+      </c>
+      <c r="E39" s="50"/>
+      <c r="F39" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="80"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="44" t="s">
+        <v>367</v>
+      </c>
+      <c r="E40" s="50"/>
+      <c r="F40" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="80"/>
+      <c r="B41" s="85"/>
+      <c r="C41" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="44" t="s">
+        <v>379</v>
+      </c>
+      <c r="E41" s="50"/>
+      <c r="F41" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="80"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" s="44" t="s">
+        <v>365</v>
+      </c>
+      <c r="E42" s="50"/>
+      <c r="F42" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="80"/>
+      <c r="B43" s="85"/>
+      <c r="C43" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" s="44" t="s">
+        <v>366</v>
+      </c>
+      <c r="E43" s="49"/>
+      <c r="F43" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="80"/>
+      <c r="B44" s="85"/>
+      <c r="C44" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="44" t="s">
+        <v>368</v>
+      </c>
+      <c r="E44" s="49"/>
+      <c r="F44" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="80"/>
+      <c r="B45" s="85"/>
+      <c r="E45" s="49"/>
+    </row>
+    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="79" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="89" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="45" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="45" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="55"/>
+      <c r="F46" s="45" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="80"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" s="44" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="49"/>
+      <c r="F47" s="44" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="80"/>
+      <c r="B48" s="85"/>
+      <c r="C48" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" s="44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="50"/>
+      <c r="F48" s="44" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="80"/>
+      <c r="B49" s="85"/>
+      <c r="C49" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="D49" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" s="49"/>
+      <c r="F49" s="44" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="80"/>
+      <c r="B50" s="85"/>
+      <c r="C50" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D50" s="44" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="49"/>
+      <c r="F50" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="80"/>
+      <c r="B51" s="85"/>
+      <c r="C51" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="49"/>
+      <c r="F51" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="80"/>
+      <c r="B52" s="85"/>
+      <c r="C52" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" s="44" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" s="49"/>
+      <c r="F52" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="80"/>
+      <c r="B53" s="85"/>
+      <c r="C53" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" s="49"/>
+      <c r="F53" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="80"/>
+      <c r="B54" s="85"/>
+      <c r="C54" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D54" s="44" t="s">
+        <v>193</v>
+      </c>
+      <c r="E54" s="49"/>
+      <c r="F54" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="80"/>
+      <c r="B55" s="90"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="54"/>
+      <c r="F55" s="53"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="80"/>
+      <c r="B56" s="85" t="s">
+        <v>315</v>
+      </c>
+      <c r="C56" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="44" t="s">
+        <v>325</v>
+      </c>
+      <c r="E56" s="47"/>
+      <c r="F56" s="44" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="80"/>
+      <c r="B57" s="85"/>
+      <c r="C57" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="44" t="s">
+        <v>326</v>
+      </c>
+      <c r="E57" s="49"/>
+      <c r="F57" s="44" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="80"/>
+      <c r="B58" s="85"/>
+      <c r="C58" s="44" t="s">
+        <v>135</v>
+      </c>
+      <c r="D58" s="44" t="s">
+        <v>327</v>
+      </c>
+      <c r="E58" s="50"/>
+      <c r="F58" s="44" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="80"/>
+      <c r="B59" s="85"/>
+      <c r="C59" s="44" t="s">
+        <v>136</v>
+      </c>
+      <c r="D59" s="44" t="s">
+        <v>328</v>
+      </c>
+      <c r="E59" s="49"/>
+      <c r="F59" s="44" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="80"/>
+      <c r="B60" s="85"/>
+      <c r="C60" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D60" s="44" t="s">
+        <v>329</v>
+      </c>
+      <c r="E60" s="49"/>
+      <c r="F60" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="80"/>
+      <c r="B61" s="85"/>
+      <c r="C61" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D61" s="44" t="s">
+        <v>330</v>
+      </c>
+      <c r="E61" s="49"/>
+      <c r="F61" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="80"/>
+      <c r="B62" s="85"/>
+      <c r="C62" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D62" s="44" t="s">
+        <v>331</v>
+      </c>
+      <c r="E62" s="49"/>
+      <c r="F62" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="80"/>
+      <c r="B63" s="85"/>
+      <c r="C63" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D63" s="44" t="s">
+        <v>332</v>
+      </c>
+      <c r="E63" s="49"/>
+      <c r="F63" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="80"/>
+      <c r="B64" s="85"/>
+      <c r="C64" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D64" s="44" t="s">
+        <v>333</v>
+      </c>
+      <c r="E64" s="49"/>
+      <c r="F64" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="80"/>
+      <c r="B65" s="90"/>
+      <c r="E65" s="49"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="80"/>
+      <c r="B66" s="87" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="51" t="s">
+        <v>100</v>
+      </c>
+      <c r="E66" s="56"/>
+      <c r="F66" s="51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="80"/>
+      <c r="B67" s="85"/>
+      <c r="C67" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="44" t="s">
+        <v>102</v>
+      </c>
+      <c r="E67" s="49"/>
+      <c r="F67" s="44" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="80"/>
+      <c r="B68" s="82"/>
+      <c r="C68" s="44" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="E68" s="47"/>
+      <c r="F68" s="44" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="80"/>
+      <c r="B69" s="82"/>
+      <c r="C69" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D69" s="44" t="s">
+        <v>185</v>
+      </c>
+      <c r="E69" s="47"/>
+      <c r="F69" s="44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="80"/>
+      <c r="B70" s="82"/>
+      <c r="C70" s="44" t="s">
+        <v>126</v>
+      </c>
+      <c r="D70" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="E70" s="47"/>
+      <c r="F70" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="80"/>
+      <c r="B71" s="82"/>
+      <c r="C71" s="44" t="s">
+        <v>127</v>
+      </c>
+      <c r="D71" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="E71" s="49"/>
+      <c r="F71" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="80"/>
+      <c r="B72" s="82"/>
+      <c r="C72" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D72" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="E72" s="47"/>
+      <c r="F72" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="80"/>
+      <c r="B73" s="82"/>
+      <c r="C73" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D73" s="44" t="s">
+        <v>157</v>
+      </c>
+      <c r="E73" s="49"/>
+      <c r="F73" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="80"/>
+      <c r="B74" s="82"/>
+      <c r="C74" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D74" s="44" t="s">
+        <v>200</v>
+      </c>
+      <c r="E74" s="49"/>
+      <c r="F74" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="80"/>
+      <c r="B75" s="82"/>
+      <c r="C75" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D75" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="E75" s="49"/>
+      <c r="F75" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="80"/>
+      <c r="B76" s="82"/>
+      <c r="C76" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D76" s="44" t="s">
+        <v>192</v>
+      </c>
+      <c r="E76" s="49"/>
+      <c r="F76" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="86"/>
+      <c r="B77" s="88"/>
+      <c r="C77" s="57"/>
+      <c r="D77" s="57"/>
+      <c r="E77" s="58"/>
+      <c r="F77" s="57"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="79" t="s">
+        <v>72</v>
+      </c>
+      <c r="B78" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="C78" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="D78" s="45" t="s">
+        <v>116</v>
+      </c>
+      <c r="E78" s="55"/>
+      <c r="F78" s="45" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="80"/>
+      <c r="B79" s="78"/>
+      <c r="C79" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="D79" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="E79" s="60"/>
+      <c r="F79" s="59" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="80"/>
+      <c r="B80" s="84"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="61"/>
+      <c r="F80" s="53"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="80"/>
+      <c r="B81" s="83" t="s">
+        <v>341</v>
+      </c>
+      <c r="C81" s="51" t="s">
+        <v>344</v>
+      </c>
+      <c r="D81" s="51" t="s">
+        <v>347</v>
+      </c>
+      <c r="E81" s="52"/>
+      <c r="F81" s="51" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="80"/>
+      <c r="B82" s="78"/>
+      <c r="C82" s="59" t="s">
+        <v>345</v>
+      </c>
+      <c r="D82" s="59" t="s">
+        <v>348</v>
+      </c>
+      <c r="E82" s="60"/>
+      <c r="F82" s="59" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="80"/>
+      <c r="B83" s="84"/>
+      <c r="C83" s="53"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="61"/>
+      <c r="F83" s="53"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="80"/>
+      <c r="B84" s="78" t="s">
+        <v>383</v>
+      </c>
+      <c r="C84" s="59" t="s">
+        <v>384</v>
+      </c>
+      <c r="D84" s="59" t="s">
+        <v>386</v>
+      </c>
+      <c r="E84" s="60"/>
+      <c r="F84" s="59" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="80"/>
+      <c r="B85" s="78"/>
+      <c r="C85" s="44" t="s">
+        <v>385</v>
+      </c>
+      <c r="D85" s="44" t="s">
+        <v>387</v>
+      </c>
+      <c r="E85" s="47"/>
+      <c r="F85" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="80"/>
+      <c r="B86" s="78"/>
+      <c r="E86" s="47"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A87" s="80"/>
+      <c r="B87" s="87" t="s">
+        <v>4</v>
+      </c>
+      <c r="C87" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D87" s="51" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="64"/>
-      <c r="B3" s="65"/>
-      <c r="C3" s="59" t="s">
+      <c r="E87" s="56"/>
+      <c r="F87" s="51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A88" s="80"/>
+      <c r="B88" s="85"/>
+      <c r="C88" s="44" t="s">
+        <v>107</v>
+      </c>
+      <c r="D88" s="44" t="s">
+        <v>109</v>
+      </c>
+      <c r="E88" s="1"/>
+      <c r="F88" s="44" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A89" s="80"/>
+      <c r="B89" s="85"/>
+      <c r="C89" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="D89" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="E89" s="1"/>
+      <c r="F89" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A90" s="80"/>
+      <c r="B90" s="85"/>
+      <c r="C90" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D90" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="E90" s="47"/>
+      <c r="F90" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A91" s="80"/>
+      <c r="B91" s="85"/>
+      <c r="C91" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D91" s="44" t="s">
+        <v>156</v>
+      </c>
+      <c r="E91" s="50"/>
+      <c r="F91" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A92" s="80"/>
+      <c r="B92" s="85"/>
+      <c r="C92" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D92" s="44" t="s">
+        <v>162</v>
+      </c>
+      <c r="E92" s="47"/>
+      <c r="F92" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A93" s="80"/>
+      <c r="B93" s="85"/>
+      <c r="C93" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D93" s="44" t="s">
+        <v>198</v>
+      </c>
+      <c r="E93" s="47"/>
+      <c r="F93" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A94" s="80"/>
+      <c r="B94" s="85"/>
+      <c r="C94" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D94" s="44" t="s">
+        <v>169</v>
+      </c>
+      <c r="E94" s="49"/>
+      <c r="F94" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A95" s="80"/>
+      <c r="B95" s="85"/>
+      <c r="C95" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D95" s="44" t="s">
+        <v>190</v>
+      </c>
+      <c r="E95" s="49"/>
+      <c r="F95" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A96" s="80"/>
+      <c r="B96" s="90"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A97" s="80"/>
+      <c r="B97" s="87" t="s">
+        <v>5</v>
+      </c>
+      <c r="C97" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="D97" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="E97" s="56"/>
+      <c r="F97" s="51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A98" s="80"/>
+      <c r="B98" s="85"/>
+      <c r="C98" s="44" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="59" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="59" t="s">
+      <c r="D98" s="44" t="s">
+        <v>106</v>
+      </c>
+      <c r="E98" s="1"/>
+      <c r="F98" s="44" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="64"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" s="59" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="67"/>
-      <c r="F4" s="59" t="s">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="80"/>
+      <c r="B99" s="85"/>
+      <c r="C99" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="D99" s="44" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="64"/>
-      <c r="B5" s="65"/>
-      <c r="C5" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="D5" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="68"/>
-      <c r="F5" s="59" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="64"/>
-      <c r="B6" s="65"/>
-      <c r="C6" s="59" t="s">
+      <c r="E99" s="1"/>
+      <c r="F99" s="44" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="80"/>
+      <c r="B100" s="85"/>
+      <c r="C100" s="44" t="s">
+        <v>141</v>
+      </c>
+      <c r="D100" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="59" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="69"/>
-      <c r="F6" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="64"/>
-      <c r="B7" s="65"/>
-      <c r="C7" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="69"/>
-      <c r="F7" s="59" t="s">
+      <c r="E100" s="1"/>
+      <c r="F100" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="80"/>
+      <c r="B101" s="85"/>
+      <c r="C101" s="44" t="s">
+        <v>155</v>
+      </c>
+      <c r="D101" s="44" t="s">
+        <v>154</v>
+      </c>
+      <c r="E101" s="50"/>
+      <c r="F101" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="80"/>
+      <c r="B102" s="85"/>
+      <c r="C102" s="44" t="s">
+        <v>161</v>
+      </c>
+      <c r="D102" s="44" t="s">
+        <v>160</v>
+      </c>
+      <c r="E102" s="62"/>
+      <c r="F102" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A103" s="80"/>
+      <c r="B103" s="85"/>
+      <c r="C103" s="44" t="s">
+        <v>196</v>
+      </c>
+      <c r="D103" s="44" t="s">
+        <v>197</v>
+      </c>
+      <c r="E103" s="62"/>
+      <c r="F103" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="80"/>
+      <c r="B104" s="85"/>
+      <c r="C104" s="44" t="s">
+        <v>167</v>
+      </c>
+      <c r="D104" s="44" t="s">
+        <v>168</v>
+      </c>
+      <c r="E104" s="49"/>
+      <c r="F104" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="80"/>
+      <c r="B105" s="85"/>
+      <c r="C105" s="44" t="s">
+        <v>188</v>
+      </c>
+      <c r="D105" s="44" t="s">
+        <v>189</v>
+      </c>
+      <c r="E105" s="49"/>
+      <c r="F105" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A106" s="86"/>
+      <c r="B106" s="91"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B107" s="81" t="s">
+        <v>73</v>
+      </c>
+      <c r="C107" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="D107" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="E107" s="46"/>
+      <c r="F107" s="45" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="80"/>
+      <c r="B108" s="82"/>
+      <c r="C108" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="D108" s="44" t="s">
+        <v>227</v>
+      </c>
+      <c r="E108" s="49"/>
+      <c r="F108" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="80"/>
+      <c r="B109" s="82"/>
+      <c r="C109" s="44" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="64"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="59" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="69"/>
-      <c r="F8" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="64"/>
-      <c r="B9" s="65"/>
-      <c r="C9" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" s="69"/>
-      <c r="F9" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="64"/>
-      <c r="B10" s="65"/>
-      <c r="C10" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="69"/>
-      <c r="F10" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="64"/>
-      <c r="B11" s="65"/>
-      <c r="E11" s="68"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="64"/>
-      <c r="B12" s="70" t="s">
-        <v>231</v>
-      </c>
-      <c r="C12" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="71" t="s">
-        <v>247</v>
-      </c>
-      <c r="E12" s="72"/>
-      <c r="F12" s="71" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="64"/>
-      <c r="B13" s="65"/>
-      <c r="C13" s="59" t="s">
-        <v>255</v>
-      </c>
-      <c r="D13" s="59" t="s">
-        <v>298</v>
-      </c>
-      <c r="E13" s="66"/>
-      <c r="F13" s="59" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="64"/>
-      <c r="B14" s="65"/>
-      <c r="C14" s="59" t="s">
+      <c r="D109" s="44" t="s">
+        <v>147</v>
+      </c>
+      <c r="E109" s="49"/>
+      <c r="F109" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="80"/>
+      <c r="B110" s="84"/>
+      <c r="C110" s="53"/>
+      <c r="D110" s="53"/>
+      <c r="E110" s="54"/>
+      <c r="F110" s="53"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="80"/>
+      <c r="B111" s="83" t="s">
+        <v>301</v>
+      </c>
+      <c r="C111" s="44" t="s">
+        <v>302</v>
+      </c>
+      <c r="D111" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="E111" s="49"/>
+      <c r="F111" s="44" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="80"/>
+      <c r="B112" s="82"/>
+      <c r="C112" s="44" t="s">
+        <v>306</v>
+      </c>
+      <c r="D112" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="E112" s="49"/>
+      <c r="F112" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="80"/>
+      <c r="B113" s="82"/>
+      <c r="C113" s="44" t="s">
+        <v>307</v>
+      </c>
+      <c r="D113" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="E113" s="49"/>
+      <c r="F113" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="80"/>
+      <c r="B114" s="84"/>
+      <c r="E114" s="49"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A115" s="80"/>
+      <c r="B115" s="83" t="s">
+        <v>79</v>
+      </c>
+      <c r="C115" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D115" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="E115" s="56"/>
+      <c r="F115" s="51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="80"/>
+      <c r="B116" s="82"/>
+      <c r="C116" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="D116" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="E116" s="49"/>
+      <c r="F116" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="80"/>
+      <c r="B117" s="84"/>
+      <c r="C117" s="53"/>
+      <c r="D117" s="53"/>
+      <c r="E117" s="54"/>
+      <c r="F117" s="53"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A118" s="80"/>
+      <c r="B118" s="83" t="s">
+        <v>260</v>
+      </c>
+      <c r="C118" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="D118" s="44" t="s">
+        <v>262</v>
+      </c>
+      <c r="E118" s="49"/>
+      <c r="F118" s="44" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A119" s="80"/>
+      <c r="B119" s="82"/>
+      <c r="C119" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="D119" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="E119" s="49"/>
+      <c r="F119" s="44" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="86"/>
+      <c r="B120" s="88"/>
+      <c r="C120" s="57"/>
+      <c r="D120" s="57"/>
+      <c r="E120" s="58"/>
+      <c r="F120" s="57"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="79" t="s">
+        <v>163</v>
+      </c>
+      <c r="B121" s="81" t="s">
+        <v>13</v>
+      </c>
+      <c r="C121" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D121" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E121" s="45"/>
+      <c r="F121" s="45" t="s">
         <v>140</v>
-      </c>
-      <c r="D14" s="59" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="64"/>
-      <c r="B15" s="65"/>
-      <c r="C15" s="59" t="s">
-        <v>256</v>
-      </c>
-      <c r="D15" s="59" t="s">
-        <v>257</v>
-      </c>
-      <c r="E15" s="68"/>
-      <c r="F15" s="59" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="64"/>
-      <c r="B16" s="65"/>
-      <c r="C16" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D16" s="59" t="s">
-        <v>249</v>
-      </c>
-      <c r="E16" s="66"/>
-      <c r="F16" s="59" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="64"/>
-      <c r="B17" s="65"/>
-      <c r="C17" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="59" t="s">
-        <v>250</v>
-      </c>
-      <c r="E17" s="66"/>
-      <c r="F17" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="64"/>
-      <c r="B18" s="65"/>
-      <c r="C18" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="59" t="s">
-        <v>251</v>
-      </c>
-      <c r="E18" s="69"/>
-      <c r="F18" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="64"/>
-      <c r="B19" s="65"/>
-      <c r="C19" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19" s="59" t="s">
-        <v>252</v>
-      </c>
-      <c r="E19" s="69"/>
-      <c r="F19" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="64"/>
-      <c r="B20" s="65"/>
-      <c r="C20" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="59" t="s">
-        <v>253</v>
-      </c>
-      <c r="E20" s="69"/>
-      <c r="F20" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="64"/>
-      <c r="B21" s="65"/>
-      <c r="C21" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="59" t="s">
-        <v>254</v>
-      </c>
-      <c r="E21" s="69"/>
-      <c r="F21" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="64"/>
-      <c r="B22" s="73"/>
-      <c r="C22" s="74"/>
-      <c r="D22" s="74"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="74"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="64"/>
-      <c r="B23" s="70" t="s">
-        <v>273</v>
-      </c>
-      <c r="C23" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="59" t="s">
-        <v>285</v>
-      </c>
-      <c r="E23" s="66"/>
-      <c r="F23" s="59" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="64"/>
-      <c r="B24" s="65"/>
-      <c r="C24" s="59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D24" s="59" t="s">
-        <v>286</v>
-      </c>
-      <c r="E24" s="66"/>
-      <c r="F24" s="59" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="64"/>
-      <c r="B25" s="65"/>
-      <c r="C25" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="59" t="s">
-        <v>287</v>
-      </c>
-      <c r="E25" s="68"/>
-      <c r="F25" s="59" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="64"/>
-      <c r="B26" s="65"/>
-      <c r="C26" s="59" t="s">
-        <v>295</v>
-      </c>
-      <c r="D26" s="59" t="s">
-        <v>296</v>
-      </c>
-      <c r="E26" s="69"/>
-      <c r="F26" s="59" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="64"/>
-      <c r="B27" s="65"/>
-      <c r="C27" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="59" t="s">
-        <v>288</v>
-      </c>
-      <c r="E27" s="69"/>
-      <c r="F27" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="64"/>
-      <c r="B28" s="65"/>
-      <c r="C28" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="59" t="s">
-        <v>289</v>
-      </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="64"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D29" s="59" t="s">
-        <v>290</v>
-      </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="64"/>
-      <c r="B30" s="65"/>
-      <c r="C30" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="59" t="s">
-        <v>291</v>
-      </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="64"/>
-      <c r="B31" s="65"/>
-      <c r="C31" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="59" t="s">
-        <v>292</v>
-      </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="64"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="74"/>
-      <c r="D32" s="74"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="74"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="64"/>
-      <c r="B33" s="76" t="s">
-        <v>360</v>
-      </c>
-      <c r="C33" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" s="59" t="s">
-        <v>361</v>
-      </c>
-      <c r="E33" s="66"/>
-      <c r="F33" s="59" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="64"/>
-      <c r="B34" s="76"/>
-      <c r="C34" s="59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="59" t="s">
-        <v>362</v>
-      </c>
-      <c r="E34" s="66"/>
-      <c r="F34" s="59" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="64"/>
-      <c r="B35" s="76"/>
-      <c r="C35" s="59" t="s">
-        <v>84</v>
-      </c>
-      <c r="D35" s="59" t="s">
-        <v>363</v>
-      </c>
-      <c r="E35" s="68"/>
-      <c r="F35" s="59" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="64"/>
-      <c r="B36" s="76"/>
-      <c r="C36" s="59" t="s">
-        <v>283</v>
-      </c>
-      <c r="D36" s="59" t="s">
-        <v>365</v>
-      </c>
-      <c r="E36" s="68"/>
-      <c r="F36" s="59" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="64"/>
-      <c r="B37" s="76"/>
-      <c r="C37" s="59" t="s">
-        <v>372</v>
-      </c>
-      <c r="D37" s="59" t="s">
-        <v>375</v>
-      </c>
-      <c r="E37" s="68"/>
-      <c r="F37" s="59" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="64"/>
-      <c r="B38" s="76"/>
-      <c r="C38" s="59" t="s">
-        <v>260</v>
-      </c>
-      <c r="D38" s="59" t="s">
-        <v>364</v>
-      </c>
-      <c r="E38" s="69"/>
-      <c r="F38" s="59" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="64"/>
-      <c r="B39" s="76"/>
-      <c r="C39" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D39" s="59" t="s">
-        <v>366</v>
-      </c>
-      <c r="E39" s="69"/>
-      <c r="F39" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="64"/>
-      <c r="B40" s="76"/>
-      <c r="C40" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D40" s="59" t="s">
-        <v>369</v>
-      </c>
-      <c r="E40" s="69"/>
-      <c r="F40" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="64"/>
-      <c r="B41" s="76"/>
-      <c r="C41" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="D41" s="59" t="s">
-        <v>381</v>
-      </c>
-      <c r="E41" s="69"/>
-      <c r="F41" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="64"/>
-      <c r="B42" s="76"/>
-      <c r="C42" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D42" s="59" t="s">
-        <v>367</v>
-      </c>
-      <c r="E42" s="69"/>
-      <c r="F42" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="64"/>
-      <c r="B43" s="76"/>
-      <c r="C43" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="59" t="s">
-        <v>368</v>
-      </c>
-      <c r="E43" s="68"/>
-      <c r="F43" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="64"/>
-      <c r="B44" s="76"/>
-      <c r="C44" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="59" t="s">
-        <v>370</v>
-      </c>
-      <c r="E44" s="68"/>
-      <c r="F44" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="64"/>
-      <c r="B45" s="76"/>
-      <c r="E45" s="68"/>
-    </row>
-    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="60" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="77" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="62" t="s">
-        <v>114</v>
-      </c>
-      <c r="D46" s="62" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" s="78"/>
-      <c r="F46" s="62" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="64"/>
-      <c r="B47" s="76"/>
-      <c r="C47" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" s="59" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="68"/>
-      <c r="F47" s="59" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="64"/>
-      <c r="B48" s="76"/>
-      <c r="C48" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="D48" s="59" t="s">
-        <v>134</v>
-      </c>
-      <c r="E48" s="69"/>
-      <c r="F48" s="59" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="64"/>
-      <c r="B49" s="76"/>
-      <c r="C49" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="D49" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" s="68"/>
-      <c r="F49" s="59" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="64"/>
-      <c r="B50" s="76"/>
-      <c r="C50" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D50" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="E50" s="68"/>
-      <c r="F50" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="64"/>
-      <c r="B51" s="76"/>
-      <c r="C51" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D51" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="E51" s="68"/>
-      <c r="F51" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="64"/>
-      <c r="B52" s="76"/>
-      <c r="C52" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D52" s="59" t="s">
-        <v>201</v>
-      </c>
-      <c r="E52" s="68"/>
-      <c r="F52" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="64"/>
-      <c r="B53" s="76"/>
-      <c r="C53" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D53" s="59" t="s">
-        <v>172</v>
-      </c>
-      <c r="E53" s="68"/>
-      <c r="F53" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="64"/>
-      <c r="B54" s="76"/>
-      <c r="C54" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D54" s="59" t="s">
-        <v>195</v>
-      </c>
-      <c r="E54" s="68"/>
-      <c r="F54" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="64"/>
-      <c r="B55" s="79"/>
-      <c r="C55" s="74"/>
-      <c r="D55" s="74"/>
-      <c r="E55" s="75"/>
-      <c r="F55" s="74"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="64"/>
-      <c r="B56" s="76" t="s">
-        <v>317</v>
-      </c>
-      <c r="C56" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="59" t="s">
-        <v>327</v>
-      </c>
-      <c r="E56" s="66"/>
-      <c r="F56" s="59" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="64"/>
-      <c r="B57" s="76"/>
-      <c r="C57" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" s="59" t="s">
-        <v>328</v>
-      </c>
-      <c r="E57" s="68"/>
-      <c r="F57" s="59" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="64"/>
-      <c r="B58" s="76"/>
-      <c r="C58" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="D58" s="59" t="s">
-        <v>329</v>
-      </c>
-      <c r="E58" s="69"/>
-      <c r="F58" s="59" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="64"/>
-      <c r="B59" s="76"/>
-      <c r="C59" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="59" t="s">
-        <v>330</v>
-      </c>
-      <c r="E59" s="68"/>
-      <c r="F59" s="59" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="64"/>
-      <c r="B60" s="76"/>
-      <c r="C60" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D60" s="59" t="s">
-        <v>331</v>
-      </c>
-      <c r="E60" s="68"/>
-      <c r="F60" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="64"/>
-      <c r="B61" s="76"/>
-      <c r="C61" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D61" s="59" t="s">
-        <v>332</v>
-      </c>
-      <c r="E61" s="68"/>
-      <c r="F61" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="64"/>
-      <c r="B62" s="76"/>
-      <c r="C62" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D62" s="59" t="s">
-        <v>333</v>
-      </c>
-      <c r="E62" s="68"/>
-      <c r="F62" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="64"/>
-      <c r="B63" s="76"/>
-      <c r="C63" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D63" s="59" t="s">
-        <v>334</v>
-      </c>
-      <c r="E63" s="68"/>
-      <c r="F63" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="64"/>
-      <c r="B64" s="76"/>
-      <c r="C64" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D64" s="59" t="s">
-        <v>335</v>
-      </c>
-      <c r="E64" s="68"/>
-      <c r="F64" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="64"/>
-      <c r="B65" s="79"/>
-      <c r="E65" s="68"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="64"/>
-      <c r="B66" s="80" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="D66" s="71" t="s">
-        <v>101</v>
-      </c>
-      <c r="E66" s="81"/>
-      <c r="F66" s="71" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="64"/>
-      <c r="B67" s="76"/>
-      <c r="C67" s="59" t="s">
-        <v>114</v>
-      </c>
-      <c r="D67" s="59" t="s">
-        <v>103</v>
-      </c>
-      <c r="E67" s="68"/>
-      <c r="F67" s="59" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="64"/>
-      <c r="B68" s="65"/>
-      <c r="C68" s="59" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" s="59" t="s">
-        <v>113</v>
-      </c>
-      <c r="E68" s="66"/>
-      <c r="F68" s="59" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="64"/>
-      <c r="B69" s="65"/>
-      <c r="C69" s="59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D69" s="59" t="s">
-        <v>186</v>
-      </c>
-      <c r="E69" s="66"/>
-      <c r="F69" s="59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="64"/>
-      <c r="B70" s="65"/>
-      <c r="C70" s="59" t="s">
-        <v>127</v>
-      </c>
-      <c r="D70" s="59" t="s">
-        <v>125</v>
-      </c>
-      <c r="E70" s="66"/>
-      <c r="F70" s="59" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="64"/>
-      <c r="B71" s="65"/>
-      <c r="C71" s="59" t="s">
-        <v>128</v>
-      </c>
-      <c r="D71" s="59" t="s">
-        <v>126</v>
-      </c>
-      <c r="E71" s="68"/>
-      <c r="F71" s="59" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="64"/>
-      <c r="B72" s="65"/>
-      <c r="C72" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D72" s="59" t="s">
-        <v>146</v>
-      </c>
-      <c r="E72" s="66"/>
-      <c r="F72" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="64"/>
-      <c r="B73" s="65"/>
-      <c r="C73" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D73" s="59" t="s">
-        <v>158</v>
-      </c>
-      <c r="E73" s="68"/>
-      <c r="F73" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="64"/>
-      <c r="B74" s="65"/>
-      <c r="C74" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D74" s="59" t="s">
-        <v>202</v>
-      </c>
-      <c r="E74" s="68"/>
-      <c r="F74" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="64"/>
-      <c r="B75" s="65"/>
-      <c r="C75" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D75" s="59" t="s">
-        <v>171</v>
-      </c>
-      <c r="E75" s="68"/>
-      <c r="F75" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="64"/>
-      <c r="B76" s="65"/>
-      <c r="C76" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D76" s="59" t="s">
-        <v>194</v>
-      </c>
-      <c r="E76" s="68"/>
-      <c r="F76" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="82"/>
-      <c r="B77" s="83"/>
-      <c r="C77" s="84"/>
-      <c r="D77" s="84"/>
-      <c r="E77" s="85"/>
-      <c r="F77" s="84"/>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="60" t="s">
-        <v>72</v>
-      </c>
-      <c r="B78" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="C78" s="62" t="s">
-        <v>118</v>
-      </c>
-      <c r="D78" s="62" t="s">
-        <v>117</v>
-      </c>
-      <c r="E78" s="78"/>
-      <c r="F78" s="62" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="64"/>
-      <c r="B79" s="86"/>
-      <c r="C79" s="87" t="s">
-        <v>154</v>
-      </c>
-      <c r="D79" s="87" t="s">
-        <v>153</v>
-      </c>
-      <c r="E79" s="88"/>
-      <c r="F79" s="87" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="64"/>
-      <c r="B80" s="73"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="74"/>
-      <c r="E80" s="89"/>
-      <c r="F80" s="74"/>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="64"/>
-      <c r="B81" s="70" t="s">
-        <v>343</v>
-      </c>
-      <c r="C81" s="71" t="s">
-        <v>346</v>
-      </c>
-      <c r="D81" s="71" t="s">
-        <v>349</v>
-      </c>
-      <c r="E81" s="72"/>
-      <c r="F81" s="71" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="64"/>
-      <c r="B82" s="86"/>
-      <c r="C82" s="87" t="s">
-        <v>347</v>
-      </c>
-      <c r="D82" s="87" t="s">
-        <v>350</v>
-      </c>
-      <c r="E82" s="88"/>
-      <c r="F82" s="87" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="64"/>
-      <c r="B83" s="73"/>
-      <c r="C83" s="74"/>
-      <c r="D83" s="74"/>
-      <c r="E83" s="89"/>
-      <c r="F83" s="74"/>
-    </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="64"/>
-      <c r="B84" s="86" t="s">
-        <v>385</v>
-      </c>
-      <c r="C84" s="87" t="s">
-        <v>386</v>
-      </c>
-      <c r="D84" s="87" t="s">
-        <v>388</v>
-      </c>
-      <c r="E84" s="88"/>
-      <c r="F84" s="87" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="64"/>
-      <c r="B85" s="86"/>
-      <c r="C85" s="59" t="s">
-        <v>387</v>
-      </c>
-      <c r="D85" s="59" t="s">
-        <v>389</v>
-      </c>
-      <c r="E85" s="66"/>
-      <c r="F85" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="64"/>
-      <c r="B86" s="86"/>
-      <c r="E86" s="66"/>
-    </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="64"/>
-      <c r="B87" s="80" t="s">
-        <v>4</v>
-      </c>
-      <c r="C87" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="D87" s="71" t="s">
-        <v>100</v>
-      </c>
-      <c r="E87" s="81"/>
-      <c r="F87" s="71" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="64"/>
-      <c r="B88" s="76"/>
-      <c r="C88" s="59" t="s">
-        <v>108</v>
-      </c>
-      <c r="D88" s="59" t="s">
-        <v>110</v>
-      </c>
-      <c r="E88" s="1"/>
-      <c r="F88" s="59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="64"/>
-      <c r="B89" s="76"/>
-      <c r="C89" s="59" t="s">
-        <v>123</v>
-      </c>
-      <c r="D89" s="59" t="s">
-        <v>122</v>
-      </c>
-      <c r="E89" s="1"/>
-      <c r="F89" s="59" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="64"/>
-      <c r="B90" s="76"/>
-      <c r="C90" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D90" s="59" t="s">
-        <v>145</v>
-      </c>
-      <c r="E90" s="66"/>
-      <c r="F90" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="64"/>
-      <c r="B91" s="76"/>
-      <c r="C91" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D91" s="59" t="s">
-        <v>157</v>
-      </c>
-      <c r="E91" s="69"/>
-      <c r="F91" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="64"/>
-      <c r="B92" s="76"/>
-      <c r="C92" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="D92" s="59" t="s">
-        <v>163</v>
-      </c>
-      <c r="E92" s="66"/>
-      <c r="F92" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="64"/>
-      <c r="B93" s="76"/>
-      <c r="C93" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D93" s="59" t="s">
-        <v>200</v>
-      </c>
-      <c r="E93" s="66"/>
-      <c r="F93" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="64"/>
-      <c r="B94" s="76"/>
-      <c r="C94" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D94" s="59" t="s">
-        <v>170</v>
-      </c>
-      <c r="E94" s="68"/>
-      <c r="F94" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="64"/>
-      <c r="B95" s="76"/>
-      <c r="C95" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D95" s="59" t="s">
-        <v>192</v>
-      </c>
-      <c r="E95" s="68"/>
-      <c r="F95" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="64"/>
-      <c r="B96" s="79"/>
-    </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="64"/>
-      <c r="B97" s="80" t="s">
-        <v>5</v>
-      </c>
-      <c r="C97" s="71" t="s">
-        <v>97</v>
-      </c>
-      <c r="D97" s="71" t="s">
-        <v>102</v>
-      </c>
-      <c r="E97" s="81"/>
-      <c r="F97" s="71" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="64"/>
-      <c r="B98" s="76"/>
-      <c r="C98" s="59" t="s">
-        <v>109</v>
-      </c>
-      <c r="D98" s="59" t="s">
-        <v>107</v>
-      </c>
-      <c r="E98" s="1"/>
-      <c r="F98" s="59" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="64"/>
-      <c r="B99" s="76"/>
-      <c r="C99" s="59" t="s">
-        <v>121</v>
-      </c>
-      <c r="D99" s="59" t="s">
-        <v>120</v>
-      </c>
-      <c r="E99" s="1"/>
-      <c r="F99" s="59" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="64"/>
-      <c r="B100" s="76"/>
-      <c r="C100" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D100" s="59" t="s">
-        <v>143</v>
-      </c>
-      <c r="E100" s="1"/>
-      <c r="F100" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="64"/>
-      <c r="B101" s="76"/>
-      <c r="C101" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="D101" s="59" t="s">
-        <v>155</v>
-      </c>
-      <c r="E101" s="69"/>
-      <c r="F101" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="64"/>
-      <c r="B102" s="76"/>
-      <c r="C102" s="59" t="s">
-        <v>162</v>
-      </c>
-      <c r="D102" s="59" t="s">
-        <v>161</v>
-      </c>
-      <c r="E102" s="90"/>
-      <c r="F102" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="64"/>
-      <c r="B103" s="76"/>
-      <c r="C103" s="59" t="s">
-        <v>198</v>
-      </c>
-      <c r="D103" s="59" t="s">
-        <v>199</v>
-      </c>
-      <c r="E103" s="90"/>
-      <c r="F103" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="64"/>
-      <c r="B104" s="76"/>
-      <c r="C104" s="59" t="s">
-        <v>168</v>
-      </c>
-      <c r="D104" s="59" t="s">
-        <v>169</v>
-      </c>
-      <c r="E104" s="68"/>
-      <c r="F104" s="59" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="64"/>
-      <c r="B105" s="76"/>
-      <c r="C105" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="D105" s="59" t="s">
-        <v>191</v>
-      </c>
-      <c r="E105" s="68"/>
-      <c r="F105" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="82"/>
-      <c r="B106" s="91"/>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="60" t="s">
-        <v>76</v>
-      </c>
-      <c r="B107" s="61" t="s">
-        <v>73</v>
-      </c>
-      <c r="C107" s="62" t="s">
-        <v>130</v>
-      </c>
-      <c r="D107" s="62" t="s">
-        <v>129</v>
-      </c>
-      <c r="E107" s="63"/>
-      <c r="F107" s="62" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="64"/>
-      <c r="B108" s="65"/>
-      <c r="C108" s="59" t="s">
-        <v>230</v>
-      </c>
-      <c r="D108" s="59" t="s">
-        <v>229</v>
-      </c>
-      <c r="E108" s="68"/>
-      <c r="F108" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="64"/>
-      <c r="B109" s="65"/>
-      <c r="C109" s="59" t="s">
-        <v>151</v>
-      </c>
-      <c r="D109" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="E109" s="68"/>
-      <c r="F109" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="64"/>
-      <c r="B110" s="73"/>
-      <c r="C110" s="74"/>
-      <c r="D110" s="74"/>
-      <c r="E110" s="75"/>
-      <c r="F110" s="74"/>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="64"/>
-      <c r="B111" s="70" t="s">
-        <v>303</v>
-      </c>
-      <c r="C111" s="59" t="s">
-        <v>304</v>
-      </c>
-      <c r="D111" s="59" t="s">
-        <v>305</v>
-      </c>
-      <c r="E111" s="68"/>
-      <c r="F111" s="59" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="64"/>
-      <c r="B112" s="65"/>
-      <c r="C112" s="59" t="s">
-        <v>308</v>
-      </c>
-      <c r="D112" s="59" t="s">
-        <v>306</v>
-      </c>
-      <c r="E112" s="68"/>
-      <c r="F112" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="64"/>
-      <c r="B113" s="65"/>
-      <c r="C113" s="59" t="s">
-        <v>309</v>
-      </c>
-      <c r="D113" s="59" t="s">
-        <v>307</v>
-      </c>
-      <c r="E113" s="68"/>
-      <c r="F113" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="64"/>
-      <c r="B114" s="73"/>
-      <c r="E114" s="68"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="64"/>
-      <c r="B115" s="70" t="s">
-        <v>79</v>
-      </c>
-      <c r="C115" s="71" t="s">
-        <v>132</v>
-      </c>
-      <c r="D115" s="71" t="s">
-        <v>131</v>
-      </c>
-      <c r="E115" s="81"/>
-      <c r="F115" s="71" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="64"/>
-      <c r="B116" s="65"/>
-      <c r="C116" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="D116" s="59" t="s">
-        <v>149</v>
-      </c>
-      <c r="E116" s="68"/>
-      <c r="F116" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="64"/>
-      <c r="B117" s="73"/>
-      <c r="C117" s="74"/>
-      <c r="D117" s="74"/>
-      <c r="E117" s="75"/>
-      <c r="F117" s="74"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="64"/>
-      <c r="B118" s="70" t="s">
-        <v>262</v>
-      </c>
-      <c r="C118" s="59" t="s">
-        <v>261</v>
-      </c>
-      <c r="D118" s="59" t="s">
-        <v>264</v>
-      </c>
-      <c r="E118" s="68"/>
-      <c r="F118" s="59" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="64"/>
-      <c r="B119" s="65"/>
-      <c r="C119" s="59" t="s">
-        <v>263</v>
-      </c>
-      <c r="D119" s="59" t="s">
-        <v>265</v>
-      </c>
-      <c r="E119" s="68"/>
-      <c r="F119" s="59" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="82"/>
-      <c r="B120" s="83"/>
-      <c r="C120" s="84"/>
-      <c r="D120" s="84"/>
-      <c r="E120" s="85"/>
-      <c r="F120" s="84"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="60" t="s">
-        <v>164</v>
-      </c>
-      <c r="B121" s="61" t="s">
-        <v>13</v>
-      </c>
-      <c r="C121" s="62" t="s">
-        <v>174</v>
-      </c>
-      <c r="D121" s="62" t="s">
-        <v>173</v>
-      </c>
-      <c r="E121" s="62"/>
-      <c r="F121" s="62" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="92"/>
-      <c r="B122" s="65"/>
-      <c r="C122" s="59" t="s">
+      <c r="B122" s="82"/>
+      <c r="C122" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="D122" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="D122" s="59" t="s">
-        <v>176</v>
-      </c>
-      <c r="F122" s="59" t="s">
-        <v>141</v>
+      <c r="F122" s="44" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="92"/>
-      <c r="B123" s="73"/>
-      <c r="C123" s="74"/>
-      <c r="D123" s="74"/>
-      <c r="E123" s="74"/>
-      <c r="F123" s="74"/>
+      <c r="B123" s="84"/>
+      <c r="C123" s="53"/>
+      <c r="D123" s="53"/>
+      <c r="E123" s="53"/>
+      <c r="F123" s="53"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="92"/>
-      <c r="B124" s="70" t="s">
-        <v>184</v>
-      </c>
-      <c r="C124" s="59" t="s">
-        <v>166</v>
-      </c>
-      <c r="D124" s="59" t="s">
+      <c r="B124" s="83" t="s">
+        <v>183</v>
+      </c>
+      <c r="C124" s="44" t="s">
         <v>165</v>
       </c>
-      <c r="F124" s="59" t="s">
-        <v>150</v>
+      <c r="D124" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="F124" s="44" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="92"/>
-      <c r="B125" s="65"/>
-      <c r="C125" s="59" t="s">
-        <v>182</v>
-      </c>
-      <c r="D125" s="59" t="s">
-        <v>311</v>
-      </c>
-      <c r="F125" s="59" t="s">
-        <v>150</v>
+      <c r="B125" s="82"/>
+      <c r="C125" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="D125" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="F125" s="44" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="92"/>
-      <c r="B126" s="65"/>
-      <c r="C126" s="59" t="s">
-        <v>178</v>
-      </c>
-      <c r="D126" s="59" t="s">
+      <c r="B126" s="82"/>
+      <c r="C126" s="44" t="s">
         <v>177</v>
       </c>
-      <c r="F126" s="59" t="s">
-        <v>150</v>
+      <c r="D126" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="F126" s="44" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="92"/>
-      <c r="B127" s="65"/>
-      <c r="C127" s="59" t="s">
-        <v>180</v>
-      </c>
-      <c r="D127" s="59" t="s">
+      <c r="B127" s="82"/>
+      <c r="C127" s="44" t="s">
         <v>179</v>
       </c>
-      <c r="F127" s="59" t="s">
-        <v>150</v>
+      <c r="D127" s="44" t="s">
+        <v>178</v>
+      </c>
+      <c r="F127" s="44" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="92"/>
-      <c r="B128" s="65"/>
-      <c r="C128" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="D128" s="59" t="s">
-        <v>181</v>
-      </c>
-      <c r="F128" s="59" t="s">
-        <v>150</v>
+      <c r="B128" s="82"/>
+      <c r="C128" s="44" t="s">
+        <v>182</v>
+      </c>
+      <c r="D128" s="44" t="s">
+        <v>180</v>
+      </c>
+      <c r="F128" s="44" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="92"/>
-      <c r="B129" s="65"/>
-      <c r="C129" s="59" t="s">
-        <v>193</v>
-      </c>
-      <c r="D129" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="F129" s="59" t="s">
-        <v>150</v>
+      <c r="B129" s="82"/>
+      <c r="C129" s="44" t="s">
+        <v>191</v>
+      </c>
+      <c r="D129" s="44" t="s">
+        <v>187</v>
+      </c>
+      <c r="F129" s="44" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="92"/>
-      <c r="B130" s="65"/>
+      <c r="B130" s="82"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="92"/>
-      <c r="B131" s="70" t="s">
+      <c r="B131" s="83" t="s">
+        <v>206</v>
+      </c>
+      <c r="C131" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="D131" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="E131" s="51"/>
+      <c r="F131" s="51" t="s">
         <v>208</v>
-      </c>
-      <c r="C131" s="71" t="s">
-        <v>205</v>
-      </c>
-      <c r="D131" s="71" t="s">
-        <v>209</v>
-      </c>
-      <c r="E131" s="71"/>
-      <c r="F131" s="71" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="92"/>
-      <c r="B132" s="65"/>
-      <c r="C132" s="59" t="s">
-        <v>206</v>
-      </c>
-      <c r="D132" s="59" t="s">
-        <v>212</v>
-      </c>
-      <c r="F132" s="59" t="s">
+      <c r="B132" s="82"/>
+      <c r="C132" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="D132" s="44" t="s">
         <v>210</v>
+      </c>
+      <c r="F132" s="44" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="92"/>
-      <c r="B133" s="65"/>
-      <c r="C133" s="59" t="s">
-        <v>217</v>
-      </c>
-      <c r="D133" s="59" t="s">
-        <v>216</v>
-      </c>
-      <c r="F133" s="59" t="s">
-        <v>221</v>
+      <c r="B133" s="82"/>
+      <c r="C133" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="D133" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="F133" s="44" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="92"/>
-      <c r="B134" s="65"/>
-      <c r="C134" s="59" t="s">
-        <v>207</v>
-      </c>
-      <c r="D134" s="59" t="s">
-        <v>211</v>
-      </c>
-      <c r="F134" s="59" t="s">
-        <v>210</v>
+      <c r="B134" s="82"/>
+      <c r="C134" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="D134" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="F134" s="44" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="92"/>
-      <c r="B135" s="65"/>
-      <c r="C135" s="59" t="s">
-        <v>312</v>
-      </c>
-      <c r="D135" s="59" t="s">
-        <v>313</v>
-      </c>
-      <c r="F135" s="59" t="s">
-        <v>316</v>
+      <c r="B135" s="82"/>
+      <c r="C135" s="44" t="s">
+        <v>310</v>
+      </c>
+      <c r="D135" s="44" t="s">
+        <v>311</v>
+      </c>
+      <c r="F135" s="44" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="92"/>
-      <c r="B136" s="65"/>
-      <c r="C136" s="59" t="s">
-        <v>336</v>
-      </c>
-      <c r="D136" s="59" t="s">
-        <v>337</v>
-      </c>
-      <c r="F136" s="59" t="s">
-        <v>316</v>
+      <c r="B136" s="82"/>
+      <c r="C136" s="44" t="s">
+        <v>334</v>
+      </c>
+      <c r="D136" s="44" t="s">
+        <v>335</v>
+      </c>
+      <c r="F136" s="44" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="92"/>
-      <c r="B137" s="65"/>
-      <c r="C137" s="59" t="s">
-        <v>338</v>
-      </c>
-      <c r="D137" s="59" t="s">
-        <v>339</v>
-      </c>
-      <c r="F137" s="59" t="s">
-        <v>316</v>
+      <c r="B137" s="82"/>
+      <c r="C137" s="44" t="s">
+        <v>336</v>
+      </c>
+      <c r="D137" s="44" t="s">
+        <v>337</v>
+      </c>
+      <c r="F137" s="44" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="92"/>
-      <c r="B138" s="65"/>
-      <c r="C138" s="59" t="s">
-        <v>219</v>
-      </c>
-      <c r="D138" s="59" t="s">
+      <c r="B138" s="82"/>
+      <c r="C138" s="44" t="s">
+        <v>217</v>
+      </c>
+      <c r="D138" s="44" t="s">
+        <v>216</v>
+      </c>
+      <c r="F138" s="44" t="s">
         <v>218</v>
-      </c>
-      <c r="F138" s="59" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="92"/>
-      <c r="B139" s="65"/>
-      <c r="C139" s="59" t="s">
-        <v>223</v>
-      </c>
-      <c r="D139" s="59" t="s">
-        <v>213</v>
-      </c>
-      <c r="F139" s="59" t="s">
-        <v>214</v>
+      <c r="B139" s="82"/>
+      <c r="C139" s="44" t="s">
+        <v>221</v>
+      </c>
+      <c r="D139" s="44" t="s">
+        <v>211</v>
+      </c>
+      <c r="F139" s="44" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="92"/>
-      <c r="B140" s="65"/>
-      <c r="C140" s="59" t="s">
-        <v>204</v>
-      </c>
-      <c r="D140" s="59" t="s">
-        <v>222</v>
-      </c>
-      <c r="F140" s="59" t="s">
-        <v>214</v>
+      <c r="B140" s="82"/>
+      <c r="C140" s="44" t="s">
+        <v>202</v>
+      </c>
+      <c r="D140" s="44" t="s">
+        <v>220</v>
+      </c>
+      <c r="F140" s="44" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="92"/>
-      <c r="B141" s="65"/>
-      <c r="C141" s="59" t="s">
-        <v>266</v>
-      </c>
-      <c r="D141" s="59" t="s">
-        <v>371</v>
-      </c>
-      <c r="F141" s="59" t="s">
-        <v>214</v>
+      <c r="B141" s="82"/>
+      <c r="C141" s="44" t="s">
+        <v>264</v>
+      </c>
+      <c r="D141" s="44" t="s">
+        <v>369</v>
+      </c>
+      <c r="F141" s="44" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="92"/>
-      <c r="B142" s="65"/>
-      <c r="C142" s="59" t="s">
-        <v>268</v>
-      </c>
-      <c r="D142" s="59" t="s">
-        <v>267</v>
-      </c>
-      <c r="F142" s="59" t="s">
-        <v>215</v>
+      <c r="B142" s="82"/>
+      <c r="C142" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="D142" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="F142" s="44" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="92"/>
-      <c r="B143" s="65"/>
+      <c r="B143" s="82"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="92"/>
-      <c r="B144" s="70" t="s">
+      <c r="B144" s="83" t="s">
+        <v>222</v>
+      </c>
+      <c r="C144" s="51" t="s">
         <v>224</v>
       </c>
-      <c r="C144" s="71" t="s">
-        <v>226</v>
-      </c>
-      <c r="D144" s="71" t="s">
-        <v>225</v>
-      </c>
-      <c r="E144" s="71"/>
-      <c r="F144" s="71" t="s">
-        <v>210</v>
+      <c r="D144" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="E144" s="51"/>
+      <c r="F144" s="51" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="92"/>
-      <c r="B145" s="86"/>
-      <c r="C145" s="59" t="s">
+      <c r="B145" s="78"/>
+      <c r="C145" s="44" t="s">
+        <v>312</v>
+      </c>
+      <c r="D145" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="F145" s="44" t="s">
         <v>314</v>
-      </c>
-      <c r="D145" s="59" t="s">
-        <v>315</v>
-      </c>
-      <c r="F145" s="59" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="92"/>
-      <c r="B146" s="86"/>
-      <c r="C146" s="59" t="s">
-        <v>227</v>
-      </c>
-      <c r="D146" s="59" t="s">
-        <v>228</v>
-      </c>
-      <c r="F146" s="59" t="s">
-        <v>214</v>
+      <c r="B146" s="78"/>
+      <c r="C146" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="D146" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="F146" s="44" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="92"/>
-      <c r="B147" s="86"/>
-      <c r="C147" s="59" t="s">
-        <v>269</v>
-      </c>
-      <c r="D147" s="59" t="s">
-        <v>270</v>
-      </c>
-      <c r="F147" s="59" t="s">
-        <v>214</v>
+      <c r="B147" s="78"/>
+      <c r="C147" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="D147" s="44" t="s">
+        <v>268</v>
+      </c>
+      <c r="F147" s="44" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="92"/>
-      <c r="B148" s="86"/>
-      <c r="C148" s="59" t="s">
-        <v>271</v>
-      </c>
-      <c r="D148" s="59" t="s">
-        <v>310</v>
-      </c>
-      <c r="F148" s="59" t="s">
-        <v>215</v>
+      <c r="B148" s="78"/>
+      <c r="C148" s="44" t="s">
+        <v>269</v>
+      </c>
+      <c r="D148" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="F148" s="44" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="92"/>
-      <c r="B149" s="73"/>
+      <c r="B149" s="84"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" s="92"/>
-      <c r="B150" s="70" t="s">
+      <c r="B150" s="83" t="s">
+        <v>388</v>
+      </c>
+      <c r="C150" s="51" t="s">
+        <v>389</v>
+      </c>
+      <c r="D150" s="51" t="s">
         <v>390</v>
       </c>
-      <c r="C150" s="71" t="s">
-        <v>391</v>
-      </c>
-      <c r="D150" s="71" t="s">
-        <v>392</v>
-      </c>
-      <c r="E150" s="71"/>
-      <c r="F150" s="71" t="s">
-        <v>275</v>
+      <c r="E150" s="51"/>
+      <c r="F150" s="51" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" s="92"/>
-      <c r="B151" s="65"/>
-      <c r="C151" s="59" t="s">
-        <v>393</v>
-      </c>
-      <c r="D151" s="59" t="s">
-        <v>394</v>
-      </c>
-      <c r="F151" s="59" t="s">
-        <v>275</v>
+      <c r="B151" s="82"/>
+      <c r="C151" s="44" t="s">
+        <v>391</v>
+      </c>
+      <c r="D151" s="44" t="s">
+        <v>392</v>
+      </c>
+      <c r="F151" s="44" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="B150:B151"/>
+    <mergeCell ref="B144:B149"/>
+    <mergeCell ref="A121:A151"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="B124:B130"/>
+    <mergeCell ref="B131:B143"/>
+    <mergeCell ref="B121:B123"/>
+    <mergeCell ref="A107:A120"/>
+    <mergeCell ref="B115:B117"/>
+    <mergeCell ref="B107:B110"/>
+    <mergeCell ref="B111:B114"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
@@ -5377,17 +5388,6 @@
     <mergeCell ref="B97:B106"/>
     <mergeCell ref="B78:B80"/>
     <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="B144:B149"/>
-    <mergeCell ref="A121:A151"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="B124:B130"/>
-    <mergeCell ref="B131:B143"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="A107:A120"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="B111:B114"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_H2_Methanolreaktor_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55259489-E8F6-46AD-93F3-6F6BBC09001B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00B9B83E-7CBB-4442-89BA-8596911F45B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-53868" yWindow="3444" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -180,7 +180,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="670" uniqueCount="393">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -865,12 +865,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>Methanolsynthese</t>
   </si>
   <si>
@@ -1096,13 +1090,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1657,38 +1645,41 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1698,9 +1689,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2118,7 +2106,7 @@
         <v>26</v>
       </c>
       <c r="E4" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>83</v>
@@ -2175,19 +2163,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="64"/>
       <c r="B8" s="75" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E8" s="14">
         <v>1.5</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2197,7 +2185,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E9" s="9">
         <v>285.39999999999998</v>
@@ -2213,13 +2201,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="36" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E10" s="40">
         <v>0</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2229,14 +2217,14 @@
         <v>11</v>
       </c>
       <c r="D11" s="36" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E11" s="38">
         <f>0.05*5110</f>
         <v>255.5</v>
       </c>
       <c r="F11" s="39" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -2246,29 +2234,29 @@
         <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E12" s="9">
         <v>0.189</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="64"/>
       <c r="B13" s="72"/>
       <c r="C13" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E13" s="9">
         <v>1.375</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2278,7 +2266,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E14" s="12">
         <v>25</v>
@@ -2294,7 +2282,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E15" s="16">
         <v>0.08</v>
@@ -2306,13 +2294,13 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="64"/>
       <c r="B16" s="75" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E16" s="17">
         <v>3.7</v>
@@ -2328,13 +2316,13 @@
         <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E17" s="11">
         <v>0.27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2344,13 +2332,13 @@
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E18" s="11">
         <v>700</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2360,7 +2348,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E19" s="11">
         <v>0.02</v>
@@ -2376,7 +2364,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E20" s="11">
         <v>20</v>
@@ -2392,7 +2380,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E21" s="16">
         <v>0.05</v>
@@ -2404,35 +2392,35 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="64"/>
       <c r="B22" s="77" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E22" s="9">
         <v>0.2</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="64"/>
       <c r="B23" s="77"/>
       <c r="C23" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E23" s="9">
         <v>0.92800000000000005</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2442,23 +2430,23 @@
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E24" s="9">
         <v>1640</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="64"/>
       <c r="B25" s="77"/>
       <c r="C25" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E25" s="11">
         <v>0.04</v>
@@ -2471,48 +2459,48 @@
       <c r="A26" s="64"/>
       <c r="B26" s="77"/>
       <c r="C26" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E26" s="11">
         <v>2.5</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="64"/>
       <c r="B27" s="77"/>
       <c r="C27" s="6" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E27" s="11">
         <v>1.5</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="64"/>
       <c r="B28" s="77"/>
       <c r="C28" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E28" s="11">
         <v>1.5E-3</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2522,7 +2510,7 @@
         <v>13</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E29" s="12">
         <v>25</v>
@@ -2538,7 +2526,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E30" s="11">
         <v>0.08</v>
@@ -2682,19 +2670,19 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="64"/>
       <c r="B39" s="70" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E39" s="18">
         <v>2.83</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2704,7 +2692,7 @@
         <v>11</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E40" s="11">
         <v>0.03</v>
@@ -2720,7 +2708,7 @@
         <v>13</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E41" s="12">
         <v>30</v>
@@ -2736,7 +2724,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E42" s="11">
         <v>7.3999999999999999E-4</v>
@@ -2752,7 +2740,7 @@
         <v>35</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E43" s="11">
         <v>0.98</v>
@@ -2768,7 +2756,7 @@
         <v>36</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E44" s="11">
         <v>0.98</v>
@@ -2784,7 +2772,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E45" s="11">
         <v>0.05</v>
@@ -2800,7 +2788,7 @@
         <v>88</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E46" s="16">
         <v>0</v>
@@ -2995,13 +2983,13 @@
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="66"/>
       <c r="B58" s="25" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="D58" s="26" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="E58" s="27">
         <v>5</v>
@@ -3013,13 +3001,13 @@
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="66"/>
       <c r="B59" s="28" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C59" s="29" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E59" s="30">
         <v>0</v>
@@ -3270,7 +3258,7 @@
         <v>78</v>
       </c>
       <c r="E74" s="24">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F74" s="23" t="s">
         <v>19</v>
@@ -3279,19 +3267,19 @@
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="64"/>
       <c r="B75" s="5" t="s">
+        <v>295</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D75" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="C75" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>299</v>
-      </c>
       <c r="E75" s="11">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3315,19 +3303,19 @@
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="65"/>
       <c r="B77" s="3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C77" s="20" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D77" s="20" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E77" s="21">
         <v>-0.6</v>
       </c>
       <c r="F77" s="20" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3354,7 +3342,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="44" customWidth="1"/>
@@ -3387,10 +3375,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="79" t="s">
+      <c r="A2" s="82" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="81" t="s">
+      <c r="B2" s="85" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="45" t="s">
@@ -3405,8 +3393,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="80"/>
-      <c r="B3" s="82"/>
+      <c r="A3" s="86"/>
+      <c r="B3" s="79"/>
       <c r="C3" s="44" t="s">
         <v>107</v>
       </c>
@@ -3419,8 +3407,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="80"/>
-      <c r="B4" s="82"/>
+      <c r="A4" s="86"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="44" t="s">
         <v>84</v>
       </c>
@@ -3433,8 +3421,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="80"/>
-      <c r="B5" s="82"/>
+      <c r="A5" s="86"/>
+      <c r="B5" s="79"/>
       <c r="C5" s="44" t="s">
         <v>138</v>
       </c>
@@ -3447,8 +3435,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="80"/>
-      <c r="B6" s="82"/>
+      <c r="A6" s="86"/>
+      <c r="B6" s="79"/>
       <c r="C6" s="44" t="s">
         <v>141</v>
       </c>
@@ -3461,8 +3449,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="80"/>
-      <c r="B7" s="82"/>
+      <c r="A7" s="86"/>
+      <c r="B7" s="79"/>
       <c r="C7" s="44" t="s">
         <v>155</v>
       </c>
@@ -3475,8 +3463,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="80"/>
-      <c r="B8" s="82"/>
+      <c r="A8" s="86"/>
+      <c r="B8" s="79"/>
       <c r="C8" s="44" t="s">
         <v>196</v>
       </c>
@@ -3489,8 +3477,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="80"/>
-      <c r="B9" s="82"/>
+      <c r="A9" s="86"/>
+      <c r="B9" s="79"/>
       <c r="C9" s="44" t="s">
         <v>167</v>
       </c>
@@ -3503,8 +3491,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="80"/>
-      <c r="B10" s="82"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="79"/>
       <c r="C10" s="44" t="s">
         <v>188</v>
       </c>
@@ -3517,20 +3505,20 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="80"/>
-      <c r="B11" s="82"/>
+      <c r="A11" s="86"/>
+      <c r="B11" s="79"/>
       <c r="E11" s="49"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="80"/>
-      <c r="B12" s="83" t="s">
-        <v>229</v>
+      <c r="A12" s="86"/>
+      <c r="B12" s="78" t="s">
+        <v>227</v>
       </c>
       <c r="C12" s="51" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="51" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E12" s="52"/>
       <c r="F12" s="51" t="s">
@@ -3538,27 +3526,27 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="80"/>
-      <c r="B13" s="82"/>
+      <c r="A13" s="86"/>
+      <c r="B13" s="79"/>
       <c r="C13" s="44" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D13" s="44" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E13" s="47"/>
       <c r="F13" s="44" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="80"/>
-      <c r="B14" s="82"/>
+      <c r="A14" s="86"/>
+      <c r="B14" s="79"/>
       <c r="C14" s="44" t="s">
         <v>139</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E14" s="47"/>
       <c r="F14" s="47" t="s">
@@ -3566,27 +3554,27 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="80"/>
-      <c r="B15" s="82"/>
+      <c r="A15" s="86"/>
+      <c r="B15" s="79"/>
       <c r="C15" s="44" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E15" s="49"/>
       <c r="F15" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="80"/>
-      <c r="B16" s="82"/>
+      <c r="A16" s="86"/>
+      <c r="B16" s="79"/>
       <c r="C16" s="44" t="s">
         <v>84</v>
       </c>
       <c r="D16" s="44" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E16" s="47"/>
       <c r="F16" s="44" t="s">
@@ -3594,13 +3582,13 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="80"/>
-      <c r="B17" s="82"/>
+      <c r="A17" s="86"/>
+      <c r="B17" s="79"/>
       <c r="C17" s="44" t="s">
         <v>141</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17" s="47"/>
       <c r="F17" s="44" t="s">
@@ -3608,13 +3596,13 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="80"/>
-      <c r="B18" s="82"/>
+      <c r="A18" s="86"/>
+      <c r="B18" s="79"/>
       <c r="C18" s="44" t="s">
         <v>155</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E18" s="50"/>
       <c r="F18" s="44" t="s">
@@ -3622,13 +3610,13 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="80"/>
-      <c r="B19" s="82"/>
+      <c r="A19" s="86"/>
+      <c r="B19" s="79"/>
       <c r="C19" s="44" t="s">
         <v>196</v>
       </c>
       <c r="D19" s="44" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E19" s="50"/>
       <c r="F19" s="44" t="s">
@@ -3636,13 +3624,13 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="80"/>
-      <c r="B20" s="82"/>
+      <c r="A20" s="86"/>
+      <c r="B20" s="79"/>
       <c r="C20" s="44" t="s">
         <v>167</v>
       </c>
       <c r="D20" s="44" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E20" s="50"/>
       <c r="F20" s="44" t="s">
@@ -3650,13 +3638,13 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="80"/>
-      <c r="B21" s="82"/>
+      <c r="A21" s="86"/>
+      <c r="B21" s="79"/>
       <c r="C21" s="44" t="s">
         <v>188</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E21" s="50"/>
       <c r="F21" s="44" t="s">
@@ -3664,37 +3652,37 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="80"/>
-      <c r="B22" s="84"/>
+      <c r="A22" s="86"/>
+      <c r="B22" s="81"/>
       <c r="C22" s="53"/>
       <c r="D22" s="53"/>
       <c r="E22" s="54"/>
       <c r="F22" s="53"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="80"/>
-      <c r="B23" s="83" t="s">
-        <v>271</v>
+      <c r="A23" s="86"/>
+      <c r="B23" s="78" t="s">
+        <v>269</v>
       </c>
       <c r="C23" s="44" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E23" s="47"/>
       <c r="F23" s="44" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="80"/>
-      <c r="B24" s="82"/>
+      <c r="A24" s="86"/>
+      <c r="B24" s="79"/>
       <c r="C24" s="44" t="s">
         <v>107</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E24" s="47"/>
       <c r="F24" s="44" t="s">
@@ -3702,41 +3690,41 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="80"/>
-      <c r="B25" s="82"/>
+      <c r="A25" s="86"/>
+      <c r="B25" s="79"/>
       <c r="C25" s="44" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="44" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E25" s="49"/>
       <c r="F25" s="44" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="80"/>
-      <c r="B26" s="82"/>
+      <c r="A26" s="86"/>
+      <c r="B26" s="79"/>
       <c r="C26" s="44" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D26" s="44" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E26" s="50"/>
       <c r="F26" s="44" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="80"/>
-      <c r="B27" s="82"/>
+      <c r="A27" s="86"/>
+      <c r="B27" s="79"/>
       <c r="C27" s="44" t="s">
         <v>141</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E27" s="50"/>
       <c r="F27" s="44" t="s">
@@ -3744,13 +3732,13 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="80"/>
-      <c r="B28" s="82"/>
+      <c r="A28" s="86"/>
+      <c r="B28" s="79"/>
       <c r="C28" s="44" t="s">
         <v>155</v>
       </c>
       <c r="D28" s="44" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E28" s="50"/>
       <c r="F28" s="44" t="s">
@@ -3758,13 +3746,13 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="80"/>
-      <c r="B29" s="82"/>
+      <c r="A29" s="86"/>
+      <c r="B29" s="79"/>
       <c r="C29" s="44" t="s">
         <v>196</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E29" s="50"/>
       <c r="F29" s="44" t="s">
@@ -3772,13 +3760,13 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="80"/>
-      <c r="B30" s="82"/>
+      <c r="A30" s="86"/>
+      <c r="B30" s="79"/>
       <c r="C30" s="44" t="s">
         <v>167</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E30" s="49"/>
       <c r="F30" s="44" t="s">
@@ -3786,13 +3774,13 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="80"/>
-      <c r="B31" s="82"/>
+      <c r="A31" s="86"/>
+      <c r="B31" s="79"/>
       <c r="C31" s="44" t="s">
         <v>188</v>
       </c>
       <c r="D31" s="44" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E31" s="49"/>
       <c r="F31" s="44" t="s">
@@ -3800,23 +3788,23 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="80"/>
-      <c r="B32" s="84"/>
+      <c r="A32" s="86"/>
+      <c r="B32" s="81"/>
       <c r="C32" s="53"/>
       <c r="D32" s="53"/>
       <c r="E32" s="54"/>
       <c r="F32" s="53"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="80"/>
-      <c r="B33" s="85" t="s">
-        <v>358</v>
+      <c r="A33" s="86"/>
+      <c r="B33" s="88" t="s">
+        <v>354</v>
       </c>
       <c r="C33" s="44" t="s">
         <v>96</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E33" s="47"/>
       <c r="F33" s="44" t="s">
@@ -3824,13 +3812,13 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="80"/>
-      <c r="B34" s="85"/>
+      <c r="A34" s="86"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="44" t="s">
         <v>107</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E34" s="47"/>
       <c r="F34" s="44" t="s">
@@ -3838,13 +3826,13 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="80"/>
-      <c r="B35" s="85"/>
+      <c r="A35" s="86"/>
+      <c r="B35" s="88"/>
       <c r="C35" s="44" t="s">
         <v>84</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E35" s="49"/>
       <c r="F35" s="44" t="s">
@@ -3852,55 +3840,55 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="80"/>
-      <c r="B36" s="85"/>
+      <c r="A36" s="86"/>
+      <c r="B36" s="88"/>
       <c r="C36" s="44" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E36" s="49"/>
       <c r="F36" s="44" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="80"/>
-      <c r="B37" s="85"/>
+      <c r="A37" s="86"/>
+      <c r="B37" s="88"/>
       <c r="C37" s="44" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E37" s="49"/>
       <c r="F37" s="44" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="80"/>
-      <c r="B38" s="85"/>
+      <c r="A38" s="86"/>
+      <c r="B38" s="88"/>
       <c r="C38" s="44" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D38" s="44" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E38" s="50"/>
       <c r="F38" s="44" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="80"/>
-      <c r="B39" s="85"/>
+      <c r="A39" s="86"/>
+      <c r="B39" s="88"/>
       <c r="C39" s="44" t="s">
         <v>141</v>
       </c>
       <c r="D39" s="44" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E39" s="50"/>
       <c r="F39" s="44" t="s">
@@ -3908,13 +3896,13 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="80"/>
-      <c r="B40" s="85"/>
+      <c r="A40" s="86"/>
+      <c r="B40" s="88"/>
       <c r="C40" s="44" t="s">
         <v>155</v>
       </c>
       <c r="D40" s="44" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E40" s="50"/>
       <c r="F40" s="44" t="s">
@@ -3922,13 +3910,13 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="80"/>
-      <c r="B41" s="85"/>
+      <c r="A41" s="86"/>
+      <c r="B41" s="88"/>
       <c r="C41" s="44" t="s">
         <v>161</v>
       </c>
       <c r="D41" s="44" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E41" s="50"/>
       <c r="F41" s="44" t="s">
@@ -3936,13 +3924,13 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="80"/>
-      <c r="B42" s="85"/>
+      <c r="A42" s="86"/>
+      <c r="B42" s="88"/>
       <c r="C42" s="44" t="s">
         <v>196</v>
       </c>
       <c r="D42" s="44" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E42" s="50"/>
       <c r="F42" s="44" t="s">
@@ -3950,13 +3938,13 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="80"/>
-      <c r="B43" s="85"/>
+      <c r="A43" s="86"/>
+      <c r="B43" s="88"/>
       <c r="C43" s="44" t="s">
         <v>167</v>
       </c>
       <c r="D43" s="44" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E43" s="49"/>
       <c r="F43" s="44" t="s">
@@ -3964,13 +3952,13 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="80"/>
-      <c r="B44" s="85"/>
+      <c r="A44" s="86"/>
+      <c r="B44" s="88"/>
       <c r="C44" s="44" t="s">
         <v>188</v>
       </c>
       <c r="D44" s="44" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E44" s="49"/>
       <c r="F44" s="44" t="s">
@@ -3978,15 +3966,15 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="80"/>
-      <c r="B45" s="85"/>
+      <c r="A45" s="86"/>
+      <c r="B45" s="88"/>
       <c r="E45" s="49"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="79" t="s">
+      <c r="A46" s="82" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="89" t="s">
+      <c r="B46" s="90" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="45" t="s">
@@ -3997,12 +3985,12 @@
       </c>
       <c r="E46" s="55"/>
       <c r="F46" s="45" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="80"/>
-      <c r="B47" s="85"/>
+      <c r="A47" s="86"/>
+      <c r="B47" s="88"/>
       <c r="C47" s="44" t="s">
         <v>111</v>
       </c>
@@ -4011,12 +3999,12 @@
       </c>
       <c r="E47" s="49"/>
       <c r="F47" s="44" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="80"/>
-      <c r="B48" s="85"/>
+      <c r="A48" s="86"/>
+      <c r="B48" s="88"/>
       <c r="C48" s="44" t="s">
         <v>135</v>
       </c>
@@ -4029,8 +4017,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="80"/>
-      <c r="B49" s="85"/>
+      <c r="A49" s="86"/>
+      <c r="B49" s="88"/>
       <c r="C49" s="44" t="s">
         <v>136</v>
       </c>
@@ -4043,8 +4031,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="80"/>
-      <c r="B50" s="85"/>
+      <c r="A50" s="86"/>
+      <c r="B50" s="88"/>
       <c r="C50" s="44" t="s">
         <v>141</v>
       </c>
@@ -4057,8 +4045,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="80"/>
-      <c r="B51" s="85"/>
+      <c r="A51" s="86"/>
+      <c r="B51" s="88"/>
       <c r="C51" s="44" t="s">
         <v>155</v>
       </c>
@@ -4071,8 +4059,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="80"/>
-      <c r="B52" s="85"/>
+      <c r="A52" s="86"/>
+      <c r="B52" s="88"/>
       <c r="C52" s="44" t="s">
         <v>196</v>
       </c>
@@ -4085,8 +4073,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="80"/>
-      <c r="B53" s="85"/>
+      <c r="A53" s="86"/>
+      <c r="B53" s="88"/>
       <c r="C53" s="44" t="s">
         <v>167</v>
       </c>
@@ -4099,8 +4087,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="80"/>
-      <c r="B54" s="85"/>
+      <c r="A54" s="86"/>
+      <c r="B54" s="88"/>
       <c r="C54" s="44" t="s">
         <v>188</v>
       </c>
@@ -4113,79 +4101,79 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="80"/>
-      <c r="B55" s="90"/>
+      <c r="A55" s="86"/>
+      <c r="B55" s="91"/>
       <c r="C55" s="53"/>
       <c r="D55" s="53"/>
       <c r="E55" s="54"/>
       <c r="F55" s="53"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="80"/>
-      <c r="B56" s="85" t="s">
-        <v>315</v>
+      <c r="A56" s="86"/>
+      <c r="B56" s="88" t="s">
+        <v>311</v>
       </c>
       <c r="C56" s="44" t="s">
         <v>113</v>
       </c>
       <c r="D56" s="44" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E56" s="47"/>
       <c r="F56" s="44" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="80"/>
-      <c r="B57" s="85"/>
+      <c r="A57" s="86"/>
+      <c r="B57" s="88"/>
       <c r="C57" s="44" t="s">
         <v>111</v>
       </c>
       <c r="D57" s="44" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E57" s="49"/>
       <c r="F57" s="44" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="80"/>
-      <c r="B58" s="85"/>
+      <c r="A58" s="86"/>
+      <c r="B58" s="88"/>
       <c r="C58" s="44" t="s">
         <v>135</v>
       </c>
       <c r="D58" s="44" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E58" s="50"/>
       <c r="F58" s="44" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="80"/>
-      <c r="B59" s="85"/>
+      <c r="A59" s="86"/>
+      <c r="B59" s="88"/>
       <c r="C59" s="44" t="s">
         <v>136</v>
       </c>
       <c r="D59" s="44" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E59" s="49"/>
       <c r="F59" s="44" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="80"/>
-      <c r="B60" s="85"/>
+      <c r="A60" s="86"/>
+      <c r="B60" s="88"/>
       <c r="C60" s="44" t="s">
         <v>141</v>
       </c>
       <c r="D60" s="44" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E60" s="49"/>
       <c r="F60" s="44" t="s">
@@ -4193,13 +4181,13 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="80"/>
-      <c r="B61" s="85"/>
+      <c r="A61" s="86"/>
+      <c r="B61" s="88"/>
       <c r="C61" s="44" t="s">
         <v>155</v>
       </c>
       <c r="D61" s="44" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E61" s="49"/>
       <c r="F61" s="44" t="s">
@@ -4207,13 +4195,13 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="80"/>
-      <c r="B62" s="85"/>
+      <c r="A62" s="86"/>
+      <c r="B62" s="88"/>
       <c r="C62" s="44" t="s">
         <v>196</v>
       </c>
       <c r="D62" s="44" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E62" s="49"/>
       <c r="F62" s="44" t="s">
@@ -4221,13 +4209,13 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="80"/>
-      <c r="B63" s="85"/>
+      <c r="A63" s="86"/>
+      <c r="B63" s="88"/>
       <c r="C63" s="44" t="s">
         <v>167</v>
       </c>
       <c r="D63" s="44" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E63" s="49"/>
       <c r="F63" s="44" t="s">
@@ -4235,13 +4223,13 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="80"/>
-      <c r="B64" s="85"/>
+      <c r="A64" s="86"/>
+      <c r="B64" s="88"/>
       <c r="C64" s="44" t="s">
         <v>188</v>
       </c>
       <c r="D64" s="44" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E64" s="49"/>
       <c r="F64" s="44" t="s">
@@ -4249,13 +4237,13 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="80"/>
-      <c r="B65" s="90"/>
+      <c r="A65" s="86"/>
+      <c r="B65" s="91"/>
       <c r="E65" s="49"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="80"/>
-      <c r="B66" s="87" t="s">
+      <c r="A66" s="86"/>
+      <c r="B66" s="89" t="s">
         <v>6</v>
       </c>
       <c r="C66" s="51" t="s">
@@ -4270,8 +4258,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="80"/>
-      <c r="B67" s="85"/>
+      <c r="A67" s="86"/>
+      <c r="B67" s="88"/>
       <c r="C67" s="44" t="s">
         <v>113</v>
       </c>
@@ -4284,8 +4272,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="80"/>
-      <c r="B68" s="82"/>
+      <c r="A68" s="86"/>
+      <c r="B68" s="79"/>
       <c r="C68" s="44" t="s">
         <v>111</v>
       </c>
@@ -4298,8 +4286,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="80"/>
-      <c r="B69" s="82"/>
+      <c r="A69" s="86"/>
+      <c r="B69" s="79"/>
       <c r="C69" s="44" t="s">
         <v>107</v>
       </c>
@@ -4312,8 +4300,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="80"/>
-      <c r="B70" s="82"/>
+      <c r="A70" s="86"/>
+      <c r="B70" s="79"/>
       <c r="C70" s="44" t="s">
         <v>126</v>
       </c>
@@ -4326,8 +4314,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="80"/>
-      <c r="B71" s="82"/>
+      <c r="A71" s="86"/>
+      <c r="B71" s="79"/>
       <c r="C71" s="44" t="s">
         <v>127</v>
       </c>
@@ -4340,8 +4328,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="80"/>
-      <c r="B72" s="82"/>
+      <c r="A72" s="86"/>
+      <c r="B72" s="79"/>
       <c r="C72" s="44" t="s">
         <v>141</v>
       </c>
@@ -4354,8 +4342,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="80"/>
-      <c r="B73" s="82"/>
+      <c r="A73" s="86"/>
+      <c r="B73" s="79"/>
       <c r="C73" s="44" t="s">
         <v>155</v>
       </c>
@@ -4368,8 +4356,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="80"/>
-      <c r="B74" s="82"/>
+      <c r="A74" s="86"/>
+      <c r="B74" s="79"/>
       <c r="C74" s="44" t="s">
         <v>196</v>
       </c>
@@ -4382,8 +4370,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="80"/>
-      <c r="B75" s="82"/>
+      <c r="A75" s="86"/>
+      <c r="B75" s="79"/>
       <c r="C75" s="44" t="s">
         <v>167</v>
       </c>
@@ -4396,8 +4384,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="80"/>
-      <c r="B76" s="82"/>
+      <c r="A76" s="86"/>
+      <c r="B76" s="79"/>
       <c r="C76" s="44" t="s">
         <v>188</v>
       </c>
@@ -4410,18 +4398,18 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="86"/>
-      <c r="B77" s="88"/>
+      <c r="A77" s="87"/>
+      <c r="B77" s="84"/>
       <c r="C77" s="57"/>
       <c r="D77" s="57"/>
       <c r="E77" s="58"/>
       <c r="F77" s="57"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="79" t="s">
+      <c r="A78" s="82" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="81" t="s">
+      <c r="B78" s="85" t="s">
         <v>73</v>
       </c>
       <c r="C78" s="45" t="s">
@@ -4436,8 +4424,8 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="80"/>
-      <c r="B79" s="78"/>
+      <c r="A79" s="86"/>
+      <c r="B79" s="80"/>
       <c r="C79" s="59" t="s">
         <v>153</v>
       </c>
@@ -4450,37 +4438,37 @@
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="80"/>
-      <c r="B80" s="84"/>
+      <c r="A80" s="86"/>
+      <c r="B80" s="81"/>
       <c r="C80" s="53"/>
       <c r="D80" s="53"/>
       <c r="E80" s="61"/>
       <c r="F80" s="53"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="80"/>
-      <c r="B81" s="83" t="s">
-        <v>341</v>
+      <c r="A81" s="86"/>
+      <c r="B81" s="78" t="s">
+        <v>337</v>
       </c>
       <c r="C81" s="51" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D81" s="51" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E81" s="52"/>
       <c r="F81" s="51" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="80"/>
-      <c r="B82" s="78"/>
+      <c r="A82" s="86"/>
+      <c r="B82" s="80"/>
       <c r="C82" s="59" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D82" s="59" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E82" s="60"/>
       <c r="F82" s="59" t="s">
@@ -4488,23 +4476,23 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="80"/>
-      <c r="B83" s="84"/>
+      <c r="A83" s="86"/>
+      <c r="B83" s="81"/>
       <c r="C83" s="53"/>
       <c r="D83" s="53"/>
       <c r="E83" s="61"/>
       <c r="F83" s="53"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="80"/>
-      <c r="B84" s="78" t="s">
-        <v>383</v>
+      <c r="A84" s="86"/>
+      <c r="B84" s="80" t="s">
+        <v>379</v>
       </c>
       <c r="C84" s="59" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D84" s="59" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E84" s="60"/>
       <c r="F84" s="59" t="s">
@@ -4512,13 +4500,13 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="80"/>
-      <c r="B85" s="78"/>
+      <c r="A85" s="86"/>
+      <c r="B85" s="80"/>
       <c r="C85" s="44" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="D85" s="44" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="E85" s="47"/>
       <c r="F85" s="44" t="s">
@@ -4526,13 +4514,13 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="80"/>
-      <c r="B86" s="78"/>
+      <c r="A86" s="86"/>
+      <c r="B86" s="80"/>
       <c r="E86" s="47"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="80"/>
-      <c r="B87" s="87" t="s">
+      <c r="A87" s="86"/>
+      <c r="B87" s="89" t="s">
         <v>4</v>
       </c>
       <c r="C87" s="51" t="s">
@@ -4547,8 +4535,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="80"/>
-      <c r="B88" s="85"/>
+      <c r="A88" s="86"/>
+      <c r="B88" s="88"/>
       <c r="C88" s="44" t="s">
         <v>107</v>
       </c>
@@ -4561,8 +4549,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="80"/>
-      <c r="B89" s="85"/>
+      <c r="A89" s="86"/>
+      <c r="B89" s="88"/>
       <c r="C89" s="44" t="s">
         <v>122</v>
       </c>
@@ -4575,8 +4563,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="80"/>
-      <c r="B90" s="85"/>
+      <c r="A90" s="86"/>
+      <c r="B90" s="88"/>
       <c r="C90" s="44" t="s">
         <v>141</v>
       </c>
@@ -4589,8 +4577,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="80"/>
-      <c r="B91" s="85"/>
+      <c r="A91" s="86"/>
+      <c r="B91" s="88"/>
       <c r="C91" s="44" t="s">
         <v>155</v>
       </c>
@@ -4603,8 +4591,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="80"/>
-      <c r="B92" s="85"/>
+      <c r="A92" s="86"/>
+      <c r="B92" s="88"/>
       <c r="C92" s="44" t="s">
         <v>161</v>
       </c>
@@ -4617,8 +4605,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="80"/>
-      <c r="B93" s="85"/>
+      <c r="A93" s="86"/>
+      <c r="B93" s="88"/>
       <c r="C93" s="44" t="s">
         <v>196</v>
       </c>
@@ -4631,8 +4619,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="80"/>
-      <c r="B94" s="85"/>
+      <c r="A94" s="86"/>
+      <c r="B94" s="88"/>
       <c r="C94" s="44" t="s">
         <v>167</v>
       </c>
@@ -4645,8 +4633,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="80"/>
-      <c r="B95" s="85"/>
+      <c r="A95" s="86"/>
+      <c r="B95" s="88"/>
       <c r="C95" s="44" t="s">
         <v>188</v>
       </c>
@@ -4659,12 +4647,12 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="80"/>
-      <c r="B96" s="90"/>
+      <c r="A96" s="86"/>
+      <c r="B96" s="91"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="80"/>
-      <c r="B97" s="87" t="s">
+      <c r="A97" s="86"/>
+      <c r="B97" s="89" t="s">
         <v>5</v>
       </c>
       <c r="C97" s="51" t="s">
@@ -4679,8 +4667,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="80"/>
-      <c r="B98" s="85"/>
+      <c r="A98" s="86"/>
+      <c r="B98" s="88"/>
       <c r="C98" s="44" t="s">
         <v>108</v>
       </c>
@@ -4693,8 +4681,8 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="80"/>
-      <c r="B99" s="85"/>
+      <c r="A99" s="86"/>
+      <c r="B99" s="88"/>
       <c r="C99" s="44" t="s">
         <v>120</v>
       </c>
@@ -4707,8 +4695,8 @@
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="80"/>
-      <c r="B100" s="85"/>
+      <c r="A100" s="86"/>
+      <c r="B100" s="88"/>
       <c r="C100" s="44" t="s">
         <v>141</v>
       </c>
@@ -4721,8 +4709,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="80"/>
-      <c r="B101" s="85"/>
+      <c r="A101" s="86"/>
+      <c r="B101" s="88"/>
       <c r="C101" s="44" t="s">
         <v>155</v>
       </c>
@@ -4735,8 +4723,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="80"/>
-      <c r="B102" s="85"/>
+      <c r="A102" s="86"/>
+      <c r="B102" s="88"/>
       <c r="C102" s="44" t="s">
         <v>161</v>
       </c>
@@ -4749,8 +4737,8 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="80"/>
-      <c r="B103" s="85"/>
+      <c r="A103" s="86"/>
+      <c r="B103" s="88"/>
       <c r="C103" s="44" t="s">
         <v>196</v>
       </c>
@@ -4763,8 +4751,8 @@
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="80"/>
-      <c r="B104" s="85"/>
+      <c r="A104" s="86"/>
+      <c r="B104" s="88"/>
       <c r="C104" s="44" t="s">
         <v>167</v>
       </c>
@@ -4777,8 +4765,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="80"/>
-      <c r="B105" s="85"/>
+      <c r="A105" s="86"/>
+      <c r="B105" s="88"/>
       <c r="C105" s="44" t="s">
         <v>188</v>
       </c>
@@ -4791,14 +4779,14 @@
       </c>
     </row>
     <row r="106" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="86"/>
-      <c r="B106" s="91"/>
+      <c r="A106" s="87"/>
+      <c r="B106" s="92"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="79" t="s">
+      <c r="A107" s="82" t="s">
         <v>76</v>
       </c>
-      <c r="B107" s="81" t="s">
+      <c r="B107" s="85" t="s">
         <v>73</v>
       </c>
       <c r="C107" s="45" t="s">
@@ -4813,13 +4801,13 @@
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="80"/>
-      <c r="B108" s="82"/>
+      <c r="A108" s="86"/>
+      <c r="B108" s="79"/>
       <c r="C108" s="44" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D108" s="44" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E108" s="49"/>
       <c r="F108" s="44" t="s">
@@ -4827,552 +4815,513 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="80"/>
-      <c r="B109" s="82"/>
-      <c r="C109" s="44" t="s">
-        <v>150</v>
-      </c>
-      <c r="D109" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="E109" s="49"/>
-      <c r="F109" s="44" t="s">
-        <v>149</v>
-      </c>
+      <c r="A109" s="86"/>
+      <c r="B109" s="81"/>
+      <c r="C109" s="53"/>
+      <c r="D109" s="53"/>
+      <c r="E109" s="54"/>
+      <c r="F109" s="53"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="80"/>
-      <c r="B110" s="84"/>
-      <c r="C110" s="53"/>
-      <c r="D110" s="53"/>
-      <c r="E110" s="54"/>
-      <c r="F110" s="53"/>
+      <c r="A110" s="86"/>
+      <c r="B110" s="78" t="s">
+        <v>299</v>
+      </c>
+      <c r="C110" s="44" t="s">
+        <v>300</v>
+      </c>
+      <c r="D110" s="44" t="s">
+        <v>301</v>
+      </c>
+      <c r="E110" s="49"/>
+      <c r="F110" s="44" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="80"/>
-      <c r="B111" s="83" t="s">
-        <v>301</v>
-      </c>
+      <c r="A111" s="86"/>
+      <c r="B111" s="79"/>
       <c r="C111" s="44" t="s">
+        <v>303</v>
+      </c>
+      <c r="D111" s="44" t="s">
         <v>302</v>
-      </c>
-      <c r="D111" s="44" t="s">
-        <v>303</v>
       </c>
       <c r="E111" s="49"/>
       <c r="F111" s="44" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="80"/>
-      <c r="B112" s="82"/>
-      <c r="C112" s="44" t="s">
-        <v>306</v>
-      </c>
-      <c r="D112" s="44" t="s">
-        <v>304</v>
-      </c>
+      <c r="A112" s="86"/>
+      <c r="B112" s="81"/>
       <c r="E112" s="49"/>
-      <c r="F112" s="44" t="s">
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="86"/>
+      <c r="B113" s="78" t="s">
+        <v>79</v>
+      </c>
+      <c r="C113" s="51" t="s">
+        <v>131</v>
+      </c>
+      <c r="D113" s="51" t="s">
+        <v>130</v>
+      </c>
+      <c r="E113" s="56"/>
+      <c r="F113" s="51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A114" s="86"/>
+      <c r="B114" s="79"/>
+      <c r="C114" s="44" t="s">
+        <v>151</v>
+      </c>
+      <c r="D114" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="E114" s="49"/>
+      <c r="F114" s="44" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="80"/>
-      <c r="B113" s="82"/>
-      <c r="C113" s="44" t="s">
-        <v>307</v>
-      </c>
-      <c r="D113" s="44" t="s">
-        <v>305</v>
-      </c>
-      <c r="E113" s="49"/>
-      <c r="F113" s="44" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="80"/>
-      <c r="B114" s="84"/>
-      <c r="E114" s="49"/>
-    </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="80"/>
-      <c r="B115" s="83" t="s">
-        <v>79</v>
-      </c>
-      <c r="C115" s="51" t="s">
-        <v>131</v>
-      </c>
-      <c r="D115" s="51" t="s">
-        <v>130</v>
-      </c>
-      <c r="E115" s="56"/>
-      <c r="F115" s="51" t="s">
-        <v>132</v>
-      </c>
+      <c r="A115" s="86"/>
+      <c r="B115" s="81"/>
+      <c r="C115" s="53"/>
+      <c r="D115" s="53"/>
+      <c r="E115" s="54"/>
+      <c r="F115" s="53"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="80"/>
-      <c r="B116" s="82"/>
+      <c r="A116" s="86"/>
+      <c r="B116" s="78" t="s">
+        <v>258</v>
+      </c>
       <c r="C116" s="44" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="D116" s="44" t="s">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="E116" s="49"/>
       <c r="F116" s="44" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="86"/>
+      <c r="B117" s="79"/>
+      <c r="C117" s="44" t="s">
+        <v>259</v>
+      </c>
+      <c r="D117" s="44" t="s">
+        <v>261</v>
+      </c>
+      <c r="E117" s="49"/>
+      <c r="F117" s="44" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="80"/>
-      <c r="B117" s="84"/>
-      <c r="C117" s="53"/>
-      <c r="D117" s="53"/>
-      <c r="E117" s="54"/>
-      <c r="F117" s="53"/>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="80"/>
-      <c r="B118" s="83" t="s">
-        <v>260</v>
-      </c>
-      <c r="C118" s="44" t="s">
-        <v>259</v>
-      </c>
-      <c r="D118" s="44" t="s">
-        <v>262</v>
-      </c>
-      <c r="E118" s="49"/>
-      <c r="F118" s="44" t="s">
-        <v>256</v>
-      </c>
+    <row r="118" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="87"/>
+      <c r="B118" s="84"/>
+      <c r="C118" s="57"/>
+      <c r="D118" s="57"/>
+      <c r="E118" s="58"/>
+      <c r="F118" s="57"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="80"/>
-      <c r="B119" s="82"/>
-      <c r="C119" s="44" t="s">
-        <v>261</v>
-      </c>
-      <c r="D119" s="44" t="s">
-        <v>263</v>
-      </c>
-      <c r="E119" s="49"/>
-      <c r="F119" s="44" t="s">
+      <c r="A119" s="82" t="s">
+        <v>163</v>
+      </c>
+      <c r="B119" s="85" t="s">
+        <v>13</v>
+      </c>
+      <c r="C119" s="45" t="s">
+        <v>173</v>
+      </c>
+      <c r="D119" s="45" t="s">
+        <v>172</v>
+      </c>
+      <c r="E119" s="45"/>
+      <c r="F119" s="45" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A120" s="83"/>
+      <c r="B120" s="79"/>
+      <c r="C120" s="44" t="s">
+        <v>174</v>
+      </c>
+      <c r="D120" s="44" t="s">
+        <v>175</v>
+      </c>
+      <c r="F120" s="44" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A121" s="83"/>
+      <c r="B121" s="81"/>
+      <c r="C121" s="53"/>
+      <c r="D121" s="53"/>
+      <c r="E121" s="53"/>
+      <c r="F121" s="53"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A122" s="83"/>
+      <c r="B122" s="78" t="s">
+        <v>183</v>
+      </c>
+      <c r="C122" s="44" t="s">
+        <v>165</v>
+      </c>
+      <c r="D122" s="44" t="s">
+        <v>164</v>
+      </c>
+      <c r="F122" s="44" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="120" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="86"/>
-      <c r="B120" s="88"/>
-      <c r="C120" s="57"/>
-      <c r="D120" s="57"/>
-      <c r="E120" s="58"/>
-      <c r="F120" s="57"/>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="79" t="s">
-        <v>163</v>
-      </c>
-      <c r="B121" s="81" t="s">
-        <v>13</v>
-      </c>
-      <c r="C121" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="D121" s="45" t="s">
-        <v>172</v>
-      </c>
-      <c r="E121" s="45"/>
-      <c r="F121" s="45" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="92"/>
-      <c r="B122" s="82"/>
-      <c r="C122" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="D122" s="44" t="s">
-        <v>175</v>
-      </c>
-      <c r="F122" s="44" t="s">
-        <v>140</v>
-      </c>
-    </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="92"/>
-      <c r="B123" s="84"/>
-      <c r="C123" s="53"/>
-      <c r="D123" s="53"/>
-      <c r="E123" s="53"/>
-      <c r="F123" s="53"/>
+      <c r="A123" s="83"/>
+      <c r="B123" s="79"/>
+      <c r="C123" s="44" t="s">
+        <v>181</v>
+      </c>
+      <c r="D123" s="44" t="s">
+        <v>305</v>
+      </c>
+      <c r="F123" s="44" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="92"/>
-      <c r="B124" s="83" t="s">
-        <v>183</v>
-      </c>
+      <c r="A124" s="83"/>
+      <c r="B124" s="79"/>
       <c r="C124" s="44" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D124" s="44" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F124" s="44" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="92"/>
-      <c r="B125" s="82"/>
+      <c r="A125" s="83"/>
+      <c r="B125" s="79"/>
       <c r="C125" s="44" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D125" s="44" t="s">
-        <v>309</v>
+        <v>178</v>
       </c>
       <c r="F125" s="44" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="92"/>
-      <c r="B126" s="82"/>
+      <c r="A126" s="83"/>
+      <c r="B126" s="79"/>
       <c r="C126" s="44" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D126" s="44" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F126" s="44" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="92"/>
-      <c r="B127" s="82"/>
+      <c r="A127" s="83"/>
+      <c r="B127" s="79"/>
       <c r="C127" s="44" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D127" s="44" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F127" s="44" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="92"/>
-      <c r="B128" s="82"/>
-      <c r="C128" s="44" t="s">
-        <v>182</v>
-      </c>
-      <c r="D128" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="F128" s="44" t="s">
-        <v>149</v>
-      </c>
+      <c r="A128" s="83"/>
+      <c r="B128" s="79"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="92"/>
-      <c r="B129" s="82"/>
-      <c r="C129" s="44" t="s">
-        <v>191</v>
-      </c>
-      <c r="D129" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="F129" s="44" t="s">
-        <v>149</v>
+      <c r="A129" s="83"/>
+      <c r="B129" s="78" t="s">
+        <v>206</v>
+      </c>
+      <c r="C129" s="51" t="s">
+        <v>203</v>
+      </c>
+      <c r="D129" s="51" t="s">
+        <v>207</v>
+      </c>
+      <c r="E129" s="51"/>
+      <c r="F129" s="51" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="92"/>
-      <c r="B130" s="82"/>
+      <c r="A130" s="83"/>
+      <c r="B130" s="79"/>
+      <c r="C130" s="44" t="s">
+        <v>204</v>
+      </c>
+      <c r="D130" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="F130" s="44" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="92"/>
-      <c r="B131" s="83" t="s">
-        <v>206</v>
-      </c>
-      <c r="C131" s="51" t="s">
-        <v>203</v>
-      </c>
-      <c r="D131" s="51" t="s">
-        <v>207</v>
-      </c>
-      <c r="E131" s="51"/>
-      <c r="F131" s="51" t="s">
-        <v>208</v>
+      <c r="A131" s="83"/>
+      <c r="B131" s="79"/>
+      <c r="C131" s="44" t="s">
+        <v>215</v>
+      </c>
+      <c r="D131" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="F131" s="44" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="92"/>
-      <c r="B132" s="82"/>
+      <c r="A132" s="83"/>
+      <c r="B132" s="79"/>
       <c r="C132" s="44" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D132" s="44" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F132" s="44" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="92"/>
-      <c r="B133" s="82"/>
+      <c r="A133" s="83"/>
+      <c r="B133" s="79"/>
       <c r="C133" s="44" t="s">
-        <v>215</v>
+        <v>306</v>
       </c>
       <c r="D133" s="44" t="s">
-        <v>214</v>
+        <v>307</v>
       </c>
       <c r="F133" s="44" t="s">
-        <v>219</v>
+        <v>310</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="92"/>
-      <c r="B134" s="82"/>
+      <c r="A134" s="83"/>
+      <c r="B134" s="79"/>
       <c r="C134" s="44" t="s">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="D134" s="44" t="s">
-        <v>209</v>
+        <v>331</v>
       </c>
       <c r="F134" s="44" t="s">
-        <v>208</v>
+        <v>310</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="92"/>
-      <c r="B135" s="82"/>
+      <c r="A135" s="83"/>
+      <c r="B135" s="79"/>
       <c r="C135" s="44" t="s">
+        <v>332</v>
+      </c>
+      <c r="D135" s="44" t="s">
+        <v>333</v>
+      </c>
+      <c r="F135" s="44" t="s">
         <v>310</v>
       </c>
-      <c r="D135" s="44" t="s">
-        <v>311</v>
-      </c>
-      <c r="F135" s="44" t="s">
-        <v>314</v>
-      </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="92"/>
-      <c r="B136" s="82"/>
+      <c r="A136" s="83"/>
+      <c r="B136" s="79"/>
       <c r="C136" s="44" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
       <c r="D136" s="44" t="s">
-        <v>335</v>
+        <v>216</v>
       </c>
       <c r="F136" s="44" t="s">
-        <v>314</v>
+        <v>218</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="92"/>
-      <c r="B137" s="82"/>
+      <c r="A137" s="83"/>
+      <c r="B137" s="79"/>
       <c r="C137" s="44" t="s">
-        <v>336</v>
+        <v>221</v>
       </c>
       <c r="D137" s="44" t="s">
-        <v>337</v>
+        <v>211</v>
       </c>
       <c r="F137" s="44" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="92"/>
-      <c r="B138" s="82"/>
+      <c r="A138" s="83"/>
+      <c r="B138" s="79"/>
       <c r="C138" s="44" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D138" s="44" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F138" s="44" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="92"/>
-      <c r="B139" s="82"/>
+      <c r="A139" s="83"/>
+      <c r="B139" s="79"/>
       <c r="C139" s="44" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="D139" s="44" t="s">
-        <v>211</v>
+        <v>365</v>
       </c>
       <c r="F139" s="44" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="92"/>
-      <c r="B140" s="82"/>
+      <c r="A140" s="83"/>
+      <c r="B140" s="79"/>
       <c r="C140" s="44" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="D140" s="44" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="F140" s="44" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A141" s="83"/>
+      <c r="B141" s="79"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A142" s="83"/>
+      <c r="B142" s="78" t="s">
+        <v>222</v>
+      </c>
+      <c r="C142" s="51" t="s">
+        <v>224</v>
+      </c>
+      <c r="D142" s="51" t="s">
+        <v>223</v>
+      </c>
+      <c r="E142" s="51"/>
+      <c r="F142" s="51" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A143" s="83"/>
+      <c r="B143" s="80"/>
+      <c r="C143" s="44" t="s">
+        <v>308</v>
+      </c>
+      <c r="D143" s="44" t="s">
+        <v>309</v>
+      </c>
+      <c r="F143" s="44" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A144" s="83"/>
+      <c r="B144" s="80"/>
+      <c r="C144" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="D144" s="44" t="s">
+        <v>226</v>
+      </c>
+      <c r="F144" s="44" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="92"/>
-      <c r="B141" s="82"/>
-      <c r="C141" s="44" t="s">
-        <v>264</v>
-      </c>
-      <c r="D141" s="44" t="s">
-        <v>369</v>
-      </c>
-      <c r="F141" s="44" t="s">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="83"/>
+      <c r="B145" s="80"/>
+      <c r="C145" s="44" t="s">
+        <v>265</v>
+      </c>
+      <c r="D145" s="44" t="s">
+        <v>266</v>
+      </c>
+      <c r="F145" s="44" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="92"/>
-      <c r="B142" s="82"/>
-      <c r="C142" s="44" t="s">
-        <v>266</v>
-      </c>
-      <c r="D142" s="44" t="s">
-        <v>265</v>
-      </c>
-      <c r="F142" s="44" t="s">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="83"/>
+      <c r="B146" s="80"/>
+      <c r="C146" s="44" t="s">
+        <v>267</v>
+      </c>
+      <c r="D146" s="44" t="s">
+        <v>304</v>
+      </c>
+      <c r="F146" s="44" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="92"/>
-      <c r="B143" s="82"/>
-    </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="92"/>
-      <c r="B144" s="83" t="s">
-        <v>222</v>
-      </c>
-      <c r="C144" s="51" t="s">
-        <v>224</v>
-      </c>
-      <c r="D144" s="51" t="s">
-        <v>223</v>
-      </c>
-      <c r="E144" s="51"/>
-      <c r="F144" s="51" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="92"/>
-      <c r="B145" s="78"/>
-      <c r="C145" s="44" t="s">
-        <v>312</v>
-      </c>
-      <c r="D145" s="44" t="s">
-        <v>313</v>
-      </c>
-      <c r="F145" s="44" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="92"/>
-      <c r="B146" s="78"/>
-      <c r="C146" s="44" t="s">
-        <v>225</v>
-      </c>
-      <c r="D146" s="44" t="s">
-        <v>226</v>
-      </c>
-      <c r="F146" s="44" t="s">
-        <v>212</v>
-      </c>
-    </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="92"/>
-      <c r="B147" s="78"/>
-      <c r="C147" s="44" t="s">
-        <v>267</v>
-      </c>
-      <c r="D147" s="44" t="s">
-        <v>268</v>
-      </c>
-      <c r="F147" s="44" t="s">
-        <v>212</v>
-      </c>
+      <c r="A147" s="83"/>
+      <c r="B147" s="81"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="92"/>
-      <c r="B148" s="78"/>
-      <c r="C148" s="44" t="s">
-        <v>269</v>
-      </c>
-      <c r="D148" s="44" t="s">
-        <v>308</v>
-      </c>
-      <c r="F148" s="44" t="s">
-        <v>213</v>
+      <c r="A148" s="83"/>
+      <c r="B148" s="78" t="s">
+        <v>384</v>
+      </c>
+      <c r="C148" s="51" t="s">
+        <v>385</v>
+      </c>
+      <c r="D148" s="51" t="s">
+        <v>386</v>
+      </c>
+      <c r="E148" s="51"/>
+      <c r="F148" s="51" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="92"/>
-      <c r="B149" s="84"/>
-    </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="92"/>
-      <c r="B150" s="83" t="s">
+      <c r="A149" s="83"/>
+      <c r="B149" s="79"/>
+      <c r="C149" s="44" t="s">
+        <v>387</v>
+      </c>
+      <c r="D149" s="44" t="s">
         <v>388</v>
       </c>
-      <c r="C150" s="51" t="s">
-        <v>389</v>
-      </c>
-      <c r="D150" s="51" t="s">
-        <v>390</v>
-      </c>
-      <c r="E150" s="51"/>
-      <c r="F150" s="51" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A151" s="92"/>
-      <c r="B151" s="82"/>
-      <c r="C151" s="44" t="s">
-        <v>391</v>
-      </c>
-      <c r="D151" s="44" t="s">
-        <v>392</v>
-      </c>
-      <c r="F151" s="44" t="s">
-        <v>273</v>
+      <c r="F149" s="44" t="s">
+        <v>271</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="B150:B151"/>
-    <mergeCell ref="B144:B149"/>
-    <mergeCell ref="A121:A151"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="B124:B130"/>
-    <mergeCell ref="B131:B143"/>
-    <mergeCell ref="B121:B123"/>
-    <mergeCell ref="A107:A120"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B107:B110"/>
-    <mergeCell ref="B111:B114"/>
     <mergeCell ref="B84:B86"/>
     <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
@@ -5388,6 +5337,17 @@
     <mergeCell ref="B97:B106"/>
     <mergeCell ref="B78:B80"/>
     <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="A119:A149"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="B122:B128"/>
+    <mergeCell ref="B129:B141"/>
+    <mergeCell ref="B119:B121"/>
+    <mergeCell ref="A107:A118"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B110:B112"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
